--- a/src/inventory/Syl.xlsx
+++ b/src/inventory/Syl.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="656">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -281,19 +281,19 @@
     <t>৳12,450.00</t>
   </si>
   <si>
-    <t>৳16,275.00</t>
-  </si>
-  <si>
-    <t>৳33,460.00</t>
+    <t>৳15,112.50</t>
+  </si>
+  <si>
+    <t>৳31,070.00</t>
   </si>
   <si>
     <t>৳1,476.19</t>
   </si>
   <si>
-    <t>৳14,761.90</t>
-  </si>
-  <si>
-    <t>৳25,900.00</t>
+    <t>৳11,809.52</t>
+  </si>
+  <si>
+    <t>৳20,720.00</t>
   </si>
   <si>
     <t>৳7,770.00</t>
@@ -317,10 +317,10 @@
     <t>৳1,458.82</t>
   </si>
   <si>
-    <t>৳17,505.88</t>
-  </si>
-  <si>
-    <t>৳28,680.00</t>
+    <t>৳16,047.06</t>
+  </si>
+  <si>
+    <t>৳26,290.00</t>
   </si>
   <si>
     <t>109-0101-008</t>
@@ -719,27 +719,15 @@
     <t>৳2,800.00</t>
   </si>
   <si>
-    <t>109-0102-063</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 063</t>
+    <t>109-0102-064</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 064</t>
   </si>
   <si>
     <t>৳950.00</t>
   </si>
   <si>
-    <t>109-0102-064</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 064</t>
-  </si>
-  <si>
-    <t>109-0102-070</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 070</t>
-  </si>
-  <si>
     <t>109-0102-071</t>
   </si>
   <si>
@@ -857,9 +845,6 @@
     <t>৳275.24</t>
   </si>
   <si>
-    <t>৳550.47</t>
-  </si>
-  <si>
     <t>1105-0301-001</t>
   </si>
   <si>
@@ -1010,7 +995,10 @@
     <t>৳522.28</t>
   </si>
   <si>
-    <t>৳2,089.14</t>
+    <t>৳1,566.85</t>
+  </si>
+  <si>
+    <t>৳2,370.00</t>
   </si>
   <si>
     <t>105-0201-035</t>
@@ -1154,9 +1142,6 @@
     <t>৳214.93</t>
   </si>
   <si>
-    <t>৳2,370.00</t>
-  </si>
-  <si>
     <t>৳2,200.00</t>
   </si>
   <si>
@@ -1535,6 +1520,9 @@
     <t>৳175.00</t>
   </si>
   <si>
+    <t>৳525.00</t>
+  </si>
+  <si>
     <t>105-0401-008</t>
   </si>
   <si>
@@ -1673,21 +1661,21 @@
     <t>৳140.00</t>
   </si>
   <si>
+    <t>105-0201-032</t>
+  </si>
+  <si>
+    <t>Full Sleeve White Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>৳209.53</t>
+  </si>
+  <si>
+    <t>৳1,047.64</t>
+  </si>
+  <si>
     <t>৳420.00</t>
   </si>
   <si>
-    <t>105-0201-032</t>
-  </si>
-  <si>
-    <t>Full Sleeve White Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>৳209.53</t>
-  </si>
-  <si>
-    <t>৳1,047.64</t>
-  </si>
-  <si>
     <t>105-0201-030</t>
   </si>
   <si>
@@ -1736,9 +1724,6 @@
     <t>৳145.83</t>
   </si>
   <si>
-    <t>৳729.17</t>
-  </si>
-  <si>
     <t>105-0101-379</t>
   </si>
   <si>
@@ -1790,15 +1775,6 @@
     <t>Men / 30% OFF,MEN,SHIRT,CASUAL SHIRT,HALF SLEEVE,Draft Items</t>
   </si>
   <si>
-    <t>107-0100-040</t>
-  </si>
-  <si>
-    <t>Mint Belt Blue Boxer Brief</t>
-  </si>
-  <si>
-    <t>Men / 30% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
-  </si>
-  <si>
     <t>109-0102-004</t>
   </si>
   <si>
@@ -1853,9 +1829,6 @@
     <t>৳5,900.00</t>
   </si>
   <si>
-    <t>৳3,840.00</t>
-  </si>
-  <si>
     <t>109-0102-052</t>
   </si>
   <si>
@@ -1949,61 +1922,58 @@
     <t>৳2,980.00</t>
   </si>
   <si>
+    <t>৳4,770.00</t>
+  </si>
+  <si>
+    <t>102-0501-005</t>
+  </si>
+  <si>
+    <t>Formal Shirt 005</t>
+  </si>
+  <si>
+    <t>৳4,050.00</t>
+  </si>
+  <si>
+    <t>102-0501-006-</t>
+  </si>
+  <si>
+    <t>Formal Shirt 006</t>
+  </si>
+  <si>
+    <t>102-0501-006</t>
+  </si>
+  <si>
+    <t>৳5,400.00</t>
+  </si>
+  <si>
+    <t>102-0501-008</t>
+  </si>
+  <si>
+    <t>Formal Shirt 008</t>
+  </si>
+  <si>
+    <t>৳1,490.00</t>
+  </si>
+  <si>
+    <t>৳4,470.00</t>
+  </si>
+  <si>
+    <t>102-0501-009</t>
+  </si>
+  <si>
+    <t>Formal Shirt 009</t>
+  </si>
+  <si>
+    <t>102-0501-011</t>
+  </si>
+  <si>
+    <t>Formal Shirt 011</t>
+  </si>
+  <si>
+    <t>৳9,540.00</t>
+  </si>
+  <si>
     <t>৳3,180.00</t>
-  </si>
-  <si>
-    <t>৳6,360.00</t>
-  </si>
-  <si>
-    <t>৳4,770.00</t>
-  </si>
-  <si>
-    <t>102-0501-005</t>
-  </si>
-  <si>
-    <t>Formal Shirt 005</t>
-  </si>
-  <si>
-    <t>৳4,050.00</t>
-  </si>
-  <si>
-    <t>102-0501-006-</t>
-  </si>
-  <si>
-    <t>Formal Shirt 006</t>
-  </si>
-  <si>
-    <t>102-0501-006</t>
-  </si>
-  <si>
-    <t>৳5,400.00</t>
-  </si>
-  <si>
-    <t>102-0501-008</t>
-  </si>
-  <si>
-    <t>Formal Shirt 008</t>
-  </si>
-  <si>
-    <t>৳1,490.00</t>
-  </si>
-  <si>
-    <t>৳4,470.00</t>
-  </si>
-  <si>
-    <t>102-0501-009</t>
-  </si>
-  <si>
-    <t>Formal Shirt 009</t>
-  </si>
-  <si>
-    <t>102-0501-011</t>
-  </si>
-  <si>
-    <t>Formal Shirt 011</t>
-  </si>
-  <si>
-    <t>৳9,540.00</t>
   </si>
   <si>
     <t>102-0501-007</t>
@@ -2352,7 +2322,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I368"/>
+  <dimension ref="A1:I362"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3438,7 +3408,7 @@
         <v>43</v>
       </c>
       <c r="F42">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="G42" t="s">
         <v>68</v>
@@ -3464,7 +3434,7 @@
         <v>43</v>
       </c>
       <c r="F43">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G43" t="s">
         <v>90</v>
@@ -3594,7 +3564,7 @@
         <v>43</v>
       </c>
       <c r="F48">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G48" t="s">
         <v>99</v>
@@ -4656,209 +4626,215 @@
         <v>131</v>
       </c>
       <c r="I90" t="s">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
+        <v>231</v>
+      </c>
+      <c r="B91" t="s">
+        <v>232</v>
+      </c>
+      <c r="C91" t="s">
+        <v>146</v>
+      </c>
+      <c r="E91" t="s">
+        <v>137</v>
+      </c>
+      <c r="F91">
+        <v>5.0</v>
+      </c>
+      <c r="G91" t="s">
         <v>239</v>
       </c>
-      <c r="B91" t="s">
+      <c r="H91" t="s">
         <v>240</v>
       </c>
-      <c r="E91" t="s">
-        <v>130</v>
-      </c>
-      <c r="F91">
-        <v>1.0</v>
-      </c>
-      <c r="G91" t="s">
-        <v>131</v>
-      </c>
-      <c r="H91" t="s">
-        <v>131</v>
-      </c>
       <c r="I91" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B92" t="s">
-        <v>242</v>
+        <v>243</v>
+      </c>
+      <c r="C92" t="s">
+        <v>168</v>
       </c>
       <c r="E92" t="s">
-        <v>130</v>
+        <v>244</v>
       </c>
       <c r="F92">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G92" t="s">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="H92" t="s">
-        <v>131</v>
+        <v>246</v>
       </c>
       <c r="I92" t="s">
-        <v>78</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B93" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C93" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E93" t="s">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="F93">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G93" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="H93" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="I93" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B94" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C94" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="E94" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F94">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G94" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H94" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I94" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B95" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C95" t="s">
         <v>136</v>
       </c>
       <c r="E95" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="F95">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G95" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B96" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C96" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="E96" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F96">
         <v>5.0</v>
       </c>
       <c r="G96" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H96" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I96" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="B97" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C97" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="E97" t="s">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="F97">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G97" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="H97" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I97" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B98" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C98" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="E98" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="F98">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G98" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="H98" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I98" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -4869,192 +4845,192 @@
         <v>232</v>
       </c>
       <c r="C99" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E99" t="s">
         <v>137</v>
       </c>
       <c r="F99">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G99" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="H99" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I99" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B100" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C100" t="s">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="E100" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F100">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G100" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H100" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I100" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="B101" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="C101" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E101" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="F101">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G101" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H101" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="I101" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B102" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C102" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E102" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F102">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G102" t="s">
-        <v>274</v>
+        <v>105</v>
       </c>
       <c r="H102" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I102" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B103" t="s">
-        <v>278</v>
-      </c>
-      <c r="C103" t="s">
-        <v>171</v>
+        <v>281</v>
       </c>
       <c r="E103" t="s">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="F103">
         <v>2.0</v>
       </c>
       <c r="G103" t="s">
-        <v>279</v>
+        <v>229</v>
       </c>
       <c r="H103" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="I103" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B104" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C104" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E104" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F104">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G104" t="s">
         <v>105</v>
       </c>
       <c r="H104" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I104" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>285</v>
+        <v>207</v>
       </c>
       <c r="B105" t="s">
-        <v>286</v>
+        <v>208</v>
+      </c>
+      <c r="C105" t="s">
+        <v>168</v>
       </c>
       <c r="E105" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="F105">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="G105" t="s">
-        <v>229</v>
+        <v>287</v>
       </c>
       <c r="H105" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="I105" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="B106" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="C106" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="E106" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F106">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G106" t="s">
         <v>105</v>
@@ -5068,152 +5044,152 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="B107" t="s">
-        <v>208</v>
-      </c>
-      <c r="C107" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="E107" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="F107">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
       <c r="G107" t="s">
-        <v>292</v>
+        <v>37</v>
       </c>
       <c r="H107" t="s">
+        <v>37</v>
+      </c>
+      <c r="I107" t="s">
         <v>293</v>
-      </c>
-      <c r="I107" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="B108" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C108" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="E108" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="F108">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G108" t="s">
-        <v>105</v>
+        <v>298</v>
       </c>
       <c r="H108" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I108" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>297</v>
+        <v>173</v>
       </c>
       <c r="B109" t="s">
-        <v>190</v>
+        <v>174</v>
+      </c>
+      <c r="C109" t="s">
+        <v>168</v>
       </c>
       <c r="E109" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="F109">
         <v>3.0</v>
       </c>
       <c r="G109" t="s">
-        <v>37</v>
+        <v>301</v>
       </c>
       <c r="H109" t="s">
-        <v>37</v>
+        <v>302</v>
       </c>
       <c r="I109" t="s">
-        <v>298</v>
+        <v>182</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B110" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C110" t="s">
-        <v>301</v>
+        <v>168</v>
       </c>
       <c r="E110" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F110">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G110" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H110" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I110" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="B111" t="s">
-        <v>174</v>
-      </c>
-      <c r="C111" t="s">
-        <v>168</v>
+        <v>52</v>
+      </c>
+      <c r="C111">
+        <v>40</v>
       </c>
       <c r="E111" t="s">
-        <v>175</v>
+        <v>53</v>
       </c>
       <c r="F111">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G111" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H111" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I111" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B112" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C112" t="s">
-        <v>168</v>
+        <v>311</v>
       </c>
       <c r="E112" t="s">
-        <v>310</v>
+        <v>228</v>
       </c>
       <c r="F112">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G112" t="s">
-        <v>311</v>
+        <v>229</v>
       </c>
       <c r="H112" t="s">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="I112" t="s">
         <v>312</v>
@@ -5221,54 +5197,54 @@
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>51</v>
+        <v>313</v>
       </c>
       <c r="B113" t="s">
-        <v>52</v>
-      </c>
-      <c r="C113">
-        <v>40</v>
+        <v>314</v>
+      </c>
+      <c r="C113" t="s">
+        <v>168</v>
       </c>
       <c r="E113" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="F113">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H113" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I113" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>314</v>
+        <v>199</v>
       </c>
       <c r="B114" t="s">
-        <v>315</v>
+        <v>200</v>
       </c>
       <c r="C114" t="s">
-        <v>316</v>
+        <v>136</v>
       </c>
       <c r="E114" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="F114">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G114" t="s">
-        <v>229</v>
+        <v>317</v>
       </c>
       <c r="H114" t="s">
-        <v>262</v>
+        <v>317</v>
       </c>
       <c r="I114" t="s">
-        <v>317</v>
+        <v>202</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5279,33 +5255,33 @@
         <v>319</v>
       </c>
       <c r="C115" t="s">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="E115" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="F115">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G115" t="s">
-        <v>320</v>
+        <v>105</v>
       </c>
       <c r="H115" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="I115" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C116" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="E116" t="s">
         <v>175</v>
@@ -5314,10 +5290,10 @@
         <v>1.0</v>
       </c>
       <c r="G116" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H116" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I116" t="s">
         <v>202</v>
@@ -5325,132 +5301,132 @@
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
+        <v>321</v>
+      </c>
+      <c r="B117" t="s">
+        <v>322</v>
+      </c>
+      <c r="C117" t="s">
+        <v>168</v>
+      </c>
+      <c r="E117" t="s">
         <v>323</v>
       </c>
-      <c r="B117" t="s">
+      <c r="F117">
+        <v>1.0</v>
+      </c>
+      <c r="G117" t="s">
         <v>324</v>
       </c>
-      <c r="C117" t="s">
-        <v>227</v>
-      </c>
-      <c r="E117" t="s">
-        <v>273</v>
-      </c>
-      <c r="F117">
-        <v>7.0</v>
-      </c>
-      <c r="G117" t="s">
-        <v>105</v>
-      </c>
       <c r="H117" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="I117" t="s">
-        <v>296</v>
+        <v>170</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>178</v>
+        <v>318</v>
       </c>
       <c r="B118" t="s">
-        <v>179</v>
+        <v>319</v>
       </c>
       <c r="C118" t="s">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="E118" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="F118">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G118" t="s">
         <v>325</v>
       </c>
       <c r="H118" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I118" t="s">
-        <v>202</v>
+        <v>327</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B119" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C119" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E119" t="s">
-        <v>328</v>
+        <v>244</v>
       </c>
       <c r="F119">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G119" t="s">
-        <v>329</v>
+        <v>37</v>
       </c>
       <c r="H119" t="s">
-        <v>329</v>
+        <v>37</v>
       </c>
       <c r="I119" t="s">
-        <v>170</v>
+        <v>247</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B120" t="s">
-        <v>324</v>
-      </c>
-      <c r="C120" t="s">
-        <v>272</v>
+        <v>331</v>
+      </c>
+      <c r="C120">
+        <v>44</v>
       </c>
       <c r="E120" t="s">
-        <v>273</v>
+        <v>53</v>
       </c>
       <c r="F120">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G120" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H120" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I120" t="s">
-        <v>276</v>
+        <v>55</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="B121" t="s">
+        <v>284</v>
+      </c>
+      <c r="C121" t="s">
+        <v>227</v>
+      </c>
+      <c r="E121" t="s">
+        <v>269</v>
+      </c>
+      <c r="F121">
+        <v>1.0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>105</v>
+      </c>
+      <c r="H121" t="s">
+        <v>105</v>
+      </c>
+      <c r="I121" t="s">
         <v>333</v>
-      </c>
-      <c r="C121" t="s">
-        <v>171</v>
-      </c>
-      <c r="E121" t="s">
-        <v>248</v>
-      </c>
-      <c r="F121">
-        <v>2.0</v>
-      </c>
-      <c r="G121" t="s">
-        <v>37</v>
-      </c>
-      <c r="H121" t="s">
-        <v>37</v>
-      </c>
-      <c r="I121" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5460,37 +5436,31 @@
       <c r="B122" t="s">
         <v>335</v>
       </c>
-      <c r="C122">
-        <v>44</v>
-      </c>
       <c r="E122" t="s">
-        <v>53</v>
+        <v>336</v>
       </c>
       <c r="F122">
         <v>1.0</v>
       </c>
       <c r="G122" t="s">
-        <v>336</v>
+        <v>131</v>
       </c>
       <c r="H122" t="s">
-        <v>336</v>
+        <v>131</v>
       </c>
       <c r="I122" t="s">
-        <v>55</v>
+        <v>337</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="B123" t="s">
-        <v>289</v>
-      </c>
-      <c r="C123" t="s">
-        <v>227</v>
+        <v>339</v>
       </c>
       <c r="E123" t="s">
-        <v>273</v>
+        <v>165</v>
       </c>
       <c r="F123">
         <v>1.0</v>
@@ -5502,73 +5472,76 @@
         <v>105</v>
       </c>
       <c r="I123" t="s">
-        <v>337</v>
+        <v>236</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B124" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E124" t="s">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c r="F124">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G124" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="H124" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="I124" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B125" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E125" t="s">
         <v>165</v>
       </c>
       <c r="F125">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G125" t="s">
         <v>105</v>
       </c>
       <c r="H125" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="I125" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>344</v>
+        <v>294</v>
       </c>
       <c r="B126" t="s">
+        <v>295</v>
+      </c>
+      <c r="C126" t="s">
         <v>345</v>
       </c>
       <c r="E126" t="s">
-        <v>165</v>
+        <v>297</v>
       </c>
       <c r="F126">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G126" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="H126" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="I126" t="s">
         <v>346</v>
@@ -5581,34 +5554,34 @@
       <c r="B127" t="s">
         <v>348</v>
       </c>
+      <c r="C127" t="s">
+        <v>168</v>
+      </c>
       <c r="E127" t="s">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="F127">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G127" t="s">
-        <v>105</v>
+        <v>349</v>
       </c>
       <c r="H127" t="s">
-        <v>166</v>
+        <v>350</v>
       </c>
       <c r="I127" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="B128" t="s">
-        <v>300</v>
-      </c>
-      <c r="C128" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E128" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="F128">
         <v>2.0</v>
@@ -5617,67 +5590,67 @@
         <v>229</v>
       </c>
       <c r="H128" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I128" t="s">
-        <v>350</v>
+        <v>282</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B129" t="s">
-        <v>352</v>
-      </c>
-      <c r="C129" t="s">
-        <v>168</v>
+        <v>355</v>
       </c>
       <c r="E129" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="F129">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G129" t="s">
-        <v>353</v>
+        <v>229</v>
       </c>
       <c r="H129" t="s">
-        <v>354</v>
+        <v>258</v>
       </c>
       <c r="I129" t="s">
-        <v>355</v>
+        <v>282</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
+        <v>199</v>
+      </c>
+      <c r="B130" t="s">
+        <v>200</v>
+      </c>
+      <c r="C130" t="s">
+        <v>168</v>
+      </c>
+      <c r="E130" t="s">
+        <v>175</v>
+      </c>
+      <c r="F130">
+        <v>1.0</v>
+      </c>
+      <c r="G130" t="s">
         <v>356</v>
       </c>
-      <c r="B130" t="s">
-        <v>357</v>
-      </c>
-      <c r="E130" t="s">
-        <v>130</v>
-      </c>
-      <c r="F130">
-        <v>2.0</v>
-      </c>
-      <c r="G130" t="s">
-        <v>229</v>
-      </c>
       <c r="H130" t="s">
-        <v>262</v>
+        <v>356</v>
       </c>
       <c r="I130" t="s">
-        <v>287</v>
+        <v>202</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
+        <v>357</v>
+      </c>
+      <c r="B131" t="s">
         <v>358</v>
-      </c>
-      <c r="B131" t="s">
-        <v>359</v>
       </c>
       <c r="E131" t="s">
         <v>130</v>
@@ -5689,102 +5662,102 @@
         <v>229</v>
       </c>
       <c r="H131" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I131" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>199</v>
+        <v>359</v>
       </c>
       <c r="B132" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="C132" t="s">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="E132" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="F132">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G132" t="s">
+        <v>105</v>
+      </c>
+      <c r="H132" t="s">
+        <v>187</v>
+      </c>
+      <c r="I132" t="s">
         <v>360</v>
-      </c>
-      <c r="H132" t="s">
-        <v>360</v>
-      </c>
-      <c r="I132" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
+        <v>328</v>
+      </c>
+      <c r="B133" t="s">
+        <v>329</v>
+      </c>
+      <c r="C133" t="s">
+        <v>215</v>
+      </c>
+      <c r="E133" t="s">
+        <v>244</v>
+      </c>
+      <c r="F133">
+        <v>3.0</v>
+      </c>
+      <c r="G133" t="s">
+        <v>37</v>
+      </c>
+      <c r="H133" t="s">
+        <v>37</v>
+      </c>
+      <c r="I133" t="s">
         <v>361</v>
-      </c>
-      <c r="B133" t="s">
-        <v>362</v>
-      </c>
-      <c r="E133" t="s">
-        <v>130</v>
-      </c>
-      <c r="F133">
-        <v>2.0</v>
-      </c>
-      <c r="G133" t="s">
-        <v>229</v>
-      </c>
-      <c r="H133" t="s">
-        <v>262</v>
-      </c>
-      <c r="I133" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
+        <v>362</v>
+      </c>
+      <c r="B134" t="s">
         <v>363</v>
       </c>
-      <c r="B134" t="s">
-        <v>282</v>
-      </c>
-      <c r="C134" t="s">
-        <v>227</v>
-      </c>
       <c r="E134" t="s">
-        <v>273</v>
+        <v>165</v>
       </c>
       <c r="F134">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G134" t="s">
         <v>105</v>
       </c>
       <c r="H134" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="I134" t="s">
-        <v>364</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="B135" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="C135" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E135" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F135">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G135" t="s">
         <v>37</v>
@@ -5793,976 +5766,976 @@
         <v>37</v>
       </c>
       <c r="I135" t="s">
-        <v>365</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>366</v>
+        <v>225</v>
       </c>
       <c r="B136" t="s">
-        <v>367</v>
+        <v>226</v>
+      </c>
+      <c r="C136" t="s">
+        <v>296</v>
       </c>
       <c r="E136" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="F136">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="H136" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="I136" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
+        <v>366</v>
+      </c>
+      <c r="B137" t="s">
+        <v>367</v>
+      </c>
+      <c r="E137" t="s">
+        <v>336</v>
+      </c>
+      <c r="F137">
+        <v>3.0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>131</v>
+      </c>
+      <c r="H137" t="s">
         <v>368</v>
       </c>
-      <c r="B137" t="s">
+      <c r="I137" t="s">
         <v>369</v>
-      </c>
-      <c r="C137" t="s">
-        <v>171</v>
-      </c>
-      <c r="E137" t="s">
-        <v>248</v>
-      </c>
-      <c r="F137">
-        <v>6.0</v>
-      </c>
-      <c r="G137" t="s">
-        <v>37</v>
-      </c>
-      <c r="H137" t="s">
-        <v>37</v>
-      </c>
-      <c r="I137" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>225</v>
+        <v>370</v>
       </c>
       <c r="B138" t="s">
-        <v>226</v>
-      </c>
-      <c r="C138" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="E138" t="s">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="F138">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G138" t="s">
-        <v>229</v>
+        <v>105</v>
       </c>
       <c r="H138" t="s">
-        <v>262</v>
+        <v>105</v>
       </c>
       <c r="I138" t="s">
-        <v>317</v>
+        <v>195</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B139" t="s">
-        <v>371</v>
+        <v>373</v>
+      </c>
+      <c r="C139" t="s">
+        <v>168</v>
       </c>
       <c r="E139" t="s">
-        <v>340</v>
+        <v>250</v>
       </c>
       <c r="F139">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G139" t="s">
-        <v>131</v>
+        <v>374</v>
       </c>
       <c r="H139" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I139" t="s">
-        <v>373</v>
+        <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>374</v>
+        <v>266</v>
       </c>
       <c r="B140" t="s">
-        <v>375</v>
+        <v>267</v>
+      </c>
+      <c r="C140" t="s">
+        <v>345</v>
       </c>
       <c r="E140" t="s">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="F140">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G140" t="s">
         <v>105</v>
       </c>
       <c r="H140" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="I140" t="s">
-        <v>195</v>
+        <v>327</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>376</v>
+        <v>318</v>
       </c>
       <c r="B141" t="s">
-        <v>377</v>
+        <v>319</v>
       </c>
       <c r="C141" t="s">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="E141" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="F141">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G141" t="s">
-        <v>378</v>
+        <v>105</v>
       </c>
       <c r="H141" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I141" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
       <c r="B142" t="s">
-        <v>271</v>
-      </c>
-      <c r="C142" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="E142" t="s">
-        <v>273</v>
+        <v>378</v>
       </c>
       <c r="F142">
-        <v>3.0</v>
+        <v>24.0</v>
       </c>
       <c r="G142" t="s">
-        <v>105</v>
+        <v>379</v>
       </c>
       <c r="H142" t="s">
-        <v>187</v>
+        <v>380</v>
       </c>
       <c r="I142" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="B143" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="C143" t="s">
-        <v>301</v>
+        <v>168</v>
       </c>
       <c r="E143" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="F143">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G143" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="H143" t="s">
-        <v>380</v>
+        <v>37</v>
       </c>
       <c r="I143" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>381</v>
+        <v>328</v>
       </c>
       <c r="B144" t="s">
-        <v>382</v>
+        <v>329</v>
+      </c>
+      <c r="C144" t="s">
+        <v>146</v>
       </c>
       <c r="E144" t="s">
-        <v>383</v>
+        <v>244</v>
       </c>
       <c r="F144">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="s">
+        <v>37</v>
+      </c>
+      <c r="H144" t="s">
+        <v>37</v>
+      </c>
+      <c r="I144" t="s">
         <v>384</v>
-      </c>
-      <c r="H144" t="s">
-        <v>385</v>
-      </c>
-      <c r="I144" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B145" t="s">
-        <v>388</v>
-      </c>
-      <c r="C145" t="s">
-        <v>168</v>
+        <v>386</v>
       </c>
       <c r="E145" t="s">
-        <v>248</v>
+        <v>165</v>
       </c>
       <c r="F145">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="H145" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="I145" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="B146" t="s">
-        <v>333</v>
+        <v>277</v>
       </c>
       <c r="C146" t="s">
-        <v>146</v>
+        <v>296</v>
       </c>
       <c r="E146" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="F146">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G146" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="H146" t="s">
-        <v>37</v>
+        <v>166</v>
       </c>
       <c r="I146" t="s">
-        <v>389</v>
+        <v>346</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
+        <v>387</v>
+      </c>
+      <c r="B147" t="s">
+        <v>388</v>
+      </c>
+      <c r="E147" t="s">
+        <v>389</v>
+      </c>
+      <c r="F147">
+        <v>2.0</v>
+      </c>
+      <c r="G147" t="s">
         <v>390</v>
       </c>
-      <c r="B147" t="s">
+      <c r="H147" t="s">
         <v>391</v>
       </c>
-      <c r="E147" t="s">
-        <v>165</v>
-      </c>
-      <c r="F147">
-        <v>1.0</v>
-      </c>
-      <c r="G147" t="s">
-        <v>105</v>
-      </c>
-      <c r="H147" t="s">
-        <v>105</v>
-      </c>
       <c r="I147" t="s">
-        <v>236</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>363</v>
+        <v>266</v>
       </c>
       <c r="B148" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C148" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E148" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F148">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G148" t="s">
         <v>105</v>
       </c>
       <c r="H148" t="s">
-        <v>166</v>
+        <v>393</v>
       </c>
       <c r="I148" t="s">
-        <v>350</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>392</v>
+        <v>318</v>
       </c>
       <c r="B149" t="s">
-        <v>393</v>
+        <v>319</v>
+      </c>
+      <c r="C149" t="s">
+        <v>345</v>
       </c>
       <c r="E149" t="s">
-        <v>394</v>
+        <v>269</v>
       </c>
       <c r="F149">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G149" t="s">
-        <v>395</v>
+        <v>105</v>
       </c>
       <c r="H149" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="I149" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="B150" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C150" t="s">
-        <v>301</v>
+        <v>227</v>
       </c>
       <c r="E150" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="F150">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G150" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="H150" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I150" t="s">
-        <v>399</v>
+        <v>286</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="B151" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
       <c r="C151" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="E151" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F151">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="s">
         <v>105</v>
       </c>
       <c r="H151" t="s">
-        <v>380</v>
+        <v>166</v>
       </c>
       <c r="I151" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="B152" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C152" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="E152" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="F152">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="s">
-        <v>229</v>
+        <v>105</v>
       </c>
       <c r="H152" t="s">
-        <v>400</v>
+        <v>105</v>
       </c>
       <c r="I152" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>270</v>
+        <v>396</v>
       </c>
       <c r="B153" t="s">
-        <v>271</v>
-      </c>
-      <c r="C153" t="s">
-        <v>316</v>
+        <v>397</v>
       </c>
       <c r="E153" t="s">
-        <v>273</v>
+        <v>398</v>
       </c>
       <c r="F153">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="H153" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="I153" t="s">
-        <v>317</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B154" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C154" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="E154" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="F154">
         <v>1.0</v>
       </c>
       <c r="G154" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="H154" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="I154" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
+        <v>400</v>
+      </c>
+      <c r="B155" t="s">
         <v>401</v>
       </c>
-      <c r="B155" t="s">
-        <v>402</v>
+      <c r="C155" t="s">
+        <v>227</v>
       </c>
       <c r="E155" t="s">
-        <v>403</v>
+        <v>228</v>
       </c>
       <c r="F155">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G155" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="H155" t="s">
-        <v>37</v>
+        <v>258</v>
       </c>
       <c r="I155" t="s">
-        <v>404</v>
+        <v>312</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>299</v>
+        <v>402</v>
       </c>
       <c r="B156" t="s">
-        <v>300</v>
+        <v>403</v>
       </c>
       <c r="C156" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="E156" t="s">
-        <v>302</v>
+        <v>404</v>
       </c>
       <c r="F156">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G156" t="s">
         <v>229</v>
       </c>
       <c r="H156" t="s">
-        <v>229</v>
+        <v>405</v>
       </c>
       <c r="I156" t="s">
-        <v>337</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B157" t="s">
-        <v>406</v>
-      </c>
-      <c r="C157" t="s">
-        <v>227</v>
+        <v>408</v>
       </c>
       <c r="E157" t="s">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="F157">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G157" t="s">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="H157" t="s">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="I157" t="s">
-        <v>317</v>
+        <v>188</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B158" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C158" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
       <c r="E158" t="s">
+        <v>228</v>
+      </c>
+      <c r="F158">
+        <v>2.0</v>
+      </c>
+      <c r="G158" t="s">
         <v>409</v>
-      </c>
-      <c r="F158">
-        <v>3.0</v>
-      </c>
-      <c r="G158" t="s">
-        <v>229</v>
       </c>
       <c r="H158" t="s">
         <v>410</v>
       </c>
       <c r="I158" t="s">
-        <v>411</v>
+        <v>312</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>412</v>
+        <v>283</v>
       </c>
       <c r="B159" t="s">
-        <v>413</v>
+        <v>284</v>
+      </c>
+      <c r="C159" t="s">
+        <v>345</v>
       </c>
       <c r="E159" t="s">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="F159">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G159" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="H159" t="s">
-        <v>372</v>
+        <v>166</v>
       </c>
       <c r="I159" t="s">
-        <v>188</v>
+        <v>346</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>405</v>
+        <v>309</v>
       </c>
       <c r="B160" t="s">
-        <v>406</v>
+        <v>310</v>
       </c>
       <c r="C160" t="s">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="E160" t="s">
         <v>228</v>
       </c>
       <c r="F160">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G160" t="s">
-        <v>414</v>
+        <v>229</v>
       </c>
       <c r="H160" t="s">
-        <v>415</v>
+        <v>229</v>
       </c>
       <c r="I160" t="s">
-        <v>317</v>
+        <v>230</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>288</v>
+        <v>400</v>
       </c>
       <c r="B161" t="s">
-        <v>289</v>
+        <v>401</v>
       </c>
       <c r="C161" t="s">
-        <v>349</v>
+        <v>296</v>
       </c>
       <c r="E161" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="F161">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G161" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="H161" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="I161" t="s">
-        <v>350</v>
+        <v>230</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="B162" t="s">
-        <v>315</v>
-      </c>
-      <c r="C162" t="s">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="E162" t="s">
-        <v>228</v>
+        <v>413</v>
       </c>
       <c r="F162">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G162" t="s">
-        <v>229</v>
+        <v>414</v>
       </c>
       <c r="H162" t="s">
-        <v>229</v>
+        <v>415</v>
       </c>
       <c r="I162" t="s">
-        <v>230</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B163" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C163" t="s">
-        <v>301</v>
+        <v>215</v>
       </c>
       <c r="E163" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="F163">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G163" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="H163" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="I163" t="s">
-        <v>230</v>
+        <v>419</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="B164" t="s">
-        <v>417</v>
+        <v>383</v>
+      </c>
+      <c r="C164" t="s">
+        <v>215</v>
       </c>
       <c r="E164" t="s">
-        <v>418</v>
+        <v>244</v>
       </c>
       <c r="F164">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="G164" t="s">
-        <v>419</v>
+        <v>37</v>
       </c>
       <c r="H164" t="s">
-        <v>420</v>
+        <v>37</v>
       </c>
       <c r="I164" t="s">
-        <v>421</v>
+        <v>361</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B165" t="s">
-        <v>423</v>
-      </c>
-      <c r="C165" t="s">
-        <v>215</v>
+        <v>421</v>
       </c>
       <c r="E165" t="s">
-        <v>254</v>
+        <v>389</v>
       </c>
       <c r="F165">
         <v>2.0</v>
       </c>
       <c r="G165" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="H165" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="I165" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>387</v>
+        <v>309</v>
       </c>
       <c r="B166" t="s">
-        <v>388</v>
+        <v>310</v>
       </c>
       <c r="C166" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="E166" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F166">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G166" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="H166" t="s">
-        <v>37</v>
+        <v>350</v>
       </c>
       <c r="I166" t="s">
-        <v>365</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>299</v>
+        <v>423</v>
       </c>
       <c r="B167" t="s">
-        <v>300</v>
-      </c>
-      <c r="C167" t="s">
-        <v>316</v>
+        <v>424</v>
       </c>
       <c r="E167" t="s">
-        <v>302</v>
+        <v>425</v>
       </c>
       <c r="F167">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G167" t="s">
         <v>229</v>
       </c>
       <c r="H167" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="I167" t="s">
-        <v>337</v>
+        <v>426</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
+        <v>427</v>
+      </c>
+      <c r="B168" t="s">
+        <v>428</v>
+      </c>
+      <c r="E168" t="s">
         <v>425</v>
-      </c>
-      <c r="B168" t="s">
-        <v>426</v>
-      </c>
-      <c r="E168" t="s">
-        <v>394</v>
       </c>
       <c r="F168">
         <v>2.0</v>
       </c>
       <c r="G168" t="s">
-        <v>131</v>
+        <v>229</v>
       </c>
       <c r="H168" t="s">
-        <v>132</v>
+        <v>258</v>
       </c>
       <c r="I168" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="B169" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="C169" t="s">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="E169" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="F169">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G169" t="s">
-        <v>229</v>
+        <v>105</v>
       </c>
       <c r="H169" t="s">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="I169" t="s">
-        <v>276</v>
+        <v>346</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="B170" t="s">
-        <v>429</v>
+        <v>401</v>
+      </c>
+      <c r="C170" t="s">
+        <v>345</v>
       </c>
       <c r="E170" t="s">
-        <v>430</v>
+        <v>228</v>
       </c>
       <c r="F170">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G170" t="s">
         <v>229</v>
       </c>
       <c r="H170" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="I170" t="s">
-        <v>431</v>
+        <v>230</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B171" t="s">
-        <v>433</v>
+        <v>430</v>
+      </c>
+      <c r="C171" t="s">
+        <v>215</v>
       </c>
       <c r="E171" t="s">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="F171">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G171" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="H171" t="s">
-        <v>262</v>
+        <v>37</v>
       </c>
       <c r="I171" t="s">
-        <v>431</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>363</v>
+        <v>431</v>
       </c>
       <c r="B172" t="s">
-        <v>282</v>
-      </c>
-      <c r="C172" t="s">
-        <v>349</v>
+        <v>431</v>
       </c>
       <c r="E172" t="s">
-        <v>273</v>
+        <v>432</v>
       </c>
       <c r="F172">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G172" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="H172" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="I172" t="s">
-        <v>350</v>
+        <v>433</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="B173" t="s">
-        <v>406</v>
+        <v>435</v>
       </c>
       <c r="C173" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E173" t="s">
-        <v>228</v>
+        <v>436</v>
       </c>
       <c r="F173">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G173" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H173" t="s">
-        <v>229</v>
+        <v>437</v>
       </c>
       <c r="I173" t="s">
-        <v>230</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B174" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C174" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="E174" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="F174">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G174" t="s">
         <v>37</v>
@@ -6771,313 +6744,313 @@
         <v>37</v>
       </c>
       <c r="I174" t="s">
-        <v>170</v>
+        <v>247</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="B175" t="s">
-        <v>436</v>
+        <v>403</v>
+      </c>
+      <c r="C175" t="s">
+        <v>268</v>
       </c>
       <c r="E175" t="s">
-        <v>437</v>
+        <v>404</v>
       </c>
       <c r="F175">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G175" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="H175" t="s">
-        <v>37</v>
+        <v>395</v>
       </c>
       <c r="I175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B176" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C176" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E176" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="F176">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G176" t="s">
+        <v>229</v>
+      </c>
+      <c r="H176" t="s">
         <v>395</v>
       </c>
-      <c r="H176" t="s">
-        <v>442</v>
-      </c>
       <c r="I176" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>444</v>
+        <v>283</v>
       </c>
       <c r="B177" t="s">
-        <v>445</v>
+        <v>284</v>
       </c>
       <c r="C177" t="s">
-        <v>168</v>
+        <v>311</v>
       </c>
       <c r="E177" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="F177">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G177" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="H177" t="s">
-        <v>37</v>
+        <v>187</v>
       </c>
       <c r="I177" t="s">
-        <v>251</v>
+        <v>360</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="B178" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="C178" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="E178" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="F178">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G178" t="s">
         <v>229</v>
       </c>
       <c r="H178" t="s">
-        <v>400</v>
+        <v>229</v>
       </c>
       <c r="I178" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
+        <v>248</v>
+      </c>
+      <c r="B179" t="s">
+        <v>249</v>
+      </c>
+      <c r="C179" t="s">
+        <v>168</v>
+      </c>
+      <c r="E179" t="s">
+        <v>250</v>
+      </c>
+      <c r="F179">
+        <v>4.0</v>
+      </c>
+      <c r="G179" t="s">
+        <v>446</v>
+      </c>
+      <c r="H179" t="s">
         <v>447</v>
       </c>
-      <c r="B179" t="s">
+      <c r="I179" t="s">
         <v>448</v>
-      </c>
-      <c r="C179" t="s">
-        <v>272</v>
-      </c>
-      <c r="E179" t="s">
-        <v>409</v>
-      </c>
-      <c r="F179">
-        <v>5.0</v>
-      </c>
-      <c r="G179" t="s">
-        <v>229</v>
-      </c>
-      <c r="H179" t="s">
-        <v>400</v>
-      </c>
-      <c r="I179" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>288</v>
+        <v>449</v>
       </c>
       <c r="B180" t="s">
-        <v>289</v>
-      </c>
-      <c r="C180" t="s">
-        <v>316</v>
+        <v>450</v>
       </c>
       <c r="E180" t="s">
-        <v>273</v>
+        <v>191</v>
       </c>
       <c r="F180">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G180" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="H180" t="s">
-        <v>187</v>
+        <v>37</v>
       </c>
       <c r="I180" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B181" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C181" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="E181" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="F181">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G181" t="s">
-        <v>229</v>
+        <v>454</v>
       </c>
       <c r="H181" t="s">
-        <v>229</v>
+        <v>455</v>
       </c>
       <c r="I181" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>252</v>
+        <v>359</v>
       </c>
       <c r="B182" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="C182" t="s">
-        <v>168</v>
+        <v>311</v>
       </c>
       <c r="E182" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="F182">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G182" t="s">
-        <v>451</v>
+        <v>105</v>
       </c>
       <c r="H182" t="s">
-        <v>452</v>
+        <v>166</v>
       </c>
       <c r="I182" t="s">
-        <v>453</v>
+        <v>346</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B183" t="s">
-        <v>455</v>
+        <v>458</v>
+      </c>
+      <c r="C183" t="s">
+        <v>296</v>
       </c>
       <c r="E183" t="s">
-        <v>191</v>
+        <v>404</v>
       </c>
       <c r="F183">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G183" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="H183" t="s">
-        <v>37</v>
+        <v>350</v>
       </c>
       <c r="I183" t="s">
-        <v>404</v>
+        <v>459</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B184" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C184" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E184" t="s">
-        <v>458</v>
+        <v>404</v>
       </c>
       <c r="F184">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G184" t="s">
-        <v>459</v>
+        <v>229</v>
       </c>
       <c r="H184" t="s">
-        <v>460</v>
+        <v>229</v>
       </c>
       <c r="I184" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>363</v>
+        <v>457</v>
       </c>
       <c r="B185" t="s">
-        <v>282</v>
+        <v>458</v>
       </c>
       <c r="C185" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="E185" t="s">
-        <v>273</v>
+        <v>404</v>
       </c>
       <c r="F185">
         <v>3.0</v>
       </c>
       <c r="G185" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="H185" t="s">
-        <v>187</v>
+        <v>405</v>
       </c>
       <c r="I185" t="s">
-        <v>364</v>
+        <v>462</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B186" t="s">
-        <v>463</v>
-      </c>
-      <c r="C186" t="s">
-        <v>301</v>
+        <v>464</v>
       </c>
       <c r="E186" t="s">
-        <v>409</v>
+        <v>165</v>
       </c>
       <c r="F186">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G186" t="s">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="H186" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="I186" t="s">
-        <v>464</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -7087,84 +7060,87 @@
       <c r="B187" t="s">
         <v>466</v>
       </c>
-      <c r="C187" t="s">
-        <v>272</v>
-      </c>
       <c r="E187" t="s">
-        <v>409</v>
+        <v>467</v>
       </c>
       <c r="F187">
         <v>1.0</v>
       </c>
       <c r="G187" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="H187" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="I187" t="s">
-        <v>450</v>
+        <v>399</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B188" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C188" t="s">
-        <v>227</v>
+        <v>136</v>
       </c>
       <c r="E188" t="s">
-        <v>409</v>
+        <v>470</v>
       </c>
       <c r="F188">
         <v>3.0</v>
       </c>
       <c r="G188" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="H188" t="s">
-        <v>410</v>
+        <v>258</v>
       </c>
       <c r="I188" t="s">
-        <v>467</v>
+        <v>256</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B189" t="s">
-        <v>469</v>
+        <v>472</v>
+      </c>
+      <c r="C189" t="s">
+        <v>168</v>
       </c>
       <c r="E189" t="s">
-        <v>165</v>
+        <v>305</v>
       </c>
       <c r="F189">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G189" t="s">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="H189" t="s">
-        <v>372</v>
+        <v>37</v>
       </c>
       <c r="I189" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
+        <v>473</v>
+      </c>
+      <c r="B190" t="s">
+        <v>474</v>
+      </c>
+      <c r="C190" t="s">
+        <v>171</v>
+      </c>
+      <c r="E190" t="s">
         <v>470</v>
       </c>
-      <c r="B190" t="s">
-        <v>471</v>
-      </c>
-      <c r="E190" t="s">
-        <v>472</v>
-      </c>
       <c r="F190">
         <v>1.0</v>
       </c>
@@ -7175,1240 +7151,1240 @@
         <v>37</v>
       </c>
       <c r="I190" t="s">
-        <v>404</v>
+        <v>475</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="B191" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="C191" t="s">
-        <v>136</v>
+        <v>268</v>
       </c>
       <c r="E191" t="s">
-        <v>475</v>
+        <v>404</v>
       </c>
       <c r="F191">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G191" t="s">
-        <v>353</v>
+        <v>229</v>
       </c>
       <c r="H191" t="s">
-        <v>262</v>
+        <v>350</v>
       </c>
       <c r="I191" t="s">
-        <v>260</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
+        <v>451</v>
+      </c>
+      <c r="B192" t="s">
+        <v>452</v>
+      </c>
+      <c r="C192" t="s">
+        <v>268</v>
+      </c>
+      <c r="E192" t="s">
+        <v>453</v>
+      </c>
+      <c r="F192">
+        <v>7.0</v>
+      </c>
+      <c r="G192" t="s">
         <v>476</v>
       </c>
-      <c r="B192" t="s">
+      <c r="H192" t="s">
+        <v>395</v>
+      </c>
+      <c r="I192" t="s">
         <v>477</v>
-      </c>
-      <c r="C192" t="s">
-        <v>168</v>
-      </c>
-      <c r="E192" t="s">
-        <v>310</v>
-      </c>
-      <c r="F192">
-        <v>1.0</v>
-      </c>
-      <c r="G192" t="s">
-        <v>37</v>
-      </c>
-      <c r="H192" t="s">
-        <v>37</v>
-      </c>
-      <c r="I192" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="B193" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="C193" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="E193" t="s">
-        <v>475</v>
+        <v>404</v>
       </c>
       <c r="F193">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G193" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="H193" t="s">
-        <v>37</v>
+        <v>405</v>
       </c>
       <c r="I193" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>462</v>
+        <v>402</v>
       </c>
       <c r="B194" t="s">
-        <v>463</v>
+        <v>403</v>
       </c>
       <c r="C194" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="E194" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="F194">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G194" t="s">
         <v>229</v>
       </c>
       <c r="H194" t="s">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="I194" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B195" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C195" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="E195" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F195">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G195" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="H195" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="I195" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="B196" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="C196" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="E196" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="F196">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G196" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H196" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="I196" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>407</v>
+        <v>482</v>
       </c>
       <c r="B197" t="s">
-        <v>408</v>
-      </c>
-      <c r="C197" t="s">
-        <v>227</v>
+        <v>483</v>
       </c>
       <c r="E197" t="s">
-        <v>409</v>
+        <v>484</v>
       </c>
       <c r="F197">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G197" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="H197" t="s">
-        <v>400</v>
+        <v>37</v>
       </c>
       <c r="I197" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B198" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C198" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="E198" t="s">
-        <v>458</v>
+        <v>404</v>
       </c>
       <c r="F198">
         <v>2.0</v>
       </c>
       <c r="G198" t="s">
-        <v>481</v>
+        <v>229</v>
       </c>
       <c r="H198" t="s">
-        <v>395</v>
+        <v>258</v>
       </c>
       <c r="I198" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="B199" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="C199" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="E199" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="F199">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G199" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="H199" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="I199" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
+        <v>434</v>
+      </c>
+      <c r="B200" t="s">
+        <v>435</v>
+      </c>
+      <c r="C200" t="s">
+        <v>227</v>
+      </c>
+      <c r="E200" t="s">
+        <v>436</v>
+      </c>
+      <c r="F200">
+        <v>2.0</v>
+      </c>
+      <c r="G200" t="s">
+        <v>390</v>
+      </c>
+      <c r="H200" t="s">
+        <v>391</v>
+      </c>
+      <c r="I200" t="s">
         <v>487</v>
-      </c>
-      <c r="B200" t="s">
-        <v>488</v>
-      </c>
-      <c r="E200" t="s">
-        <v>489</v>
-      </c>
-      <c r="F200">
-        <v>1.0</v>
-      </c>
-      <c r="G200" t="s">
-        <v>37</v>
-      </c>
-      <c r="H200" t="s">
-        <v>37</v>
-      </c>
-      <c r="I200" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B201" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C201" t="s">
-        <v>349</v>
+        <v>227</v>
       </c>
       <c r="E201" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="F201">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G201" t="s">
         <v>229</v>
       </c>
       <c r="H201" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="I201" t="s">
-        <v>491</v>
+        <v>445</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>456</v>
+        <v>318</v>
       </c>
       <c r="B202" t="s">
-        <v>457</v>
+        <v>319</v>
       </c>
       <c r="C202" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E202" t="s">
-        <v>458</v>
+        <v>269</v>
       </c>
       <c r="F202">
         <v>2.0</v>
       </c>
       <c r="G202" t="s">
-        <v>481</v>
+        <v>105</v>
       </c>
       <c r="H202" t="s">
-        <v>395</v>
+        <v>166</v>
       </c>
       <c r="I202" t="s">
-        <v>483</v>
+        <v>312</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>439</v>
+        <v>488</v>
       </c>
       <c r="B203" t="s">
-        <v>440</v>
+        <v>489</v>
       </c>
       <c r="C203" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="E203" t="s">
-        <v>441</v>
+        <v>175</v>
       </c>
       <c r="F203">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G203" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="H203" t="s">
-        <v>396</v>
+        <v>37</v>
       </c>
       <c r="I203" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B204" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C204" t="s">
-        <v>227</v>
+        <v>136</v>
       </c>
       <c r="E204" t="s">
-        <v>409</v>
+        <v>470</v>
       </c>
       <c r="F204">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G204" t="s">
-        <v>229</v>
+        <v>491</v>
       </c>
       <c r="H204" t="s">
-        <v>229</v>
+        <v>492</v>
       </c>
       <c r="I204" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="B205" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="C205" t="s">
-        <v>316</v>
+        <v>215</v>
       </c>
       <c r="E205" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="F205">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G205" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="H205" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="I205" t="s">
-        <v>317</v>
+        <v>493</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B206" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C206" t="s">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="E206" t="s">
-        <v>175</v>
+        <v>453</v>
       </c>
       <c r="F206">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G206" t="s">
-        <v>37</v>
+        <v>476</v>
       </c>
       <c r="H206" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="I206" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B207" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C207" t="s">
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="E207" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="F207">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G207" t="s">
+        <v>390</v>
+      </c>
+      <c r="H207" t="s">
+        <v>391</v>
+      </c>
+      <c r="I207" t="s">
         <v>496</v>
-      </c>
-      <c r="H207" t="s">
-        <v>497</v>
-      </c>
-      <c r="I207" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>308</v>
+        <v>434</v>
       </c>
       <c r="B208" t="s">
-        <v>309</v>
+        <v>435</v>
       </c>
       <c r="C208" t="s">
-        <v>215</v>
+        <v>345</v>
       </c>
       <c r="E208" t="s">
-        <v>310</v>
+        <v>436</v>
       </c>
       <c r="F208">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G208" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="H208" t="s">
-        <v>37</v>
+        <v>391</v>
       </c>
       <c r="I208" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>499</v>
+        <v>434</v>
       </c>
       <c r="B209" t="s">
-        <v>500</v>
+        <v>435</v>
       </c>
       <c r="C209" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E209" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="F209">
         <v>2.0</v>
       </c>
       <c r="G209" t="s">
-        <v>481</v>
+        <v>390</v>
       </c>
       <c r="H209" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="I209" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="B210" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="C210" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="E210" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="F210">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G210" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="H210" t="s">
-        <v>396</v>
+        <v>476</v>
       </c>
       <c r="I210" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B211" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C211" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E211" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="F211">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G211" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="H211" t="s">
-        <v>396</v>
+        <v>501</v>
       </c>
       <c r="I211" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
       <c r="B212" t="s">
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="C212" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E212" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="F212">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G212" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="H212" t="s">
-        <v>396</v>
+        <v>476</v>
       </c>
       <c r="I212" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B213" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C213" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="E213" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="F213">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G213" t="s">
-        <v>481</v>
+        <v>390</v>
       </c>
       <c r="H213" t="s">
-        <v>481</v>
+        <v>391</v>
       </c>
       <c r="I213" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>462</v>
+        <v>506</v>
       </c>
       <c r="B214" t="s">
-        <v>463</v>
+        <v>507</v>
       </c>
       <c r="C214" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E214" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="F214">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G214" t="s">
-        <v>505</v>
+        <v>390</v>
       </c>
       <c r="H214" t="s">
-        <v>262</v>
+        <v>391</v>
       </c>
       <c r="I214" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B215" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C215" t="s">
-        <v>316</v>
+        <v>168</v>
       </c>
       <c r="E215" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="F215">
         <v>1.0</v>
       </c>
       <c r="G215" t="s">
-        <v>481</v>
+        <v>510</v>
       </c>
       <c r="H215" t="s">
-        <v>481</v>
+        <v>510</v>
       </c>
       <c r="I215" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B216" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C216" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="E216" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="F216">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G216" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="H216" t="s">
-        <v>396</v>
+        <v>37</v>
       </c>
       <c r="I216" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>510</v>
+        <v>328</v>
       </c>
       <c r="B217" t="s">
-        <v>511</v>
+        <v>329</v>
       </c>
       <c r="C217" t="s">
-        <v>272</v>
+        <v>168</v>
       </c>
       <c r="E217" t="s">
-        <v>441</v>
+        <v>244</v>
       </c>
       <c r="F217">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G217" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="H217" t="s">
-        <v>396</v>
+        <v>37</v>
       </c>
       <c r="I217" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>512</v>
+        <v>442</v>
       </c>
       <c r="B218" t="s">
-        <v>513</v>
+        <v>443</v>
       </c>
       <c r="C218" t="s">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="E218" t="s">
-        <v>475</v>
+        <v>404</v>
       </c>
       <c r="F218">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G218" t="s">
-        <v>514</v>
+        <v>229</v>
       </c>
       <c r="H218" t="s">
-        <v>514</v>
+        <v>258</v>
       </c>
       <c r="I218" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>515</v>
+        <v>479</v>
       </c>
       <c r="B219" t="s">
-        <v>516</v>
+        <v>480</v>
       </c>
       <c r="C219" t="s">
-        <v>171</v>
+        <v>345</v>
       </c>
       <c r="E219" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="F219">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G219" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="H219" t="s">
-        <v>37</v>
+        <v>391</v>
       </c>
       <c r="I219" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>332</v>
+        <v>479</v>
       </c>
       <c r="B220" t="s">
-        <v>333</v>
+        <v>480</v>
       </c>
       <c r="C220" t="s">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="E220" t="s">
-        <v>248</v>
+        <v>436</v>
       </c>
       <c r="F220">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G220" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="H220" t="s">
-        <v>37</v>
+        <v>391</v>
       </c>
       <c r="I220" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>447</v>
+        <v>514</v>
       </c>
       <c r="B221" t="s">
-        <v>448</v>
+        <v>515</v>
       </c>
       <c r="C221" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="E221" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="F221">
         <v>2.0</v>
       </c>
       <c r="G221" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H221" t="s">
-        <v>262</v>
+        <v>391</v>
       </c>
       <c r="I221" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>484</v>
+        <v>517</v>
       </c>
       <c r="B222" t="s">
-        <v>485</v>
-      </c>
-      <c r="C222" t="s">
-        <v>349</v>
+        <v>518</v>
       </c>
       <c r="E222" t="s">
-        <v>441</v>
+        <v>519</v>
       </c>
       <c r="F222">
         <v>2.0</v>
       </c>
       <c r="G222" t="s">
-        <v>395</v>
+        <v>520</v>
       </c>
       <c r="H222" t="s">
-        <v>396</v>
+        <v>105</v>
       </c>
       <c r="I222" t="s">
-        <v>501</v>
+        <v>422</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="B223" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="C223" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E223" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="F223">
         <v>2.0</v>
       </c>
       <c r="G223" t="s">
-        <v>395</v>
+        <v>229</v>
       </c>
       <c r="H223" t="s">
-        <v>396</v>
+        <v>258</v>
       </c>
       <c r="I223" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="B224" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="C224" t="s">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="E224" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="F224">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G224" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="H224" t="s">
-        <v>396</v>
+        <v>476</v>
       </c>
       <c r="I224" t="s">
-        <v>520</v>
+        <v>475</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="B225" t="s">
-        <v>522</v>
+        <v>512</v>
+      </c>
+      <c r="C225" t="s">
+        <v>215</v>
       </c>
       <c r="E225" t="s">
-        <v>523</v>
+        <v>470</v>
       </c>
       <c r="F225">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G225" t="s">
-        <v>524</v>
+        <v>37</v>
       </c>
       <c r="H225" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="I225" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B226" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C226" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E226" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="F226">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G226" t="s">
         <v>229</v>
       </c>
       <c r="H226" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="I226" t="s">
-        <v>491</v>
+        <v>445</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>499</v>
+        <v>402</v>
       </c>
       <c r="B227" t="s">
-        <v>500</v>
+        <v>403</v>
       </c>
       <c r="C227" t="s">
-        <v>349</v>
+        <v>296</v>
       </c>
       <c r="E227" t="s">
-        <v>458</v>
+        <v>404</v>
       </c>
       <c r="F227">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G227" t="s">
-        <v>481</v>
+        <v>229</v>
       </c>
       <c r="H227" t="s">
-        <v>481</v>
+        <v>405</v>
       </c>
       <c r="I227" t="s">
-        <v>480</v>
+        <v>406</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>515</v>
+        <v>451</v>
       </c>
       <c r="B228" t="s">
-        <v>516</v>
+        <v>452</v>
       </c>
       <c r="C228" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="E228" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="F228">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G228" t="s">
-        <v>37</v>
+        <v>521</v>
       </c>
       <c r="H228" t="s">
-        <v>37</v>
+        <v>522</v>
       </c>
       <c r="I228" t="s">
-        <v>446</v>
+        <v>523</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="B229" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="C229" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="E229" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="F229">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G229" t="s">
-        <v>229</v>
+        <v>476</v>
       </c>
       <c r="H229" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="I229" t="s">
-        <v>450</v>
+        <v>282</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>407</v>
+        <v>506</v>
       </c>
       <c r="B230" t="s">
-        <v>408</v>
+        <v>507</v>
       </c>
       <c r="C230" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="E230" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="F230">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G230" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H230" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="I230" t="s">
-        <v>411</v>
+        <v>524</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>456</v>
+        <v>514</v>
       </c>
       <c r="B231" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="C231" t="s">
         <v>227</v>
       </c>
       <c r="E231" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="F231">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G231" t="s">
-        <v>525</v>
+        <v>390</v>
       </c>
       <c r="H231" t="s">
-        <v>526</v>
+        <v>391</v>
       </c>
       <c r="I231" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B232" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C232" t="s">
         <v>227</v>
       </c>
       <c r="E232" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F232">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G232" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="H232" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="I232" t="s">
-        <v>287</v>
+        <v>475</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="B233" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C233" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E233" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="F233">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G233" t="s">
-        <v>395</v>
+        <v>525</v>
       </c>
       <c r="H233" t="s">
-        <v>395</v>
+        <v>526</v>
       </c>
       <c r="I233" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B234" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C234" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E234" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="F234">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G234" t="s">
-        <v>395</v>
+        <v>529</v>
       </c>
       <c r="H234" t="s">
-        <v>396</v>
+        <v>530</v>
       </c>
       <c r="I234" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="B235" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="C235" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="E235" t="s">
-        <v>458</v>
+        <v>244</v>
       </c>
       <c r="F235">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G235" t="s">
-        <v>481</v>
+        <v>37</v>
       </c>
       <c r="H235" t="s">
-        <v>481</v>
+        <v>37</v>
       </c>
       <c r="I235" t="s">
-        <v>480</v>
+        <v>247</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="B236" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="C236" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="E236" t="s">
-        <v>458</v>
+        <v>535</v>
       </c>
       <c r="F236">
         <v>4.0</v>
       </c>
       <c r="G236" t="s">
-        <v>529</v>
+        <v>37</v>
       </c>
       <c r="H236" t="s">
-        <v>530</v>
+        <v>37</v>
       </c>
       <c r="I236" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B237" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C237" t="s">
         <v>215</v>
       </c>
       <c r="E237" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F237">
         <v>4.0</v>
       </c>
       <c r="G237" t="s">
-        <v>533</v>
+        <v>37</v>
       </c>
       <c r="H237" t="s">
-        <v>534</v>
+        <v>37</v>
       </c>
       <c r="I237" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B238" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C238" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E238" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F238">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G238" t="s">
         <v>37</v>
@@ -8417,189 +8393,189 @@
         <v>37</v>
       </c>
       <c r="I238" t="s">
-        <v>251</v>
+        <v>406</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B239" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C239" t="s">
-        <v>301</v>
+        <v>215</v>
       </c>
       <c r="E239" t="s">
-        <v>539</v>
+        <v>470</v>
       </c>
       <c r="F239">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G239" t="s">
-        <v>37</v>
+        <v>500</v>
       </c>
       <c r="H239" t="s">
-        <v>37</v>
+        <v>350</v>
       </c>
       <c r="I239" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>541</v>
+        <v>457</v>
       </c>
       <c r="B240" t="s">
-        <v>542</v>
+        <v>458</v>
       </c>
       <c r="C240" t="s">
-        <v>215</v>
+        <v>311</v>
       </c>
       <c r="E240" t="s">
-        <v>475</v>
+        <v>404</v>
       </c>
       <c r="F240">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G240" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="H240" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="I240" t="s">
-        <v>527</v>
+        <v>445</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="B241" t="s">
-        <v>544</v>
+        <v>503</v>
       </c>
       <c r="C241" t="s">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="E241" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="F241">
         <v>3.0</v>
       </c>
       <c r="G241" t="s">
-        <v>37</v>
+        <v>476</v>
       </c>
       <c r="H241" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="I241" t="s">
-        <v>411</v>
+        <v>462</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>545</v>
+        <v>382</v>
       </c>
       <c r="B242" t="s">
-        <v>546</v>
+        <v>383</v>
       </c>
       <c r="C242" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E242" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F242">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G242" t="s">
-        <v>505</v>
+        <v>37</v>
       </c>
       <c r="H242" t="s">
-        <v>354</v>
+        <v>37</v>
       </c>
       <c r="I242" t="s">
-        <v>547</v>
+        <v>384</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>462</v>
+        <v>497</v>
       </c>
       <c r="B243" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="C243" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E243" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="F243">
         <v>1.0</v>
       </c>
       <c r="G243" t="s">
-        <v>229</v>
+        <v>476</v>
       </c>
       <c r="H243" t="s">
-        <v>229</v>
+        <v>476</v>
       </c>
       <c r="I243" t="s">
-        <v>450</v>
+        <v>499</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B244" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C244" t="s">
-        <v>301</v>
+        <v>227</v>
       </c>
       <c r="E244" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F244">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G244" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="H244" t="s">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="I244" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>387</v>
+        <v>544</v>
       </c>
       <c r="B245" t="s">
-        <v>388</v>
+        <v>545</v>
       </c>
       <c r="C245" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="E245" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F245">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G245" t="s">
-        <v>37</v>
+        <v>546</v>
       </c>
       <c r="H245" t="s">
-        <v>37</v>
+        <v>201</v>
       </c>
       <c r="I245" t="s">
-        <v>389</v>
+        <v>516</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -8610,117 +8586,117 @@
         <v>503</v>
       </c>
       <c r="C246" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
       <c r="E246" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F246">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G246" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="H246" t="s">
-        <v>481</v>
+        <v>54</v>
       </c>
       <c r="I246" t="s">
-        <v>504</v>
+        <v>444</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B247" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="C247" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="E247" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="F247">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G247" t="s">
-        <v>481</v>
+        <v>37</v>
       </c>
       <c r="H247" t="s">
-        <v>396</v>
+        <v>37</v>
       </c>
       <c r="I247" t="s">
-        <v>464</v>
+        <v>256</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>548</v>
+        <v>497</v>
       </c>
       <c r="B248" t="s">
-        <v>549</v>
+        <v>498</v>
       </c>
       <c r="C248" t="s">
-        <v>215</v>
+        <v>345</v>
       </c>
       <c r="E248" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="F248">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G248" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H248" t="s">
         <v>201</v>
       </c>
       <c r="I248" t="s">
-        <v>520</v>
+        <v>282</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>506</v>
+        <v>548</v>
       </c>
       <c r="B249" t="s">
-        <v>507</v>
+        <v>549</v>
       </c>
       <c r="C249" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="E249" t="s">
-        <v>458</v>
+        <v>244</v>
       </c>
       <c r="F249">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G249" t="s">
-        <v>481</v>
+        <v>37</v>
       </c>
       <c r="H249" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="I249" t="s">
-        <v>449</v>
+        <v>384</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>541</v>
+        <v>473</v>
       </c>
       <c r="B250" t="s">
-        <v>542</v>
+        <v>474</v>
       </c>
       <c r="C250" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="E250" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F250">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G250" t="s">
         <v>37</v>
@@ -8729,50 +8705,50 @@
         <v>37</v>
       </c>
       <c r="I250" t="s">
-        <v>260</v>
+        <v>523</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B251" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C251" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E251" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F251">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G251" t="s">
+        <v>550</v>
+      </c>
+      <c r="H251" t="s">
         <v>551</v>
       </c>
-      <c r="H251" t="s">
-        <v>552</v>
-      </c>
       <c r="I251" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="B252" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="C252" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="E252" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F252">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G252" t="s">
         <v>37</v>
@@ -8781,215 +8757,215 @@
         <v>37</v>
       </c>
       <c r="I252" t="s">
-        <v>389</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="B253" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="C253" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="E253" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="F253">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G253" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="H253" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="I253" t="s">
-        <v>527</v>
+        <v>481</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B254" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C254" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="E254" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="F254">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G254" t="s">
-        <v>555</v>
+        <v>390</v>
       </c>
       <c r="H254" t="s">
-        <v>556</v>
+        <v>390</v>
       </c>
       <c r="I254" t="s">
-        <v>446</v>
+        <v>524</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>543</v>
+        <v>434</v>
       </c>
       <c r="B255" t="s">
-        <v>544</v>
+        <v>435</v>
       </c>
       <c r="C255" t="s">
-        <v>215</v>
+        <v>311</v>
       </c>
       <c r="E255" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="F255">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G255" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="H255" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="I255" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="B256" t="s">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="C256" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="E256" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="F256">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G256" t="s">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="H256" t="s">
-        <v>395</v>
+        <v>552</v>
       </c>
       <c r="I256" t="s">
-        <v>486</v>
+        <v>406</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>510</v>
+        <v>553</v>
       </c>
       <c r="B257" t="s">
-        <v>511</v>
+        <v>554</v>
       </c>
       <c r="C257" t="s">
-        <v>227</v>
+        <v>136</v>
       </c>
       <c r="E257" t="s">
-        <v>441</v>
+        <v>244</v>
       </c>
       <c r="F257">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G257" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="H257" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="I257" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>439</v>
+        <v>527</v>
       </c>
       <c r="B258" t="s">
-        <v>440</v>
+        <v>528</v>
       </c>
       <c r="C258" t="s">
-        <v>316</v>
+        <v>136</v>
       </c>
       <c r="E258" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="F258">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G258" t="s">
-        <v>395</v>
+        <v>555</v>
       </c>
       <c r="H258" t="s">
-        <v>395</v>
+        <v>556</v>
       </c>
       <c r="I258" t="s">
-        <v>528</v>
+        <v>477</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>545</v>
+        <v>473</v>
       </c>
       <c r="B259" t="s">
-        <v>546</v>
+        <v>474</v>
       </c>
       <c r="C259" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E259" t="s">
+        <v>470</v>
+      </c>
+      <c r="F259">
+        <v>1.0</v>
+      </c>
+      <c r="G259" t="s">
+        <v>37</v>
+      </c>
+      <c r="H259" t="s">
+        <v>37</v>
+      </c>
+      <c r="I259" t="s">
         <v>475</v>
-      </c>
-      <c r="F259">
-        <v>3.0</v>
-      </c>
-      <c r="G259" t="s">
-        <v>551</v>
-      </c>
-      <c r="H259" t="s">
-        <v>552</v>
-      </c>
-      <c r="I259" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="B260" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="C260" t="s">
         <v>136</v>
       </c>
       <c r="E260" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F260">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="G260" t="s">
-        <v>37</v>
+        <v>239</v>
       </c>
       <c r="H260" t="s">
-        <v>37</v>
+        <v>557</v>
       </c>
       <c r="I260" t="s">
-        <v>517</v>
+        <v>558</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -9003,296 +8979,296 @@
         <v>136</v>
       </c>
       <c r="E261" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F261">
         <v>7.0</v>
       </c>
       <c r="G261" t="s">
+        <v>37</v>
+      </c>
+      <c r="H261" t="s">
+        <v>37</v>
+      </c>
+      <c r="I261" t="s">
         <v>559</v>
-      </c>
-      <c r="H261" t="s">
-        <v>560</v>
-      </c>
-      <c r="I261" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="B262" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="C262" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="E262" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F262">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G262" t="s">
-        <v>37</v>
+        <v>546</v>
       </c>
       <c r="H262" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="I262" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>548</v>
+        <v>504</v>
       </c>
       <c r="B263" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
       <c r="C263" t="s">
-        <v>136</v>
+        <v>345</v>
       </c>
       <c r="E263" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="F263">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G263" t="s">
-        <v>243</v>
+        <v>390</v>
       </c>
       <c r="H263" t="s">
-        <v>561</v>
+        <v>390</v>
       </c>
       <c r="I263" t="s">
-        <v>562</v>
+        <v>481</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="B264" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="C264" t="s">
-        <v>136</v>
+        <v>296</v>
       </c>
       <c r="E264" t="s">
-        <v>248</v>
+        <v>436</v>
       </c>
       <c r="F264">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G264" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="H264" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="I264" t="s">
-        <v>563</v>
+        <v>524</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B265" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C265" t="s">
-        <v>215</v>
+        <v>296</v>
       </c>
       <c r="E265" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="F265">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G265" t="s">
-        <v>550</v>
+        <v>390</v>
       </c>
       <c r="H265" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="I265" t="s">
-        <v>461</v>
+        <v>282</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>508</v>
+        <v>468</v>
       </c>
       <c r="B266" t="s">
-        <v>509</v>
+        <v>469</v>
       </c>
       <c r="C266" t="s">
-        <v>349</v>
+        <v>215</v>
       </c>
       <c r="E266" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="F266">
         <v>1.0</v>
       </c>
       <c r="G266" t="s">
-        <v>395</v>
+        <v>546</v>
       </c>
       <c r="H266" t="s">
-        <v>395</v>
+        <v>546</v>
       </c>
       <c r="I266" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B267" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C267" t="s">
-        <v>301</v>
+        <v>136</v>
       </c>
       <c r="E267" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="F267">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G267" t="s">
-        <v>395</v>
+        <v>560</v>
       </c>
       <c r="H267" t="s">
-        <v>395</v>
+        <v>561</v>
       </c>
       <c r="I267" t="s">
-        <v>528</v>
+        <v>562</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="B268" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="C268" t="s">
-        <v>301</v>
+        <v>168</v>
       </c>
       <c r="E268" t="s">
-        <v>441</v>
+        <v>244</v>
       </c>
       <c r="F268">
         <v>1.0</v>
       </c>
       <c r="G268" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="H268" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="I268" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>473</v>
+        <v>539</v>
       </c>
       <c r="B269" t="s">
-        <v>474</v>
+        <v>540</v>
       </c>
       <c r="C269" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E269" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F269">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G269" t="s">
-        <v>550</v>
+        <v>37</v>
       </c>
       <c r="H269" t="s">
-        <v>550</v>
+        <v>37</v>
       </c>
       <c r="I269" t="s">
-        <v>480</v>
+        <v>516</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>515</v>
+        <v>479</v>
       </c>
       <c r="B270" t="s">
-        <v>516</v>
+        <v>480</v>
       </c>
       <c r="C270" t="s">
-        <v>136</v>
+        <v>311</v>
       </c>
       <c r="E270" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="F270">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G270" t="s">
-        <v>564</v>
+        <v>390</v>
       </c>
       <c r="H270" t="s">
-        <v>565</v>
+        <v>390</v>
       </c>
       <c r="I270" t="s">
-        <v>566</v>
+        <v>481</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="B271" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="C271" t="s">
         <v>168</v>
       </c>
       <c r="E271" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F271">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G271" t="s">
-        <v>37</v>
+        <v>546</v>
       </c>
       <c r="H271" t="s">
-        <v>37</v>
+        <v>563</v>
       </c>
       <c r="I271" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="B272" t="s">
-        <v>544</v>
+        <v>329</v>
       </c>
       <c r="C272" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="E272" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F272">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G272" t="s">
         <v>37</v>
@@ -9301,125 +9277,125 @@
         <v>37</v>
       </c>
       <c r="I272" t="s">
-        <v>520</v>
+        <v>257</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="B273" t="s">
-        <v>485</v>
+        <v>532</v>
       </c>
       <c r="C273" t="s">
-        <v>316</v>
+        <v>146</v>
       </c>
       <c r="E273" t="s">
-        <v>441</v>
+        <v>244</v>
       </c>
       <c r="F273">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G273" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="H273" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="I273" t="s">
-        <v>486</v>
+        <v>255</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="B274" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="C274" t="s">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="E274" t="s">
-        <v>475</v>
+        <v>535</v>
       </c>
       <c r="F274">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G274" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="H274" t="s">
+        <v>566</v>
+      </c>
+      <c r="I274" t="s">
         <v>567</v>
-      </c>
-      <c r="I274" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="B275" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="C275" t="s">
-        <v>316</v>
+        <v>168</v>
       </c>
       <c r="E275" t="s">
+        <v>470</v>
+      </c>
+      <c r="F275">
+        <v>5.0</v>
+      </c>
+      <c r="G275" t="s">
+        <v>37</v>
+      </c>
+      <c r="H275" t="s">
+        <v>37</v>
+      </c>
+      <c r="I275" t="s">
         <v>441</v>
-      </c>
-      <c r="F275">
-        <v>1.0</v>
-      </c>
-      <c r="G275" t="s">
-        <v>395</v>
-      </c>
-      <c r="H275" t="s">
-        <v>395</v>
-      </c>
-      <c r="I275" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>332</v>
+        <v>508</v>
       </c>
       <c r="B276" t="s">
-        <v>333</v>
+        <v>509</v>
       </c>
       <c r="C276" t="s">
         <v>136</v>
       </c>
       <c r="E276" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F276">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G276" t="s">
-        <v>37</v>
+        <v>568</v>
       </c>
       <c r="H276" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="I276" t="s">
-        <v>261</v>
+        <v>523</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>535</v>
+        <v>364</v>
       </c>
       <c r="B277" t="s">
-        <v>536</v>
+        <v>365</v>
       </c>
       <c r="C277" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="E277" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F277">
         <v>5.0</v>
@@ -9431,50 +9407,50 @@
         <v>37</v>
       </c>
       <c r="I277" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B278" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C278" t="s">
-        <v>301</v>
+        <v>215</v>
       </c>
       <c r="E278" t="s">
-        <v>539</v>
+        <v>470</v>
       </c>
       <c r="F278">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G278" t="s">
-        <v>570</v>
+        <v>37</v>
       </c>
       <c r="H278" t="s">
-        <v>570</v>
+        <v>37</v>
       </c>
       <c r="I278" t="s">
-        <v>571</v>
+        <v>523</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>545</v>
+        <v>488</v>
       </c>
       <c r="B279" t="s">
-        <v>546</v>
+        <v>489</v>
       </c>
       <c r="C279" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="E279" t="s">
-        <v>475</v>
+        <v>175</v>
       </c>
       <c r="F279">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G279" t="s">
         <v>37</v>
@@ -9483,76 +9459,76 @@
         <v>37</v>
       </c>
       <c r="I279" t="s">
-        <v>446</v>
+        <v>177</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>512</v>
+        <v>553</v>
       </c>
       <c r="B280" t="s">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="C280" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E280" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F280">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G280" t="s">
-        <v>572</v>
+        <v>37</v>
       </c>
       <c r="H280" t="s">
-        <v>573</v>
+        <v>37</v>
       </c>
       <c r="I280" t="s">
-        <v>461</v>
+        <v>247</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>368</v>
+        <v>544</v>
       </c>
       <c r="B281" t="s">
-        <v>369</v>
+        <v>545</v>
       </c>
       <c r="C281" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="E281" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F281">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G281" t="s">
-        <v>37</v>
+        <v>560</v>
       </c>
       <c r="H281" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="I281" t="s">
-        <v>259</v>
+        <v>571</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>574</v>
+        <v>531</v>
       </c>
       <c r="B282" t="s">
-        <v>575</v>
+        <v>532</v>
       </c>
       <c r="C282" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="E282" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F282">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G282" t="s">
         <v>37</v>
@@ -9561,99 +9537,99 @@
         <v>37</v>
       </c>
       <c r="I282" t="s">
-        <v>527</v>
+        <v>361</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="B283" t="s">
-        <v>494</v>
+        <v>542</v>
       </c>
       <c r="C283" t="s">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="E283" t="s">
-        <v>175</v>
+        <v>470</v>
       </c>
       <c r="F283">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="G283" t="s">
-        <v>37</v>
+        <v>560</v>
       </c>
       <c r="H283" t="s">
-        <v>37</v>
+        <v>572</v>
       </c>
       <c r="I283" t="s">
-        <v>177</v>
+        <v>573</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="B284" t="s">
+        <v>542</v>
+      </c>
+      <c r="C284" t="s">
+        <v>136</v>
+      </c>
+      <c r="E284" t="s">
+        <v>470</v>
+      </c>
+      <c r="F284">
+        <v>14.0</v>
+      </c>
+      <c r="G284" t="s">
+        <v>574</v>
+      </c>
+      <c r="H284" t="s">
+        <v>575</v>
+      </c>
+      <c r="I284" t="s">
         <v>558</v>
-      </c>
-      <c r="C284" t="s">
-        <v>146</v>
-      </c>
-      <c r="E284" t="s">
-        <v>248</v>
-      </c>
-      <c r="F284">
-        <v>2.0</v>
-      </c>
-      <c r="G284" t="s">
-        <v>37</v>
-      </c>
-      <c r="H284" t="s">
-        <v>37</v>
-      </c>
-      <c r="I284" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B285" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C285" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="E285" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F285">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G285" t="s">
-        <v>564</v>
+        <v>37</v>
       </c>
       <c r="H285" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="I285" t="s">
-        <v>576</v>
+        <v>384</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>535</v>
+        <v>364</v>
       </c>
       <c r="B286" t="s">
-        <v>536</v>
+        <v>365</v>
       </c>
       <c r="C286" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="E286" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F286">
         <v>3.0</v>
@@ -9665,102 +9641,102 @@
         <v>37</v>
       </c>
       <c r="I286" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B287" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="C287" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="E287" t="s">
-        <v>475</v>
+        <v>175</v>
       </c>
       <c r="F287">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="G287" t="s">
-        <v>564</v>
+        <v>37</v>
       </c>
       <c r="H287" t="s">
-        <v>577</v>
+        <v>37</v>
       </c>
       <c r="I287" t="s">
-        <v>578</v>
+        <v>202</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>545</v>
+        <v>364</v>
       </c>
       <c r="B288" t="s">
-        <v>546</v>
+        <v>365</v>
       </c>
       <c r="C288" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E288" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F288">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="G288" t="s">
-        <v>579</v>
+        <v>37</v>
       </c>
       <c r="H288" t="s">
-        <v>580</v>
+        <v>37</v>
       </c>
       <c r="I288" t="s">
-        <v>562</v>
+        <v>255</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>557</v>
+        <v>511</v>
       </c>
       <c r="B289" t="s">
-        <v>558</v>
+        <v>512</v>
       </c>
       <c r="C289" t="s">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="E289" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F289">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G289" t="s">
-        <v>37</v>
+        <v>578</v>
       </c>
       <c r="H289" t="s">
-        <v>37</v>
+        <v>579</v>
       </c>
       <c r="I289" t="s">
-        <v>389</v>
+        <v>516</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>368</v>
+        <v>576</v>
       </c>
       <c r="B290" t="s">
-        <v>369</v>
+        <v>577</v>
       </c>
       <c r="C290" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E290" t="s">
-        <v>248</v>
+        <v>175</v>
       </c>
       <c r="F290">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G290" t="s">
         <v>37</v>
@@ -9769,24 +9745,24 @@
         <v>37</v>
       </c>
       <c r="I290" t="s">
-        <v>365</v>
+        <v>202</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>581</v>
+        <v>382</v>
       </c>
       <c r="B291" t="s">
-        <v>582</v>
+        <v>383</v>
       </c>
       <c r="C291" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="E291" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="F291">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G291" t="s">
         <v>37</v>
@@ -9795,24 +9771,24 @@
         <v>37</v>
       </c>
       <c r="I291" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
-        <v>368</v>
+        <v>537</v>
       </c>
       <c r="B292" t="s">
-        <v>369</v>
+        <v>538</v>
       </c>
       <c r="C292" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E292" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F292">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G292" t="s">
         <v>37</v>
@@ -9821,47 +9797,47 @@
         <v>37</v>
       </c>
       <c r="I292" t="s">
-        <v>259</v>
+        <v>475</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>515</v>
+        <v>580</v>
       </c>
       <c r="B293" t="s">
-        <v>516</v>
+        <v>581</v>
       </c>
       <c r="C293" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="E293" t="s">
-        <v>475</v>
+        <v>582</v>
       </c>
       <c r="F293">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G293" t="s">
-        <v>583</v>
+        <v>37</v>
       </c>
       <c r="H293" t="s">
-        <v>584</v>
+        <v>37</v>
       </c>
       <c r="I293" t="s">
-        <v>520</v>
+        <v>252</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B294" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C294" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="E294" t="s">
-        <v>175</v>
+        <v>585</v>
       </c>
       <c r="F294">
         <v>1.0</v>
@@ -9873,24 +9849,21 @@
         <v>37</v>
       </c>
       <c r="I294" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>387</v>
+        <v>586</v>
       </c>
       <c r="B295" t="s">
-        <v>388</v>
-      </c>
-      <c r="C295" t="s">
-        <v>146</v>
+        <v>587</v>
       </c>
       <c r="E295" t="s">
-        <v>248</v>
+        <v>588</v>
       </c>
       <c r="F295">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G295" t="s">
         <v>37</v>
@@ -9899,21 +9872,18 @@
         <v>37</v>
       </c>
       <c r="I295" t="s">
-        <v>259</v>
+        <v>589</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>541</v>
+        <v>590</v>
       </c>
       <c r="B296" t="s">
-        <v>542</v>
-      </c>
-      <c r="C296" t="s">
-        <v>136</v>
+        <v>591</v>
       </c>
       <c r="E296" t="s">
-        <v>475</v>
+        <v>104</v>
       </c>
       <c r="F296">
         <v>1.0</v>
@@ -9925,24 +9895,21 @@
         <v>37</v>
       </c>
       <c r="I296" t="s">
-        <v>480</v>
+        <v>109</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B297" t="s">
-        <v>586</v>
-      </c>
-      <c r="C297" t="s">
-        <v>168</v>
+        <v>593</v>
       </c>
       <c r="E297" t="s">
-        <v>587</v>
+        <v>467</v>
       </c>
       <c r="F297">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G297" t="s">
         <v>37</v>
@@ -9951,21 +9918,18 @@
         <v>37</v>
       </c>
       <c r="I297" t="s">
-        <v>256</v>
+        <v>399</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B298" t="s">
-        <v>589</v>
-      </c>
-      <c r="C298" t="s">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="E298" t="s">
-        <v>590</v>
+        <v>114</v>
       </c>
       <c r="F298">
         <v>1.0</v>
@@ -9977,24 +9941,24 @@
         <v>37</v>
       </c>
       <c r="I298" t="s">
-        <v>312</v>
+        <v>109</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B299" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C299" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="E299" t="s">
-        <v>593</v>
+        <v>137</v>
       </c>
       <c r="F299">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G299" t="s">
         <v>37</v>
@@ -10003,21 +9967,24 @@
         <v>37</v>
       </c>
       <c r="I299" t="s">
-        <v>211</v>
+        <v>597</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B300" t="s">
-        <v>595</v>
+        <v>596</v>
+      </c>
+      <c r="C300" t="s">
+        <v>136</v>
       </c>
       <c r="E300" t="s">
-        <v>596</v>
+        <v>137</v>
       </c>
       <c r="F300">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G300" t="s">
         <v>37</v>
@@ -10026,21 +9993,24 @@
         <v>37</v>
       </c>
       <c r="I300" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>598</v>
+        <v>488</v>
       </c>
       <c r="B301" t="s">
-        <v>599</v>
+        <v>489</v>
+      </c>
+      <c r="C301" t="s">
+        <v>168</v>
       </c>
       <c r="E301" t="s">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="F301">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G301" t="s">
         <v>37</v>
@@ -10049,19 +10019,22 @@
         <v>37</v>
       </c>
       <c r="I301" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
+        <v>599</v>
+      </c>
+      <c r="B302" t="s">
         <v>600</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" t="s">
+        <v>168</v>
+      </c>
+      <c r="E302" t="s">
         <v>601</v>
       </c>
-      <c r="E302" t="s">
-        <v>472</v>
-      </c>
       <c r="F302">
         <v>1.0</v>
       </c>
@@ -10072,18 +10045,21 @@
         <v>37</v>
       </c>
       <c r="I302" t="s">
-        <v>404</v>
+        <v>602</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>602</v>
+        <v>417</v>
       </c>
       <c r="B303" t="s">
-        <v>103</v>
+        <v>418</v>
+      </c>
+      <c r="C303" t="s">
+        <v>168</v>
       </c>
       <c r="E303" t="s">
-        <v>114</v>
+        <v>250</v>
       </c>
       <c r="F303">
         <v>1.0</v>
@@ -10095,24 +10071,24 @@
         <v>37</v>
       </c>
       <c r="I303" t="s">
-        <v>109</v>
+        <v>252</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="B304" t="s">
-        <v>604</v>
+        <v>554</v>
       </c>
       <c r="C304" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="E304" t="s">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="F304">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="G304" t="s">
         <v>37</v>
@@ -10121,24 +10097,24 @@
         <v>37</v>
       </c>
       <c r="I304" t="s">
-        <v>605</v>
+        <v>513</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>603</v>
+        <v>364</v>
       </c>
       <c r="B305" t="s">
-        <v>604</v>
+        <v>365</v>
       </c>
       <c r="C305" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="E305" t="s">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="F305">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G305" t="s">
         <v>37</v>
@@ -10147,24 +10123,24 @@
         <v>37</v>
       </c>
       <c r="I305" t="s">
-        <v>606</v>
+        <v>384</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>493</v>
+        <v>548</v>
       </c>
       <c r="B306" t="s">
-        <v>494</v>
+        <v>549</v>
       </c>
       <c r="C306" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="E306" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="F306">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G306" t="s">
         <v>37</v>
@@ -10173,24 +10149,24 @@
         <v>37</v>
       </c>
       <c r="I306" t="s">
-        <v>177</v>
+        <v>384</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>607</v>
+        <v>382</v>
       </c>
       <c r="B307" t="s">
-        <v>608</v>
+        <v>383</v>
       </c>
       <c r="C307" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="E307" t="s">
-        <v>609</v>
+        <v>244</v>
       </c>
       <c r="F307">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G307" t="s">
         <v>37</v>
@@ -10199,24 +10175,24 @@
         <v>37</v>
       </c>
       <c r="I307" t="s">
-        <v>610</v>
+        <v>255</v>
       </c>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
-        <v>422</v>
+        <v>531</v>
       </c>
       <c r="B308" t="s">
-        <v>423</v>
+        <v>532</v>
       </c>
       <c r="C308" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="E308" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="F308">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G308" t="s">
         <v>37</v>
@@ -10225,24 +10201,24 @@
         <v>37</v>
       </c>
       <c r="I308" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="B309" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="C309" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="E309" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F309">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G309" t="s">
         <v>37</v>
@@ -10251,24 +10227,24 @@
         <v>37</v>
       </c>
       <c r="I309" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
-        <v>368</v>
+        <v>539</v>
       </c>
       <c r="B310" t="s">
-        <v>369</v>
+        <v>540</v>
       </c>
       <c r="C310" t="s">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c r="E310" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F310">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G310" t="s">
         <v>37</v>
@@ -10277,24 +10253,24 @@
         <v>37</v>
       </c>
       <c r="I310" t="s">
-        <v>389</v>
+        <v>603</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="B311" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="C311" t="s">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="E311" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F311">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G311" t="s">
         <v>37</v>
@@ -10303,24 +10279,24 @@
         <v>37</v>
       </c>
       <c r="I311" t="s">
-        <v>389</v>
+        <v>456</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>387</v>
+        <v>511</v>
       </c>
       <c r="B312" t="s">
-        <v>388</v>
+        <v>512</v>
       </c>
       <c r="C312" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="E312" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F312">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G312" t="s">
         <v>37</v>
@@ -10329,24 +10305,24 @@
         <v>37</v>
       </c>
       <c r="I312" t="s">
-        <v>259</v>
+        <v>406</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="B313" t="s">
-        <v>536</v>
+        <v>570</v>
       </c>
       <c r="C313" t="s">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c r="E313" t="s">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="F313">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G313" t="s">
         <v>37</v>
@@ -10355,24 +10331,21 @@
         <v>37</v>
       </c>
       <c r="I313" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>543</v>
+        <v>604</v>
       </c>
       <c r="B314" t="s">
-        <v>544</v>
-      </c>
-      <c r="C314" t="s">
-        <v>146</v>
+        <v>605</v>
       </c>
       <c r="E314" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F314">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G314" t="s">
         <v>37</v>
@@ -10381,24 +10354,21 @@
         <v>37</v>
       </c>
       <c r="I314" t="s">
-        <v>547</v>
+        <v>176</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>543</v>
+        <v>606</v>
       </c>
       <c r="B315" t="s">
-        <v>544</v>
-      </c>
-      <c r="C315" t="s">
-        <v>136</v>
+        <v>607</v>
       </c>
       <c r="E315" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F315">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G315" t="s">
         <v>37</v>
@@ -10407,24 +10377,21 @@
         <v>37</v>
       </c>
       <c r="I315" t="s">
-        <v>611</v>
+        <v>236</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>541</v>
+        <v>608</v>
       </c>
       <c r="B316" t="s">
-        <v>542</v>
-      </c>
-      <c r="C316" t="s">
-        <v>146</v>
+        <v>609</v>
       </c>
       <c r="E316" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F316">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G316" t="s">
         <v>37</v>
@@ -10433,24 +10400,21 @@
         <v>37</v>
       </c>
       <c r="I316" t="s">
-        <v>612</v>
+        <v>258</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
-        <v>515</v>
+        <v>610</v>
       </c>
       <c r="B317" t="s">
-        <v>516</v>
-      </c>
-      <c r="C317" t="s">
-        <v>168</v>
+        <v>611</v>
       </c>
       <c r="E317" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F317">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G317" t="s">
         <v>37</v>
@@ -10459,24 +10423,21 @@
         <v>37</v>
       </c>
       <c r="I317" t="s">
-        <v>411</v>
+        <v>350</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
-        <v>574</v>
+        <v>612</v>
       </c>
       <c r="B318" t="s">
-        <v>575</v>
-      </c>
-      <c r="C318" t="s">
-        <v>136</v>
+        <v>613</v>
       </c>
       <c r="E318" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="F318">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G318" t="s">
         <v>37</v>
@@ -10485,21 +10446,21 @@
         <v>37</v>
       </c>
       <c r="I318" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B319" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E319" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F319">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G319" t="s">
         <v>37</v>
@@ -10508,21 +10469,21 @@
         <v>37</v>
       </c>
       <c r="I319" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B320" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E320" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F320">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G320" t="s">
         <v>37</v>
@@ -10531,18 +10492,18 @@
         <v>37</v>
       </c>
       <c r="I320" t="s">
-        <v>236</v>
+        <v>561</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B321" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E321" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F321">
         <v>1.0</v>
@@ -10554,21 +10515,21 @@
         <v>37</v>
       </c>
       <c r="I321" t="s">
-        <v>262</v>
+        <v>78</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B322" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E322" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F322">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G322" t="s">
         <v>37</v>
@@ -10577,67 +10538,76 @@
         <v>37</v>
       </c>
       <c r="I322" t="s">
-        <v>354</v>
+        <v>485</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
-        <v>621</v>
+        <v>533</v>
       </c>
       <c r="B323" t="s">
+        <v>534</v>
+      </c>
+      <c r="C323" t="s">
+        <v>345</v>
+      </c>
+      <c r="E323" t="s">
+        <v>535</v>
+      </c>
+      <c r="F323">
+        <v>3.0</v>
+      </c>
+      <c r="G323" t="s">
+        <v>37</v>
+      </c>
+      <c r="H323" t="s">
+        <v>37</v>
+      </c>
+      <c r="I323" t="s">
         <v>622</v>
-      </c>
-      <c r="E323" t="s">
-        <v>489</v>
-      </c>
-      <c r="F323">
-        <v>1.0</v>
-      </c>
-      <c r="G323" t="s">
-        <v>37</v>
-      </c>
-      <c r="H323" t="s">
-        <v>37</v>
-      </c>
-      <c r="I323" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
+        <v>533</v>
+      </c>
+      <c r="B324" t="s">
+        <v>534</v>
+      </c>
+      <c r="C324" t="s">
+        <v>268</v>
+      </c>
+      <c r="E324" t="s">
+        <v>535</v>
+      </c>
+      <c r="F324">
+        <v>7.0</v>
+      </c>
+      <c r="G324" t="s">
+        <v>37</v>
+      </c>
+      <c r="H324" t="s">
+        <v>37</v>
+      </c>
+      <c r="I324" t="s">
         <v>623</v>
-      </c>
-      <c r="B324" t="s">
-        <v>624</v>
-      </c>
-      <c r="E324" t="s">
-        <v>489</v>
-      </c>
-      <c r="F324">
-        <v>1.0</v>
-      </c>
-      <c r="G324" t="s">
-        <v>37</v>
-      </c>
-      <c r="H324" t="s">
-        <v>37</v>
-      </c>
-      <c r="I324" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
-        <v>625</v>
+        <v>533</v>
       </c>
       <c r="B325" t="s">
-        <v>626</v>
+        <v>534</v>
+      </c>
+      <c r="C325" t="s">
+        <v>227</v>
       </c>
       <c r="E325" t="s">
-        <v>489</v>
+        <v>535</v>
       </c>
       <c r="F325">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G325" t="s">
         <v>37</v>
@@ -10646,21 +10616,24 @@
         <v>37</v>
       </c>
       <c r="I325" t="s">
-        <v>565</v>
+        <v>536</v>
       </c>
     </row>
     <row r="326" spans="1:9">
       <c r="A326" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B326" t="s">
-        <v>628</v>
+        <v>625</v>
+      </c>
+      <c r="C326" t="s">
+        <v>345</v>
       </c>
       <c r="E326" t="s">
-        <v>489</v>
+        <v>535</v>
       </c>
       <c r="F326">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G326" t="s">
         <v>37</v>
@@ -10669,21 +10642,24 @@
         <v>37</v>
       </c>
       <c r="I326" t="s">
-        <v>78</v>
+        <v>536</v>
       </c>
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B327" t="s">
-        <v>630</v>
+        <v>625</v>
+      </c>
+      <c r="C327" t="s">
+        <v>268</v>
       </c>
       <c r="E327" t="s">
-        <v>489</v>
+        <v>535</v>
       </c>
       <c r="F327">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G327" t="s">
         <v>37</v>
@@ -10692,24 +10668,24 @@
         <v>37</v>
       </c>
       <c r="I327" t="s">
-        <v>490</v>
+        <v>626</v>
       </c>
     </row>
     <row r="328" spans="1:9">
       <c r="A328" t="s">
-        <v>537</v>
+        <v>624</v>
       </c>
       <c r="B328" t="s">
-        <v>538</v>
+        <v>625</v>
       </c>
       <c r="C328" t="s">
-        <v>349</v>
+        <v>227</v>
       </c>
       <c r="E328" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F328">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G328" t="s">
         <v>37</v>
@@ -10718,24 +10694,24 @@
         <v>37</v>
       </c>
       <c r="I328" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
-        <v>537</v>
+        <v>624</v>
       </c>
       <c r="B329" t="s">
-        <v>538</v>
+        <v>625</v>
       </c>
       <c r="C329" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="E329" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F329">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G329" t="s">
         <v>37</v>
@@ -10744,24 +10720,24 @@
         <v>37</v>
       </c>
       <c r="I329" t="s">
-        <v>632</v>
+        <v>536</v>
       </c>
     </row>
     <row r="330" spans="1:9">
       <c r="A330" t="s">
-        <v>537</v>
+        <v>628</v>
       </c>
       <c r="B330" t="s">
-        <v>538</v>
+        <v>625</v>
       </c>
       <c r="C330" t="s">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="E330" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F330">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G330" t="s">
         <v>37</v>
@@ -10770,24 +10746,24 @@
         <v>37</v>
       </c>
       <c r="I330" t="s">
-        <v>540</v>
+        <v>629</v>
       </c>
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B331" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C331" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E331" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F331">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G331" t="s">
         <v>37</v>
@@ -10796,47 +10772,47 @@
         <v>37</v>
       </c>
       <c r="I331" t="s">
-        <v>540</v>
+        <v>632</v>
       </c>
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
+        <v>630</v>
+      </c>
+      <c r="B332" t="s">
+        <v>631</v>
+      </c>
+      <c r="C332" t="s">
+        <v>227</v>
+      </c>
+      <c r="E332" t="s">
+        <v>535</v>
+      </c>
+      <c r="F332">
+        <v>5.0</v>
+      </c>
+      <c r="G332" t="s">
+        <v>37</v>
+      </c>
+      <c r="H332" t="s">
+        <v>37</v>
+      </c>
+      <c r="I332" t="s">
         <v>633</v>
-      </c>
-      <c r="B332" t="s">
-        <v>634</v>
-      </c>
-      <c r="C332" t="s">
-        <v>272</v>
-      </c>
-      <c r="E332" t="s">
-        <v>539</v>
-      </c>
-      <c r="F332">
-        <v>6.0</v>
-      </c>
-      <c r="G332" t="s">
-        <v>37</v>
-      </c>
-      <c r="H332" t="s">
-        <v>37</v>
-      </c>
-      <c r="I332" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="333" spans="1:9">
       <c r="A333" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B333" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C333" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="E333" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F333">
         <v>5.0</v>
@@ -10848,47 +10824,47 @@
         <v>37</v>
       </c>
       <c r="I333" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="334" spans="1:9">
       <c r="A334" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B334" t="s">
+        <v>631</v>
+      </c>
+      <c r="C334" t="s">
+        <v>311</v>
+      </c>
+      <c r="E334" t="s">
+        <v>535</v>
+      </c>
+      <c r="F334">
+        <v>2.0</v>
+      </c>
+      <c r="G334" t="s">
+        <v>37</v>
+      </c>
+      <c r="H334" t="s">
+        <v>37</v>
+      </c>
+      <c r="I334" t="s">
         <v>634</v>
-      </c>
-      <c r="C334" t="s">
-        <v>301</v>
-      </c>
-      <c r="E334" t="s">
-        <v>539</v>
-      </c>
-      <c r="F334">
-        <v>4.0</v>
-      </c>
-      <c r="G334" t="s">
-        <v>37</v>
-      </c>
-      <c r="H334" t="s">
-        <v>37</v>
-      </c>
-      <c r="I334" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="335" spans="1:9">
       <c r="A335" t="s">
-        <v>637</v>
+        <v>564</v>
       </c>
       <c r="B335" t="s">
-        <v>634</v>
+        <v>565</v>
       </c>
       <c r="C335" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="E335" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F335">
         <v>1.0</v>
@@ -10900,24 +10876,24 @@
         <v>37</v>
       </c>
       <c r="I335" t="s">
-        <v>638</v>
+        <v>567</v>
       </c>
     </row>
     <row r="336" spans="1:9">
       <c r="A336" t="s">
-        <v>639</v>
+        <v>564</v>
       </c>
       <c r="B336" t="s">
-        <v>640</v>
+        <v>565</v>
       </c>
       <c r="C336" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E336" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F336">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G336" t="s">
         <v>37</v>
@@ -10926,24 +10902,24 @@
         <v>37</v>
       </c>
       <c r="I336" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="337" spans="1:9">
       <c r="A337" t="s">
-        <v>639</v>
+        <v>564</v>
       </c>
       <c r="B337" t="s">
-        <v>640</v>
+        <v>565</v>
       </c>
       <c r="C337" t="s">
         <v>227</v>
       </c>
       <c r="E337" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F337">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G337" t="s">
         <v>37</v>
@@ -10952,24 +10928,24 @@
         <v>37</v>
       </c>
       <c r="I337" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="338" spans="1:9">
       <c r="A338" t="s">
-        <v>639</v>
+        <v>564</v>
       </c>
       <c r="B338" t="s">
-        <v>640</v>
+        <v>565</v>
       </c>
       <c r="C338" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E338" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F338">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G338" t="s">
         <v>37</v>
@@ -10978,21 +10954,21 @@
         <v>37</v>
       </c>
       <c r="I338" t="s">
-        <v>642</v>
+        <v>567</v>
       </c>
     </row>
     <row r="339" spans="1:9">
       <c r="A339" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B339" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C339" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="E339" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F339">
         <v>2.0</v>
@@ -11004,24 +10980,24 @@
         <v>37</v>
       </c>
       <c r="I339" t="s">
-        <v>643</v>
+        <v>444</v>
       </c>
     </row>
     <row r="340" spans="1:9">
       <c r="A340" t="s">
-        <v>568</v>
+        <v>636</v>
       </c>
       <c r="B340" t="s">
-        <v>569</v>
+        <v>637</v>
       </c>
       <c r="C340" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E340" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F340">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G340" t="s">
         <v>37</v>
@@ -11030,24 +11006,24 @@
         <v>37</v>
       </c>
       <c r="I340" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
     <row r="341" spans="1:9">
       <c r="A341" t="s">
-        <v>568</v>
+        <v>636</v>
       </c>
       <c r="B341" t="s">
-        <v>569</v>
+        <v>637</v>
       </c>
       <c r="C341" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="E341" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F341">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G341" t="s">
         <v>37</v>
@@ -11056,24 +11032,24 @@
         <v>37</v>
       </c>
       <c r="I341" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="342" spans="1:9">
       <c r="A342" t="s">
-        <v>568</v>
+        <v>636</v>
       </c>
       <c r="B342" t="s">
-        <v>569</v>
+        <v>637</v>
       </c>
       <c r="C342" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="E342" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F342">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G342" t="s">
         <v>37</v>
@@ -11082,24 +11058,24 @@
         <v>37</v>
       </c>
       <c r="I342" t="s">
-        <v>646</v>
+        <v>444</v>
       </c>
     </row>
     <row r="343" spans="1:9">
       <c r="A343" t="s">
-        <v>568</v>
+        <v>639</v>
       </c>
       <c r="B343" t="s">
-        <v>569</v>
+        <v>640</v>
       </c>
       <c r="C343" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="E343" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F343">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G343" t="s">
         <v>37</v>
@@ -11108,24 +11084,24 @@
         <v>37</v>
       </c>
       <c r="I343" t="s">
-        <v>571</v>
+        <v>444</v>
       </c>
     </row>
     <row r="344" spans="1:9">
       <c r="A344" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B344" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C344" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E344" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F344">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G344" t="s">
         <v>37</v>
@@ -11134,21 +11110,21 @@
         <v>37</v>
       </c>
       <c r="I344" t="s">
-        <v>449</v>
+        <v>642</v>
       </c>
     </row>
     <row r="345" spans="1:9">
       <c r="A345" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B345" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C345" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="E345" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F345">
         <v>3.0</v>
@@ -11160,24 +11136,24 @@
         <v>37</v>
       </c>
       <c r="I345" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
     </row>
     <row r="346" spans="1:9">
       <c r="A346" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B346" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C346" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="E346" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F346">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G346" t="s">
         <v>37</v>
@@ -11186,24 +11162,24 @@
         <v>37</v>
       </c>
       <c r="I346" t="s">
-        <v>649</v>
+        <v>444</v>
       </c>
     </row>
     <row r="347" spans="1:9">
       <c r="A347" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B347" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C347" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E347" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F347">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G347" t="s">
         <v>37</v>
@@ -11212,21 +11188,21 @@
         <v>37</v>
       </c>
       <c r="I347" t="s">
-        <v>449</v>
+        <v>368</v>
       </c>
     </row>
     <row r="348" spans="1:9">
       <c r="A348" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="B348" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C348" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E348" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F348">
         <v>2.0</v>
@@ -11238,24 +11214,24 @@
         <v>37</v>
       </c>
       <c r="I348" t="s">
-        <v>449</v>
+        <v>634</v>
       </c>
     </row>
     <row r="349" spans="1:9">
       <c r="A349" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="B349" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C349" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E349" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F349">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G349" t="s">
         <v>37</v>
@@ -11264,21 +11240,21 @@
         <v>37</v>
       </c>
       <c r="I349" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
     </row>
     <row r="350" spans="1:9">
       <c r="A350" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="B350" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C350" t="s">
         <v>227</v>
       </c>
       <c r="E350" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F350">
         <v>3.0</v>
@@ -11290,24 +11266,24 @@
         <v>37</v>
       </c>
       <c r="I350" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="351" spans="1:9">
       <c r="A351" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="B351" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C351" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E351" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F351">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G351" t="s">
         <v>37</v>
@@ -11316,24 +11292,24 @@
         <v>37</v>
       </c>
       <c r="I351" t="s">
-        <v>449</v>
+        <v>645</v>
       </c>
     </row>
     <row r="352" spans="1:9">
       <c r="A352" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B352" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C352" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
       <c r="E352" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F352">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G352" t="s">
         <v>37</v>
@@ -11342,21 +11318,21 @@
         <v>37</v>
       </c>
       <c r="I352" t="s">
-        <v>372</v>
+        <v>638</v>
       </c>
     </row>
     <row r="353" spans="1:9">
       <c r="A353" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B353" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C353" t="s">
-        <v>349</v>
+        <v>227</v>
       </c>
       <c r="E353" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F353">
         <v>2.0</v>
@@ -11368,21 +11344,21 @@
         <v>37</v>
       </c>
       <c r="I353" t="s">
-        <v>643</v>
+        <v>444</v>
       </c>
     </row>
     <row r="354" spans="1:9">
       <c r="A354" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B354" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C354" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="E354" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F354">
         <v>1.0</v>
@@ -11394,21 +11370,21 @@
         <v>37</v>
       </c>
       <c r="I354" t="s">
-        <v>656</v>
+        <v>368</v>
       </c>
     </row>
     <row r="355" spans="1:9">
       <c r="A355" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B355" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C355" t="s">
-        <v>227</v>
+        <v>345</v>
       </c>
       <c r="E355" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F355">
         <v>3.0</v>
@@ -11420,24 +11396,24 @@
         <v>37</v>
       </c>
       <c r="I355" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
     </row>
     <row r="356" spans="1:9">
       <c r="A356" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B356" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C356" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="E356" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F356">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G356" t="s">
         <v>37</v>
@@ -11446,21 +11422,21 @@
         <v>37</v>
       </c>
       <c r="I356" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="357" spans="1:9">
       <c r="A357" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="B357" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C357" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="E357" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F357">
         <v>3.0</v>
@@ -11472,24 +11448,24 @@
         <v>37</v>
       </c>
       <c r="I357" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
     </row>
     <row r="358" spans="1:9">
       <c r="A358" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="B358" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C358" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="E358" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F358">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G358" t="s">
         <v>37</v>
@@ -11498,24 +11474,24 @@
         <v>37</v>
       </c>
       <c r="I358" t="s">
-        <v>449</v>
+        <v>635</v>
       </c>
     </row>
     <row r="359" spans="1:9">
       <c r="A359" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="B359" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C359" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E359" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F359">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G359" t="s">
         <v>37</v>
@@ -11524,24 +11500,24 @@
         <v>37</v>
       </c>
       <c r="I359" t="s">
-        <v>372</v>
+        <v>652</v>
       </c>
     </row>
     <row r="360" spans="1:9">
       <c r="A360" t="s">
-        <v>660</v>
+        <v>595</v>
       </c>
       <c r="B360" t="s">
-        <v>661</v>
+        <v>596</v>
       </c>
       <c r="C360" t="s">
-        <v>349</v>
+        <v>168</v>
       </c>
       <c r="E360" t="s">
-        <v>539</v>
+        <v>137</v>
       </c>
       <c r="F360">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G360" t="s">
         <v>37</v>
@@ -11550,24 +11526,24 @@
         <v>37</v>
       </c>
       <c r="I360" t="s">
-        <v>646</v>
+        <v>170</v>
       </c>
     </row>
     <row r="361" spans="1:9">
       <c r="A361" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="B361" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="C361" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E361" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F361">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G361" t="s">
         <v>37</v>
@@ -11576,24 +11552,24 @@
         <v>37</v>
       </c>
       <c r="I361" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
     </row>
     <row r="362" spans="1:9">
       <c r="A362" t="s">
-        <v>660</v>
+        <v>533</v>
       </c>
       <c r="B362" t="s">
-        <v>661</v>
+        <v>534</v>
       </c>
       <c r="C362" t="s">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="E362" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F362">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G362" t="s">
         <v>37</v>
@@ -11602,163 +11578,7 @@
         <v>37</v>
       </c>
       <c r="I362" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9">
-      <c r="A363" t="s">
-        <v>660</v>
-      </c>
-      <c r="B363" t="s">
-        <v>661</v>
-      </c>
-      <c r="C363" t="s">
-        <v>301</v>
-      </c>
-      <c r="E363" t="s">
-        <v>539</v>
-      </c>
-      <c r="F363">
-        <v>3.0</v>
-      </c>
-      <c r="G363" t="s">
-        <v>37</v>
-      </c>
-      <c r="H363" t="s">
-        <v>37</v>
-      </c>
-      <c r="I363" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9">
-      <c r="A364" t="s">
-        <v>660</v>
-      </c>
-      <c r="B364" t="s">
-        <v>661</v>
-      </c>
-      <c r="C364" t="s">
-        <v>316</v>
-      </c>
-      <c r="E364" t="s">
-        <v>539</v>
-      </c>
-      <c r="F364">
-        <v>2.0</v>
-      </c>
-      <c r="G364" t="s">
-        <v>37</v>
-      </c>
-      <c r="H364" t="s">
-        <v>37</v>
-      </c>
-      <c r="I364" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9">
-      <c r="A365" t="s">
-        <v>603</v>
-      </c>
-      <c r="B365" t="s">
-        <v>604</v>
-      </c>
-      <c r="C365" t="s">
-        <v>168</v>
-      </c>
-      <c r="E365" t="s">
-        <v>137</v>
-      </c>
-      <c r="F365">
-        <v>1.0</v>
-      </c>
-      <c r="G365" t="s">
-        <v>37</v>
-      </c>
-      <c r="H365" t="s">
-        <v>37</v>
-      </c>
-      <c r="I365" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="366" spans="1:9">
-      <c r="A366" t="s">
-        <v>663</v>
-      </c>
-      <c r="B366" t="s">
-        <v>664</v>
-      </c>
-      <c r="C366" t="s">
-        <v>301</v>
-      </c>
-      <c r="E366" t="s">
-        <v>539</v>
-      </c>
-      <c r="F366">
-        <v>1.0</v>
-      </c>
-      <c r="G366" t="s">
-        <v>37</v>
-      </c>
-      <c r="H366" t="s">
-        <v>37</v>
-      </c>
-      <c r="I366" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="367" spans="1:9">
-      <c r="A367" t="s">
-        <v>663</v>
-      </c>
-      <c r="B367" t="s">
-        <v>664</v>
-      </c>
-      <c r="C367" t="s">
-        <v>272</v>
-      </c>
-      <c r="E367" t="s">
-        <v>539</v>
-      </c>
-      <c r="F367">
-        <v>3.0</v>
-      </c>
-      <c r="G367" t="s">
-        <v>37</v>
-      </c>
-      <c r="H367" t="s">
-        <v>37</v>
-      </c>
-      <c r="I367" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="368" spans="1:9">
-      <c r="A368" t="s">
-        <v>537</v>
-      </c>
-      <c r="B368" t="s">
-        <v>538</v>
-      </c>
-      <c r="C368" t="s">
-        <v>316</v>
-      </c>
-      <c r="E368" t="s">
-        <v>539</v>
-      </c>
-      <c r="F368">
-        <v>2.0</v>
-      </c>
-      <c r="G368" t="s">
-        <v>37</v>
-      </c>
-      <c r="H368" t="s">
-        <v>37</v>
-      </c>
-      <c r="I368" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/src/inventory/Syl.xlsx
+++ b/src/inventory/Syl.xlsx
@@ -113,7 +113,10 @@
     <t>৳512.50</t>
   </si>
   <si>
-    <t>৳11,160.00</t>
+    <t>৳1,537.50</t>
+  </si>
+  <si>
+    <t>৳8,370.00</t>
   </si>
   <si>
     <t>৳874.05</t>
@@ -122,9 +125,6 @@
     <t>৳2,622.14</t>
   </si>
   <si>
-    <t>৳8,370.00</t>
-  </si>
-  <si>
     <t>৳683.33</t>
   </si>
   <si>
@@ -1334,6 +1334,15 @@
     <t>Mid Blue Denim Shirt</t>
   </si>
   <si>
+    <t>102-0302-006</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 006</t>
+  </si>
+  <si>
+    <t>৳2,600.00</t>
+  </si>
+  <si>
     <t>109-0401-223</t>
   </si>
   <si>
@@ -1388,15 +1397,6 @@
     <t>Black Perforated Leather Trifold Wallet</t>
   </si>
   <si>
-    <t>102-0302-006</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 006</t>
-  </si>
-  <si>
-    <t>৳2,600.00</t>
-  </si>
-  <si>
     <t>102-0301-002</t>
   </si>
   <si>
@@ -1502,6 +1502,9 @@
     <t>Black Polo Shirt in Cotton Pique</t>
   </si>
   <si>
+    <t>৳3,975.00</t>
+  </si>
+  <si>
     <t>105-0101-373</t>
   </si>
   <si>
@@ -1517,9 +1520,6 @@
     <t>৳4,480.00</t>
   </si>
   <si>
-    <t>৳3,975.00</t>
-  </si>
-  <si>
     <t>৳6,625.00</t>
   </si>
   <si>
@@ -1613,6 +1613,15 @@
     <t>৳275.00</t>
   </si>
   <si>
+    <t>105-0101-372</t>
+  </si>
+  <si>
+    <t>Deep Harbor T-shirt</t>
+  </si>
+  <si>
+    <t>৳2,560.00</t>
+  </si>
+  <si>
     <t>৳1,325.00</t>
   </si>
   <si>
@@ -1622,9 +1631,6 @@
     <t>৳166.67</t>
   </si>
   <si>
-    <t>৳2,560.00</t>
-  </si>
-  <si>
     <t>৳202.55</t>
   </si>
   <si>
@@ -1634,6 +1640,15 @@
     <t>৳1,920.00</t>
   </si>
   <si>
+    <t>105-0101-376</t>
+  </si>
+  <si>
+    <t>City Slate T-shirt</t>
+  </si>
+  <si>
+    <t>৳70.00</t>
+  </si>
+  <si>
     <t>105-0101-380</t>
   </si>
   <si>
@@ -1664,12 +1679,6 @@
     <t>৳4,760.00</t>
   </si>
   <si>
-    <t>105-0101-372</t>
-  </si>
-  <si>
-    <t>Deep Harbor T-shirt</t>
-  </si>
-  <si>
     <t>105-0101-371</t>
   </si>
   <si>
@@ -1706,9 +1715,6 @@
     <t>Earth Hemp T-shirt</t>
   </si>
   <si>
-    <t>৳70.00</t>
-  </si>
-  <si>
     <t>৳140.00</t>
   </si>
   <si>
@@ -1757,15 +1763,15 @@
     <t>৳5,096.00</t>
   </si>
   <si>
-    <t>105-0101-376</t>
-  </si>
-  <si>
-    <t>City Slate T-shirt</t>
-  </si>
-  <si>
     <t>৳1,590.00</t>
   </si>
   <si>
+    <t>105-0101-379</t>
+  </si>
+  <si>
+    <t>Essential White T-shirt</t>
+  </si>
+  <si>
     <t>৳125.00</t>
   </si>
   <si>
@@ -1793,9 +1799,27 @@
     <t>Half Sleeve shirt 009</t>
   </si>
   <si>
+    <t>৳95.45</t>
+  </si>
+  <si>
+    <t>৳286.36</t>
+  </si>
+  <si>
     <t>৳210.00</t>
   </si>
   <si>
+    <t>৳1,625.00</t>
+  </si>
+  <si>
+    <t>৳7,670.00</t>
+  </si>
+  <si>
+    <t>৳116.67</t>
+  </si>
+  <si>
+    <t>৳1,633.33</t>
+  </si>
+  <si>
     <t>৳145.83</t>
   </si>
   <si>
@@ -1805,34 +1829,10 @@
     <t>Half Sleeve shirt 001</t>
   </si>
   <si>
-    <t>105-0101-379</t>
-  </si>
-  <si>
-    <t>Essential White T-shirt</t>
-  </si>
-  <si>
-    <t>৳1,625.00</t>
-  </si>
-  <si>
-    <t>৳7,670.00</t>
-  </si>
-  <si>
-    <t>৳116.67</t>
-  </si>
-  <si>
-    <t>৳1,633.33</t>
-  </si>
-  <si>
     <t>108-0101-014</t>
   </si>
   <si>
     <t>Teal Sweatshirt in French-Terry</t>
-  </si>
-  <si>
-    <t>৳95.45</t>
-  </si>
-  <si>
-    <t>৳286.36</t>
   </si>
   <si>
     <t>107-0100-038</t>
@@ -2639,16 +2639,16 @@
         <v>11</v>
       </c>
       <c r="F10">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G10" t="s">
         <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2668,13 +2668,13 @@
         <v>3.0</v>
       </c>
       <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
         <v>33</v>
-      </c>
-      <c r="H11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3220,7 +3220,7 @@
         <v>65</v>
       </c>
       <c r="I32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -6697,22 +6697,25 @@
         <v>439</v>
       </c>
       <c r="B170" t="s">
-        <v>439</v>
+        <v>440</v>
+      </c>
+      <c r="C170" t="s">
+        <v>266</v>
       </c>
       <c r="E170" t="s">
-        <v>440</v>
+        <v>387</v>
       </c>
       <c r="F170">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G170" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="H170" t="s">
-        <v>37</v>
+        <v>441</v>
       </c>
       <c r="I170" t="s">
-        <v>441</v>
+        <v>399</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -6720,16 +6723,13 @@
         <v>442</v>
       </c>
       <c r="B171" t="s">
+        <v>442</v>
+      </c>
+      <c r="E171" t="s">
         <v>443</v>
       </c>
-      <c r="C171" t="s">
-        <v>171</v>
-      </c>
-      <c r="E171" t="s">
-        <v>240</v>
-      </c>
       <c r="F171">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G171" t="s">
         <v>37</v>
@@ -6738,41 +6738,41 @@
         <v>37</v>
       </c>
       <c r="I171" t="s">
-        <v>243</v>
+        <v>444</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="B172" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="C172" t="s">
-        <v>266</v>
+        <v>171</v>
       </c>
       <c r="E172" t="s">
-        <v>410</v>
+        <v>240</v>
       </c>
       <c r="F172">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G172" t="s">
-        <v>226</v>
+        <v>37</v>
       </c>
       <c r="H172" t="s">
-        <v>444</v>
+        <v>37</v>
       </c>
       <c r="I172" t="s">
-        <v>445</v>
+        <v>243</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="B173" t="s">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="C173" t="s">
         <v>266</v>
@@ -6787,7 +6787,7 @@
         <v>226</v>
       </c>
       <c r="H173" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I173" t="s">
         <v>448</v>
@@ -6795,77 +6795,77 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>395</v>
+        <v>449</v>
       </c>
       <c r="B174" t="s">
-        <v>396</v>
+        <v>450</v>
       </c>
       <c r="C174" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="E174" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="F174">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G174" t="s">
-        <v>397</v>
+        <v>226</v>
       </c>
       <c r="H174" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I174" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
       <c r="B175" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="C175" t="s">
-        <v>312</v>
+        <v>224</v>
       </c>
       <c r="E175" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="F175">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G175" t="s">
-        <v>226</v>
+        <v>397</v>
       </c>
       <c r="H175" t="s">
-        <v>226</v>
+        <v>452</v>
       </c>
       <c r="I175" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>244</v>
+        <v>449</v>
       </c>
       <c r="B176" t="s">
-        <v>245</v>
+        <v>450</v>
       </c>
       <c r="C176" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="E176" t="s">
-        <v>246</v>
+        <v>410</v>
       </c>
       <c r="F176">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G176" t="s">
-        <v>452</v>
+        <v>226</v>
       </c>
       <c r="H176" t="s">
-        <v>453</v>
+        <v>226</v>
       </c>
       <c r="I176" t="s">
         <v>454</v>
@@ -6873,51 +6873,51 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
+        <v>244</v>
+      </c>
+      <c r="B177" t="s">
+        <v>245</v>
+      </c>
+      <c r="C177" t="s">
+        <v>171</v>
+      </c>
+      <c r="E177" t="s">
+        <v>246</v>
+      </c>
+      <c r="F177">
+        <v>4.0</v>
+      </c>
+      <c r="G177" t="s">
         <v>455</v>
       </c>
-      <c r="B177" t="s">
+      <c r="H177" t="s">
         <v>456</v>
       </c>
-      <c r="E177" t="s">
-        <v>193</v>
-      </c>
-      <c r="F177">
-        <v>1.0</v>
-      </c>
-      <c r="G177" t="s">
-        <v>37</v>
-      </c>
-      <c r="H177" t="s">
-        <v>37</v>
-      </c>
       <c r="I177" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B178" t="s">
-        <v>458</v>
-      </c>
-      <c r="C178" t="s">
-        <v>266</v>
+        <v>459</v>
       </c>
       <c r="E178" t="s">
-        <v>387</v>
+        <v>193</v>
       </c>
       <c r="F178">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G178" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="H178" t="s">
-        <v>459</v>
+        <v>37</v>
       </c>
       <c r="I178" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -7073,7 +7073,7 @@
         <v>226</v>
       </c>
       <c r="I184" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -7145,10 +7145,10 @@
         <v>397</v>
       </c>
       <c r="H187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -7280,236 +7280,236 @@
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="B193" t="s">
-        <v>396</v>
+        <v>440</v>
       </c>
       <c r="C193" t="s">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="E193" t="s">
         <v>387</v>
       </c>
       <c r="F193">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G193" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="H193" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="I193" t="s">
-        <v>450</v>
+        <v>495</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>495</v>
+        <v>395</v>
       </c>
       <c r="B194" t="s">
-        <v>496</v>
+        <v>396</v>
       </c>
       <c r="C194" t="s">
-        <v>179</v>
+        <v>296</v>
       </c>
       <c r="E194" t="s">
-        <v>488</v>
+        <v>387</v>
       </c>
       <c r="F194">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G194" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
       <c r="H194" t="s">
-        <v>37</v>
+        <v>452</v>
       </c>
       <c r="I194" t="s">
-        <v>497</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="B195" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>179</v>
       </c>
       <c r="E195" t="s">
-        <v>410</v>
+        <v>488</v>
       </c>
       <c r="F195">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G195" t="s">
-        <v>226</v>
+        <v>37</v>
       </c>
       <c r="H195" t="s">
-        <v>350</v>
+        <v>37</v>
       </c>
       <c r="I195" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B196" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C196" t="s">
         <v>266</v>
       </c>
       <c r="E196" t="s">
-        <v>469</v>
+        <v>410</v>
       </c>
       <c r="F196">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G196" t="s">
-        <v>498</v>
+        <v>226</v>
       </c>
       <c r="H196" t="s">
-        <v>444</v>
+        <v>350</v>
       </c>
       <c r="I196" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="B197" t="s">
+        <v>468</v>
+      </c>
+      <c r="C197" t="s">
+        <v>266</v>
+      </c>
+      <c r="E197" t="s">
+        <v>469</v>
+      </c>
+      <c r="F197">
+        <v>7.0</v>
+      </c>
+      <c r="G197" t="s">
+        <v>499</v>
+      </c>
+      <c r="H197" t="s">
         <v>447</v>
       </c>
-      <c r="C197" t="s">
-        <v>224</v>
-      </c>
-      <c r="E197" t="s">
-        <v>410</v>
-      </c>
-      <c r="F197">
-        <v>2.0</v>
-      </c>
-      <c r="G197" t="s">
-        <v>226</v>
-      </c>
-      <c r="H197" t="s">
-        <v>256</v>
-      </c>
       <c r="I197" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>408</v>
+        <v>439</v>
       </c>
       <c r="B198" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="C198" t="s">
-        <v>224</v>
+        <v>346</v>
       </c>
       <c r="E198" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="F198">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G198" t="s">
-        <v>226</v>
+        <v>388</v>
       </c>
       <c r="H198" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="I198" t="s">
-        <v>445</v>
+        <v>495</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="B199" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="C199" t="s">
-        <v>312</v>
+        <v>224</v>
       </c>
       <c r="E199" t="s">
-        <v>469</v>
+        <v>410</v>
       </c>
       <c r="F199">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G199" t="s">
-        <v>498</v>
+        <v>226</v>
       </c>
       <c r="H199" t="s">
-        <v>498</v>
+        <v>256</v>
       </c>
       <c r="I199" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>457</v>
+        <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="C200" t="s">
-        <v>346</v>
+        <v>224</v>
       </c>
       <c r="E200" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="F200">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G200" t="s">
-        <v>388</v>
+        <v>226</v>
       </c>
       <c r="H200" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="I200" t="s">
-        <v>500</v>
+        <v>448</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B201" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="C201" t="s">
-        <v>224</v>
+        <v>312</v>
       </c>
       <c r="E201" t="s">
-        <v>387</v>
+        <v>469</v>
       </c>
       <c r="F201">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G201" t="s">
-        <v>388</v>
+        <v>499</v>
       </c>
       <c r="H201" t="s">
-        <v>422</v>
+        <v>499</v>
       </c>
       <c r="I201" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -7607,7 +7607,7 @@
         <v>397</v>
       </c>
       <c r="H205" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I205" t="s">
         <v>506</v>
@@ -7630,7 +7630,7 @@
         <v>2.0</v>
       </c>
       <c r="G206" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H206" t="s">
         <v>397</v>
@@ -7693,10 +7693,10 @@
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B209" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C209" t="s">
         <v>138</v>
@@ -7760,7 +7760,7 @@
         <v>2.0</v>
       </c>
       <c r="G211" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H211" t="s">
         <v>397</v>
@@ -7812,10 +7812,10 @@
         <v>1.0</v>
       </c>
       <c r="G213" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H213" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I213" t="s">
         <v>516</v>
@@ -7875,13 +7875,13 @@
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>522</v>
+        <v>439</v>
       </c>
       <c r="B216" t="s">
-        <v>523</v>
+        <v>440</v>
       </c>
       <c r="C216" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="E216" t="s">
         <v>387</v>
@@ -7890,21 +7890,21 @@
         <v>2.0</v>
       </c>
       <c r="G216" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="H216" t="s">
-        <v>449</v>
+        <v>484</v>
       </c>
       <c r="I216" t="s">
-        <v>506</v>
+        <v>453</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B217" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C217" t="s">
         <v>266</v>
@@ -7919,53 +7919,53 @@
         <v>397</v>
       </c>
       <c r="H217" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I217" t="s">
-        <v>450</v>
+        <v>506</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B218" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C218" t="s">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="E218" t="s">
-        <v>488</v>
+        <v>387</v>
       </c>
       <c r="F218">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G218" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
       <c r="H218" t="s">
-        <v>37</v>
+        <v>452</v>
       </c>
       <c r="I218" t="s">
-        <v>516</v>
+        <v>453</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>330</v>
+        <v>526</v>
       </c>
       <c r="B219" t="s">
-        <v>331</v>
+        <v>527</v>
       </c>
       <c r="C219" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E219" t="s">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="F219">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G219" t="s">
         <v>37</v>
@@ -7974,70 +7974,70 @@
         <v>37</v>
       </c>
       <c r="I219" t="s">
-        <v>253</v>
+        <v>516</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>446</v>
+        <v>330</v>
       </c>
       <c r="B220" t="s">
-        <v>447</v>
+        <v>331</v>
       </c>
       <c r="C220" t="s">
-        <v>296</v>
+        <v>171</v>
       </c>
       <c r="E220" t="s">
-        <v>410</v>
+        <v>240</v>
       </c>
       <c r="F220">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G220" t="s">
-        <v>226</v>
+        <v>37</v>
       </c>
       <c r="H220" t="s">
-        <v>256</v>
+        <v>37</v>
       </c>
       <c r="I220" t="s">
-        <v>478</v>
+        <v>253</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>520</v>
+        <v>449</v>
       </c>
       <c r="B221" t="s">
-        <v>521</v>
+        <v>450</v>
       </c>
       <c r="C221" t="s">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="E221" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="F221">
         <v>2.0</v>
       </c>
       <c r="G221" t="s">
-        <v>397</v>
+        <v>226</v>
       </c>
       <c r="H221" t="s">
-        <v>449</v>
+        <v>256</v>
       </c>
       <c r="I221" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>457</v>
+        <v>520</v>
       </c>
       <c r="B222" t="s">
-        <v>458</v>
+        <v>521</v>
       </c>
       <c r="C222" t="s">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="E222" t="s">
         <v>387</v>
@@ -8046,13 +8046,13 @@
         <v>2.0</v>
       </c>
       <c r="G222" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="H222" t="s">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="I222" t="s">
-        <v>450</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -8101,7 +8101,7 @@
         <v>397</v>
       </c>
       <c r="H224" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I224" t="s">
         <v>506</v>
@@ -8127,7 +8127,7 @@
         <v>397</v>
       </c>
       <c r="H225" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I225" t="s">
         <v>506</v>
@@ -8179,223 +8179,223 @@
         <v>226</v>
       </c>
       <c r="I227" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="B228" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="C228" t="s">
-        <v>346</v>
+        <v>216</v>
       </c>
       <c r="E228" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="F228">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G228" t="s">
-        <v>498</v>
+        <v>37</v>
       </c>
       <c r="H228" t="s">
-        <v>498</v>
+        <v>37</v>
       </c>
       <c r="I228" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="B229" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="C229" t="s">
-        <v>216</v>
+        <v>346</v>
       </c>
       <c r="E229" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="F229">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G229" t="s">
-        <v>37</v>
+        <v>499</v>
       </c>
       <c r="H229" t="s">
-        <v>37</v>
+        <v>499</v>
       </c>
       <c r="I229" t="s">
-        <v>445</v>
+        <v>498</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>395</v>
+        <v>526</v>
       </c>
       <c r="B230" t="s">
-        <v>396</v>
+        <v>527</v>
       </c>
       <c r="C230" t="s">
-        <v>312</v>
+        <v>216</v>
       </c>
       <c r="E230" t="s">
-        <v>387</v>
+        <v>488</v>
       </c>
       <c r="F230">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G230" t="s">
-        <v>397</v>
+        <v>37</v>
       </c>
       <c r="H230" t="s">
-        <v>397</v>
+        <v>37</v>
       </c>
       <c r="I230" t="s">
-        <v>532</v>
+        <v>448</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="B231" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="C231" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="E231" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="F231">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G231" t="s">
-        <v>226</v>
+        <v>397</v>
       </c>
       <c r="H231" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I231" t="s">
-        <v>411</v>
+        <v>535</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>467</v>
+        <v>408</v>
       </c>
       <c r="B232" t="s">
-        <v>468</v>
+        <v>409</v>
       </c>
       <c r="C232" t="s">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="E232" t="s">
-        <v>469</v>
+        <v>410</v>
       </c>
       <c r="F232">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G232" t="s">
-        <v>533</v>
+        <v>226</v>
       </c>
       <c r="H232" t="s">
-        <v>534</v>
+        <v>400</v>
       </c>
       <c r="I232" t="s">
-        <v>535</v>
+        <v>411</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>524</v>
+        <v>467</v>
       </c>
       <c r="B233" t="s">
-        <v>525</v>
+        <v>468</v>
       </c>
       <c r="C233" t="s">
-        <v>346</v>
+        <v>224</v>
       </c>
       <c r="E233" t="s">
-        <v>387</v>
+        <v>469</v>
       </c>
       <c r="F233">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G233" t="s">
-        <v>397</v>
+        <v>536</v>
       </c>
       <c r="H233" t="s">
-        <v>397</v>
+        <v>537</v>
       </c>
       <c r="I233" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B234" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="C234" t="s">
-        <v>266</v>
+        <v>346</v>
       </c>
       <c r="E234" t="s">
-        <v>469</v>
+        <v>387</v>
       </c>
       <c r="F234">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G234" t="s">
-        <v>536</v>
+        <v>397</v>
       </c>
       <c r="H234" t="s">
-        <v>537</v>
+        <v>397</v>
       </c>
       <c r="I234" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>460</v>
+        <v>512</v>
       </c>
       <c r="B235" t="s">
-        <v>461</v>
+        <v>513</v>
       </c>
       <c r="C235" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="E235" t="s">
-        <v>387</v>
+        <v>469</v>
       </c>
       <c r="F235">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G235" t="s">
-        <v>388</v>
+        <v>538</v>
       </c>
       <c r="H235" t="s">
-        <v>459</v>
+        <v>539</v>
       </c>
       <c r="I235" t="s">
-        <v>399</v>
+        <v>540</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B236" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C236" t="s">
         <v>296</v>
@@ -8404,111 +8404,111 @@
         <v>387</v>
       </c>
       <c r="F236">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G236" t="s">
         <v>388</v>
       </c>
       <c r="H236" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="I236" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>539</v>
+        <v>464</v>
       </c>
       <c r="B237" t="s">
-        <v>540</v>
+        <v>465</v>
       </c>
       <c r="C237" t="s">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="E237" t="s">
-        <v>488</v>
+        <v>387</v>
       </c>
       <c r="F237">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G237" t="s">
-        <v>541</v>
+        <v>388</v>
       </c>
       <c r="H237" t="s">
-        <v>542</v>
+        <v>422</v>
       </c>
       <c r="I237" t="s">
-        <v>535</v>
+        <v>423</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
+        <v>541</v>
+      </c>
+      <c r="B238" t="s">
+        <v>542</v>
+      </c>
+      <c r="C238" t="s">
+        <v>216</v>
+      </c>
+      <c r="E238" t="s">
+        <v>488</v>
+      </c>
+      <c r="F238">
+        <v>5.0</v>
+      </c>
+      <c r="G238" t="s">
         <v>543</v>
       </c>
-      <c r="B238" t="s">
-        <v>544</v>
-      </c>
-      <c r="C238" t="s">
-        <v>179</v>
-      </c>
-      <c r="E238" t="s">
-        <v>240</v>
-      </c>
-      <c r="F238">
-        <v>2.0</v>
-      </c>
-      <c r="G238" t="s">
-        <v>37</v>
-      </c>
       <c r="H238" t="s">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="I238" t="s">
-        <v>243</v>
+        <v>472</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
+        <v>544</v>
+      </c>
+      <c r="B239" t="s">
         <v>545</v>
       </c>
-      <c r="B239" t="s">
-        <v>546</v>
-      </c>
       <c r="C239" t="s">
-        <v>296</v>
+        <v>216</v>
       </c>
       <c r="E239" t="s">
-        <v>547</v>
+        <v>488</v>
       </c>
       <c r="F239">
         <v>4.0</v>
       </c>
       <c r="G239" t="s">
-        <v>37</v>
+        <v>546</v>
       </c>
       <c r="H239" t="s">
-        <v>37</v>
+        <v>547</v>
       </c>
       <c r="I239" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
+        <v>548</v>
+      </c>
+      <c r="B240" t="s">
         <v>549</v>
       </c>
-      <c r="B240" t="s">
-        <v>550</v>
-      </c>
       <c r="C240" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="E240" t="s">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="F240">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G240" t="s">
         <v>37</v>
@@ -8517,24 +8517,24 @@
         <v>37</v>
       </c>
       <c r="I240" t="s">
-        <v>535</v>
+        <v>243</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
+        <v>550</v>
+      </c>
+      <c r="B241" t="s">
         <v>551</v>
       </c>
-      <c r="B241" t="s">
+      <c r="C241" t="s">
+        <v>296</v>
+      </c>
+      <c r="E241" t="s">
         <v>552</v>
       </c>
-      <c r="C241" t="s">
-        <v>171</v>
-      </c>
-      <c r="E241" t="s">
-        <v>488</v>
-      </c>
       <c r="F241">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G241" t="s">
         <v>37</v>
@@ -8543,33 +8543,33 @@
         <v>37</v>
       </c>
       <c r="I241" t="s">
-        <v>411</v>
+        <v>553</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B242" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C242" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="E242" t="s">
         <v>488</v>
       </c>
       <c r="F242">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G242" t="s">
-        <v>517</v>
+        <v>37</v>
       </c>
       <c r="H242" t="s">
-        <v>350</v>
+        <v>37</v>
       </c>
       <c r="I242" t="s">
-        <v>555</v>
+        <v>411</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -8580,59 +8580,59 @@
         <v>557</v>
       </c>
       <c r="C243" t="s">
-        <v>296</v>
+        <v>216</v>
       </c>
       <c r="E243" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="F243">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G243" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="H243" t="s">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="I243" t="s">
-        <v>519</v>
+        <v>558</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>460</v>
+        <v>559</v>
       </c>
       <c r="B244" t="s">
-        <v>461</v>
+        <v>560</v>
       </c>
       <c r="C244" t="s">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="E244" t="s">
-        <v>387</v>
+        <v>469</v>
       </c>
       <c r="F244">
         <v>3.0</v>
       </c>
       <c r="G244" t="s">
-        <v>388</v>
+        <v>499</v>
       </c>
       <c r="H244" t="s">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="I244" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>558</v>
+        <v>460</v>
       </c>
       <c r="B245" t="s">
-        <v>559</v>
+        <v>461</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>346</v>
       </c>
       <c r="E245" t="s">
         <v>387</v>
@@ -8647,527 +8647,527 @@
         <v>422</v>
       </c>
       <c r="I245" t="s">
-        <v>560</v>
+        <v>495</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>382</v>
+        <v>561</v>
       </c>
       <c r="B246" t="s">
-        <v>383</v>
+        <v>562</v>
       </c>
       <c r="C246" t="s">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="E246" t="s">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="F246">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G246" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="H246" t="s">
-        <v>37</v>
+        <v>422</v>
       </c>
       <c r="I246" t="s">
-        <v>384</v>
+        <v>563</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>556</v>
+        <v>382</v>
       </c>
       <c r="B247" t="s">
-        <v>557</v>
+        <v>383</v>
       </c>
       <c r="C247" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="E247" t="s">
-        <v>469</v>
+        <v>240</v>
       </c>
       <c r="F247">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G247" t="s">
-        <v>498</v>
+        <v>37</v>
       </c>
       <c r="H247" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="I247" t="s">
-        <v>519</v>
+        <v>384</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B248" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C248" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="E248" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="F248">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G248" t="s">
-        <v>563</v>
+        <v>499</v>
       </c>
       <c r="H248" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="I248" t="s">
-        <v>485</v>
+        <v>519</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B249" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="C249" t="s">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="E249" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="F249">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G249" t="s">
-        <v>498</v>
+        <v>543</v>
       </c>
       <c r="H249" t="s">
-        <v>53</v>
+        <v>202</v>
       </c>
       <c r="I249" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="B250" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C250" t="s">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="E250" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="F250">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G250" t="s">
-        <v>37</v>
+        <v>499</v>
       </c>
       <c r="H250" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I250" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="B251" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="C251" t="s">
-        <v>346</v>
+        <v>179</v>
       </c>
       <c r="E251" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="F251">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G251" t="s">
-        <v>564</v>
+        <v>37</v>
       </c>
       <c r="H251" t="s">
-        <v>202</v>
+        <v>37</v>
       </c>
       <c r="I251" t="s">
-        <v>283</v>
+        <v>540</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>565</v>
+        <v>514</v>
       </c>
       <c r="B252" t="s">
+        <v>515</v>
+      </c>
+      <c r="C252" t="s">
+        <v>346</v>
+      </c>
+      <c r="E252" t="s">
+        <v>469</v>
+      </c>
+      <c r="F252">
+        <v>2.0</v>
+      </c>
+      <c r="G252" t="s">
         <v>566</v>
       </c>
-      <c r="C252" t="s">
-        <v>179</v>
-      </c>
-      <c r="E252" t="s">
-        <v>240</v>
-      </c>
-      <c r="F252">
-        <v>1.0</v>
-      </c>
-      <c r="G252" t="s">
-        <v>37</v>
-      </c>
       <c r="H252" t="s">
-        <v>37</v>
+        <v>202</v>
       </c>
       <c r="I252" t="s">
-        <v>384</v>
+        <v>283</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>385</v>
+        <v>567</v>
       </c>
       <c r="B253" t="s">
-        <v>386</v>
+        <v>568</v>
       </c>
       <c r="C253" t="s">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="E253" t="s">
-        <v>387</v>
+        <v>240</v>
       </c>
       <c r="F253">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G253" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="H253" t="s">
-        <v>484</v>
+        <v>37</v>
       </c>
       <c r="I253" t="s">
-        <v>485</v>
+        <v>384</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>520</v>
+        <v>385</v>
       </c>
       <c r="B254" t="s">
-        <v>521</v>
+        <v>386</v>
       </c>
       <c r="C254" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="E254" t="s">
         <v>387</v>
       </c>
       <c r="F254">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G254" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="H254" t="s">
-        <v>397</v>
+        <v>484</v>
       </c>
       <c r="I254" t="s">
-        <v>283</v>
+        <v>485</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="B255" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="C255" t="s">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="E255" t="s">
-        <v>488</v>
+        <v>387</v>
       </c>
       <c r="F255">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G255" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
       <c r="H255" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
       <c r="I255" t="s">
-        <v>535</v>
+        <v>283</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="B256" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="C256" t="s">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="E256" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="F256">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G256" t="s">
-        <v>567</v>
+        <v>37</v>
       </c>
       <c r="H256" t="s">
-        <v>568</v>
+        <v>37</v>
       </c>
       <c r="I256" t="s">
-        <v>445</v>
+        <v>534</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="B257" t="s">
-        <v>552</v>
+        <v>515</v>
       </c>
       <c r="C257" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="E257" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="F257">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G257" t="s">
-        <v>37</v>
+        <v>569</v>
       </c>
       <c r="H257" t="s">
-        <v>37</v>
+        <v>570</v>
       </c>
       <c r="I257" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="B258" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="C258" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E258" t="s">
-        <v>387</v>
+        <v>488</v>
       </c>
       <c r="F258">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G258" t="s">
-        <v>397</v>
+        <v>37</v>
       </c>
       <c r="H258" t="s">
-        <v>397</v>
+        <v>37</v>
       </c>
       <c r="I258" t="s">
-        <v>532</v>
+        <v>485</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>553</v>
+        <v>524</v>
       </c>
       <c r="B259" t="s">
-        <v>554</v>
+        <v>525</v>
       </c>
       <c r="C259" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="E259" t="s">
-        <v>488</v>
+        <v>387</v>
       </c>
       <c r="F259">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G259" t="s">
-        <v>564</v>
+        <v>397</v>
       </c>
       <c r="H259" t="s">
-        <v>569</v>
+        <v>397</v>
       </c>
       <c r="I259" t="s">
-        <v>411</v>
+        <v>535</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="B260" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="C260" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="E260" t="s">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="F260">
         <v>3.0</v>
       </c>
       <c r="G260" t="s">
-        <v>37</v>
+        <v>566</v>
       </c>
       <c r="H260" t="s">
-        <v>37</v>
+        <v>571</v>
       </c>
       <c r="I260" t="s">
-        <v>251</v>
+        <v>411</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="B261" t="s">
-        <v>540</v>
+        <v>573</v>
       </c>
       <c r="C261" t="s">
         <v>138</v>
       </c>
       <c r="E261" t="s">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="F261">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G261" t="s">
-        <v>572</v>
+        <v>37</v>
       </c>
       <c r="H261" t="s">
-        <v>573</v>
+        <v>37</v>
       </c>
       <c r="I261" t="s">
-        <v>574</v>
+        <v>251</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
+        <v>544</v>
+      </c>
+      <c r="B262" t="s">
+        <v>545</v>
+      </c>
+      <c r="C262" t="s">
+        <v>138</v>
+      </c>
+      <c r="E262" t="s">
+        <v>488</v>
+      </c>
+      <c r="F262">
+        <v>6.0</v>
+      </c>
+      <c r="G262" t="s">
+        <v>574</v>
+      </c>
+      <c r="H262" t="s">
         <v>575</v>
       </c>
-      <c r="B262" t="s">
+      <c r="I262" t="s">
         <v>576</v>
-      </c>
-      <c r="C262" t="s">
-        <v>266</v>
-      </c>
-      <c r="E262" t="s">
-        <v>387</v>
-      </c>
-      <c r="F262">
-        <v>2.0</v>
-      </c>
-      <c r="G262" t="s">
-        <v>388</v>
-      </c>
-      <c r="H262" t="s">
-        <v>484</v>
-      </c>
-      <c r="I262" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="B263" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="C263" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="E263" t="s">
-        <v>488</v>
+        <v>387</v>
       </c>
       <c r="F263">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G263" t="s">
-        <v>236</v>
+        <v>388</v>
       </c>
       <c r="H263" t="s">
-        <v>578</v>
+        <v>484</v>
       </c>
       <c r="I263" t="s">
-        <v>466</v>
+        <v>579</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="B264" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="C264" t="s">
         <v>138</v>
       </c>
       <c r="E264" t="s">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="F264">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="G264" t="s">
-        <v>37</v>
+        <v>236</v>
       </c>
       <c r="H264" t="s">
-        <v>37</v>
+        <v>580</v>
       </c>
       <c r="I264" t="s">
-        <v>579</v>
+        <v>466</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="B265" t="s">
+        <v>549</v>
+      </c>
+      <c r="C265" t="s">
+        <v>138</v>
+      </c>
+      <c r="E265" t="s">
+        <v>240</v>
+      </c>
+      <c r="F265">
+        <v>7.0</v>
+      </c>
+      <c r="G265" t="s">
+        <v>37</v>
+      </c>
+      <c r="H265" t="s">
+        <v>37</v>
+      </c>
+      <c r="I265" t="s">
         <v>581</v>
-      </c>
-      <c r="C265" t="s">
-        <v>216</v>
-      </c>
-      <c r="E265" t="s">
-        <v>488</v>
-      </c>
-      <c r="F265">
-        <v>5.0</v>
-      </c>
-      <c r="G265" t="s">
-        <v>563</v>
-      </c>
-      <c r="H265" t="s">
-        <v>226</v>
-      </c>
-      <c r="I265" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -9219,15 +9219,15 @@
         <v>397</v>
       </c>
       <c r="I267" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B268" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C268" t="s">
         <v>224</v>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B269" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C269" t="s">
         <v>224</v>
@@ -9271,7 +9271,7 @@
         <v>484</v>
       </c>
       <c r="I269" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -9291,76 +9291,76 @@
         <v>1.0</v>
       </c>
       <c r="G270" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="H270" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="I270" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>526</v>
+        <v>583</v>
       </c>
       <c r="B271" t="s">
-        <v>527</v>
+        <v>584</v>
       </c>
       <c r="C271" t="s">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="E271" t="s">
         <v>488</v>
       </c>
       <c r="F271">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="G271" t="s">
-        <v>583</v>
+        <v>37</v>
       </c>
       <c r="H271" t="s">
-        <v>584</v>
+        <v>37</v>
       </c>
       <c r="I271" t="s">
-        <v>585</v>
+        <v>534</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>464</v>
+        <v>526</v>
       </c>
       <c r="B272" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="C272" t="s">
-        <v>312</v>
+        <v>138</v>
       </c>
       <c r="E272" t="s">
-        <v>387</v>
+        <v>488</v>
       </c>
       <c r="F272">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="G272" t="s">
-        <v>388</v>
+        <v>585</v>
       </c>
       <c r="H272" t="s">
-        <v>484</v>
+        <v>586</v>
       </c>
       <c r="I272" t="s">
-        <v>485</v>
+        <v>587</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>586</v>
+        <v>464</v>
       </c>
       <c r="B273" t="s">
-        <v>587</v>
+        <v>465</v>
       </c>
       <c r="C273" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="E273" t="s">
         <v>387</v>
@@ -9401,18 +9401,18 @@
         <v>484</v>
       </c>
       <c r="I274" t="s">
-        <v>450</v>
+        <v>485</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B275" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C275" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="E275" t="s">
         <v>387</v>
@@ -9427,7 +9427,7 @@
         <v>484</v>
       </c>
       <c r="I275" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -9438,7 +9438,7 @@
         <v>591</v>
       </c>
       <c r="C276" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="E276" t="s">
         <v>387</v>
@@ -9453,180 +9453,180 @@
         <v>484</v>
       </c>
       <c r="I276" t="s">
-        <v>577</v>
+        <v>453</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="B277" t="s">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="C277" t="s">
-        <v>171</v>
+        <v>266</v>
       </c>
       <c r="E277" t="s">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="F277">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G277" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="H277" t="s">
-        <v>37</v>
+        <v>484</v>
       </c>
       <c r="I277" t="s">
-        <v>384</v>
+        <v>579</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>551</v>
+        <v>526</v>
       </c>
       <c r="B278" t="s">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="C278" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="E278" t="s">
         <v>488</v>
       </c>
       <c r="F278">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G278" t="s">
-        <v>37</v>
+        <v>594</v>
       </c>
       <c r="H278" t="s">
-        <v>37</v>
+        <v>595</v>
       </c>
       <c r="I278" t="s">
-        <v>485</v>
+        <v>411</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>490</v>
+        <v>567</v>
       </c>
       <c r="B279" t="s">
-        <v>491</v>
+        <v>568</v>
       </c>
       <c r="C279" t="s">
-        <v>312</v>
+        <v>171</v>
       </c>
       <c r="E279" t="s">
-        <v>387</v>
+        <v>240</v>
       </c>
       <c r="F279">
         <v>1.0</v>
       </c>
       <c r="G279" t="s">
-        <v>397</v>
+        <v>37</v>
       </c>
       <c r="H279" t="s">
-        <v>397</v>
+        <v>37</v>
       </c>
       <c r="I279" t="s">
-        <v>492</v>
+        <v>384</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B280" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C280" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E280" t="s">
         <v>488</v>
       </c>
       <c r="F280">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G280" t="s">
-        <v>563</v>
+        <v>37</v>
       </c>
       <c r="H280" t="s">
-        <v>592</v>
+        <v>37</v>
       </c>
       <c r="I280" t="s">
-        <v>411</v>
+        <v>485</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>330</v>
+        <v>490</v>
       </c>
       <c r="B281" t="s">
-        <v>331</v>
+        <v>491</v>
       </c>
       <c r="C281" t="s">
-        <v>138</v>
+        <v>312</v>
       </c>
       <c r="E281" t="s">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="F281">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G281" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
       <c r="H281" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
       <c r="I281" t="s">
-        <v>365</v>
+        <v>492</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
+        <v>564</v>
+      </c>
+      <c r="B282" t="s">
+        <v>565</v>
+      </c>
+      <c r="C282" t="s">
+        <v>171</v>
+      </c>
+      <c r="E282" t="s">
+        <v>488</v>
+      </c>
+      <c r="F282">
+        <v>3.0</v>
+      </c>
+      <c r="G282" t="s">
         <v>543</v>
       </c>
-      <c r="B282" t="s">
-        <v>544</v>
-      </c>
-      <c r="C282" t="s">
-        <v>148</v>
-      </c>
-      <c r="E282" t="s">
-        <v>240</v>
-      </c>
-      <c r="F282">
-        <v>4.0</v>
-      </c>
-      <c r="G282" t="s">
-        <v>37</v>
-      </c>
       <c r="H282" t="s">
-        <v>37</v>
+        <v>596</v>
       </c>
       <c r="I282" t="s">
-        <v>253</v>
+        <v>411</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>553</v>
+        <v>330</v>
       </c>
       <c r="B283" t="s">
-        <v>554</v>
+        <v>331</v>
       </c>
       <c r="C283" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="E283" t="s">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="F283">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G283" t="s">
         <v>37</v>
@@ -9635,258 +9635,258 @@
         <v>37</v>
       </c>
       <c r="I283" t="s">
-        <v>445</v>
+        <v>365</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="B284" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="C284" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E284" t="s">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="F284">
         <v>4.0</v>
       </c>
       <c r="G284" t="s">
-        <v>593</v>
+        <v>37</v>
       </c>
       <c r="H284" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="I284" t="s">
-        <v>535</v>
+        <v>253</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>594</v>
+        <v>556</v>
       </c>
       <c r="B285" t="s">
-        <v>595</v>
+        <v>557</v>
       </c>
       <c r="C285" t="s">
-        <v>266</v>
+        <v>148</v>
       </c>
       <c r="E285" t="s">
-        <v>387</v>
+        <v>488</v>
       </c>
       <c r="F285">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="G285" t="s">
-        <v>388</v>
+        <v>585</v>
       </c>
       <c r="H285" t="s">
-        <v>484</v>
+        <v>597</v>
       </c>
       <c r="I285" t="s">
-        <v>506</v>
+        <v>598</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>460</v>
+        <v>556</v>
       </c>
       <c r="B286" t="s">
-        <v>461</v>
+        <v>557</v>
       </c>
       <c r="C286" t="s">
-        <v>312</v>
+        <v>171</v>
       </c>
       <c r="E286" t="s">
-        <v>387</v>
+        <v>488</v>
       </c>
       <c r="F286">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G286" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="H286" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="I286" t="s">
-        <v>532</v>
+        <v>448</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="B287" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="C287" t="s">
-        <v>296</v>
+        <v>138</v>
       </c>
       <c r="E287" t="s">
-        <v>387</v>
+        <v>488</v>
       </c>
       <c r="F287">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="G287" t="s">
-        <v>388</v>
+        <v>599</v>
       </c>
       <c r="H287" t="s">
-        <v>388</v>
+        <v>600</v>
       </c>
       <c r="I287" t="s">
-        <v>582</v>
+        <v>466</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>363</v>
+        <v>541</v>
       </c>
       <c r="B288" t="s">
-        <v>364</v>
+        <v>542</v>
       </c>
       <c r="C288" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="E288" t="s">
-        <v>240</v>
+        <v>488</v>
       </c>
       <c r="F288">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G288" t="s">
-        <v>37</v>
+        <v>601</v>
       </c>
       <c r="H288" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="I288" t="s">
-        <v>255</v>
+        <v>534</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B289" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="C289" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="E289" t="s">
-        <v>488</v>
+        <v>387</v>
       </c>
       <c r="F289">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G289" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="H289" t="s">
-        <v>37</v>
+        <v>484</v>
       </c>
       <c r="I289" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>507</v>
+        <v>460</v>
       </c>
       <c r="B290" t="s">
-        <v>508</v>
+        <v>461</v>
       </c>
       <c r="C290" t="s">
-        <v>216</v>
+        <v>312</v>
       </c>
       <c r="E290" t="s">
-        <v>176</v>
+        <v>387</v>
       </c>
       <c r="F290">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G290" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="H290" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="I290" t="s">
-        <v>178</v>
+        <v>535</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B291" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="C291" t="s">
-        <v>148</v>
+        <v>296</v>
       </c>
       <c r="E291" t="s">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="F291">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G291" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="H291" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="I291" t="s">
-        <v>243</v>
+        <v>582</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
-        <v>561</v>
+        <v>363</v>
       </c>
       <c r="B292" t="s">
-        <v>562</v>
+        <v>364</v>
       </c>
       <c r="C292" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="E292" t="s">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="F292">
         <v>5.0</v>
       </c>
       <c r="G292" t="s">
-        <v>583</v>
+        <v>37</v>
       </c>
       <c r="H292" t="s">
-        <v>334</v>
+        <v>37</v>
       </c>
       <c r="I292" t="s">
-        <v>445</v>
+        <v>255</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="B293" t="s">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="C293" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="E293" t="s">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="F293">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G293" t="s">
         <v>37</v>
@@ -9895,96 +9895,96 @@
         <v>37</v>
       </c>
       <c r="I293" t="s">
-        <v>251</v>
+        <v>178</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="B294" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="C294" t="s">
         <v>148</v>
       </c>
       <c r="E294" t="s">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="F294">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G294" t="s">
-        <v>583</v>
+        <v>37</v>
       </c>
       <c r="H294" t="s">
-        <v>598</v>
+        <v>37</v>
       </c>
       <c r="I294" t="s">
-        <v>599</v>
+        <v>243</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B295" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="C295" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E295" t="s">
         <v>488</v>
       </c>
       <c r="F295">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="G295" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="H295" t="s">
-        <v>601</v>
+        <v>334</v>
       </c>
       <c r="I295" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="B296" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="C296" t="s">
-        <v>346</v>
+        <v>171</v>
       </c>
       <c r="E296" t="s">
-        <v>387</v>
+        <v>240</v>
       </c>
       <c r="F296">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G296" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="H296" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="I296" t="s">
-        <v>582</v>
+        <v>251</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B297" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C297" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="E297" t="s">
         <v>387</v>
@@ -10004,13 +10004,13 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>590</v>
+        <v>561</v>
       </c>
       <c r="B298" t="s">
-        <v>591</v>
+        <v>562</v>
       </c>
       <c r="C298" t="s">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="E298" t="s">
         <v>387</v>
@@ -10030,13 +10030,13 @@
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B299" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C299" t="s">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="E299" t="s">
         <v>387</v>
@@ -10056,45 +10056,45 @@
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="B300" t="s">
-        <v>571</v>
+        <v>593</v>
       </c>
       <c r="C300" t="s">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="E300" t="s">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="F300">
         <v>1.0</v>
       </c>
       <c r="G300" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="H300" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="I300" t="s">
-        <v>384</v>
+        <v>582</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>363</v>
+        <v>572</v>
       </c>
       <c r="B301" t="s">
-        <v>364</v>
+        <v>573</v>
       </c>
       <c r="C301" t="s">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="E301" t="s">
         <v>240</v>
       </c>
       <c r="F301">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G301" t="s">
         <v>37</v>
@@ -10103,24 +10103,24 @@
         <v>37</v>
       </c>
       <c r="I301" t="s">
-        <v>251</v>
+        <v>384</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
-        <v>602</v>
+        <v>363</v>
       </c>
       <c r="B302" t="s">
-        <v>603</v>
+        <v>364</v>
       </c>
       <c r="C302" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="E302" t="s">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="F302">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G302" t="s">
         <v>37</v>
@@ -10129,24 +10129,24 @@
         <v>37</v>
       </c>
       <c r="I302" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>363</v>
+        <v>604</v>
       </c>
       <c r="B303" t="s">
-        <v>364</v>
+        <v>605</v>
       </c>
       <c r="C303" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="E303" t="s">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="F303">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G303" t="s">
         <v>37</v>
@@ -10155,41 +10155,41 @@
         <v>37</v>
       </c>
       <c r="I303" t="s">
-        <v>255</v>
+        <v>203</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>526</v>
+        <v>363</v>
       </c>
       <c r="B304" t="s">
-        <v>527</v>
+        <v>364</v>
       </c>
       <c r="C304" t="s">
         <v>148</v>
       </c>
       <c r="E304" t="s">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="F304">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G304" t="s">
-        <v>604</v>
+        <v>37</v>
       </c>
       <c r="H304" t="s">
-        <v>605</v>
+        <v>37</v>
       </c>
       <c r="I304" t="s">
-        <v>411</v>
+        <v>255</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B305" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C305" t="s">
         <v>296</v>
@@ -10212,10 +10212,10 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B306" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C306" t="s">
         <v>296</v>
@@ -10233,15 +10233,15 @@
         <v>388</v>
       </c>
       <c r="I306" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B307" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C307" t="s">
         <v>312</v>
@@ -10264,10 +10264,10 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B308" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C308" t="s">
         <v>148</v>
@@ -10316,10 +10316,10 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B310" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C310" t="s">
         <v>346</v>
@@ -10342,19 +10342,19 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>606</v>
+        <v>554</v>
       </c>
       <c r="B311" t="s">
-        <v>607</v>
+        <v>555</v>
       </c>
       <c r="C311" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="E311" t="s">
-        <v>608</v>
+        <v>488</v>
       </c>
       <c r="F311">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G311" t="s">
         <v>37</v>
@@ -10363,21 +10363,21 @@
         <v>37</v>
       </c>
       <c r="I311" t="s">
-        <v>212</v>
+        <v>558</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B312" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C312" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E312" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F312">
         <v>1.0</v>
@@ -10389,21 +10389,24 @@
         <v>37</v>
       </c>
       <c r="I312" t="s">
-        <v>308</v>
+        <v>212</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B313" t="s">
-        <v>613</v>
+        <v>610</v>
+      </c>
+      <c r="C313" t="s">
+        <v>179</v>
       </c>
       <c r="E313" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F313">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G313" t="s">
         <v>37</v>
@@ -10412,21 +10415,21 @@
         <v>37</v>
       </c>
       <c r="I313" t="s">
-        <v>615</v>
+        <v>308</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B314" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E314" t="s">
-        <v>103</v>
+        <v>614</v>
       </c>
       <c r="F314">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G314" t="s">
         <v>37</v>
@@ -10435,18 +10438,18 @@
         <v>37</v>
       </c>
       <c r="I314" t="s">
-        <v>108</v>
+        <v>615</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B315" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E315" t="s">
-        <v>483</v>
+        <v>103</v>
       </c>
       <c r="F315">
         <v>1.0</v>
@@ -10458,18 +10461,18 @@
         <v>37</v>
       </c>
       <c r="I315" t="s">
-        <v>404</v>
+        <v>108</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B316" t="s">
-        <v>102</v>
+        <v>619</v>
       </c>
       <c r="E316" t="s">
-        <v>113</v>
+        <v>483</v>
       </c>
       <c r="F316">
         <v>1.0</v>
@@ -10481,24 +10484,21 @@
         <v>37</v>
       </c>
       <c r="I316" t="s">
-        <v>108</v>
+        <v>404</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B317" t="s">
-        <v>622</v>
-      </c>
-      <c r="C317" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="E317" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="F317">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="G317" t="s">
         <v>37</v>
@@ -10507,7 +10507,7 @@
         <v>37</v>
       </c>
       <c r="I317" t="s">
-        <v>623</v>
+        <v>108</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -10518,13 +10518,13 @@
         <v>622</v>
       </c>
       <c r="C318" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E318" t="s">
         <v>139</v>
       </c>
       <c r="F318">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G318" t="s">
         <v>37</v>
@@ -10533,24 +10533,24 @@
         <v>37</v>
       </c>
       <c r="I318" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
-        <v>507</v>
+        <v>621</v>
       </c>
       <c r="B319" t="s">
-        <v>508</v>
+        <v>622</v>
       </c>
       <c r="C319" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="E319" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="F319">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G319" t="s">
         <v>37</v>
@@ -10559,24 +10559,24 @@
         <v>37</v>
       </c>
       <c r="I319" t="s">
-        <v>178</v>
+        <v>624</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
-        <v>625</v>
+        <v>507</v>
       </c>
       <c r="B320" t="s">
-        <v>626</v>
+        <v>508</v>
       </c>
       <c r="C320" t="s">
         <v>171</v>
       </c>
       <c r="E320" t="s">
-        <v>627</v>
+        <v>176</v>
       </c>
       <c r="F320">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G320" t="s">
         <v>37</v>
@@ -10585,21 +10585,21 @@
         <v>37</v>
       </c>
       <c r="I320" t="s">
-        <v>628</v>
+        <v>178</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>424</v>
+        <v>625</v>
       </c>
       <c r="B321" t="s">
-        <v>425</v>
+        <v>626</v>
       </c>
       <c r="C321" t="s">
         <v>171</v>
       </c>
       <c r="E321" t="s">
-        <v>246</v>
+        <v>627</v>
       </c>
       <c r="F321">
         <v>1.0</v>
@@ -10611,24 +10611,24 @@
         <v>37</v>
       </c>
       <c r="I321" t="s">
-        <v>248</v>
+        <v>628</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>570</v>
+        <v>424</v>
       </c>
       <c r="B322" t="s">
-        <v>571</v>
+        <v>425</v>
       </c>
       <c r="C322" t="s">
         <v>171</v>
       </c>
       <c r="E322" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F322">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G322" t="s">
         <v>37</v>
@@ -10637,24 +10637,24 @@
         <v>37</v>
       </c>
       <c r="I322" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
-        <v>363</v>
+        <v>572</v>
       </c>
       <c r="B323" t="s">
-        <v>364</v>
+        <v>573</v>
       </c>
       <c r="C323" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="E323" t="s">
         <v>240</v>
       </c>
       <c r="F323">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G323" t="s">
         <v>37</v>
@@ -10663,15 +10663,15 @@
         <v>37</v>
       </c>
       <c r="I323" t="s">
-        <v>384</v>
+        <v>253</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
-        <v>565</v>
+        <v>363</v>
       </c>
       <c r="B324" t="s">
-        <v>566</v>
+        <v>364</v>
       </c>
       <c r="C324" t="s">
         <v>216</v>
@@ -10694,19 +10694,19 @@
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
-        <v>382</v>
+        <v>567</v>
       </c>
       <c r="B325" t="s">
-        <v>383</v>
+        <v>568</v>
       </c>
       <c r="C325" t="s">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="E325" t="s">
         <v>240</v>
       </c>
       <c r="F325">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G325" t="s">
         <v>37</v>
@@ -10715,24 +10715,24 @@
         <v>37</v>
       </c>
       <c r="I325" t="s">
-        <v>253</v>
+        <v>384</v>
       </c>
     </row>
     <row r="326" spans="1:9">
       <c r="A326" t="s">
-        <v>543</v>
+        <v>382</v>
       </c>
       <c r="B326" t="s">
-        <v>544</v>
+        <v>383</v>
       </c>
       <c r="C326" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="E326" t="s">
         <v>240</v>
       </c>
       <c r="F326">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G326" t="s">
         <v>37</v>
@@ -10741,24 +10741,24 @@
         <v>37</v>
       </c>
       <c r="I326" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B327" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C327" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="E327" t="s">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="F327">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G327" t="s">
         <v>37</v>
@@ -10767,15 +10767,15 @@
         <v>37</v>
       </c>
       <c r="I327" t="s">
-        <v>555</v>
+        <v>255</v>
       </c>
     </row>
     <row r="328" spans="1:9">
       <c r="A328" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B328" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C328" t="s">
         <v>138</v>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="B329" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="C329" t="s">
         <v>148</v>
@@ -10819,7 +10819,7 @@
         <v>37</v>
       </c>
       <c r="I329" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="330" spans="1:9">
@@ -10850,10 +10850,10 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="B331" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="C331" t="s">
         <v>138</v>
@@ -11009,7 +11009,7 @@
         <v>37</v>
       </c>
       <c r="I337" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="338" spans="1:9">
@@ -11060,16 +11060,16 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B340" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C340" t="s">
         <v>346</v>
       </c>
       <c r="E340" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F340">
         <v>3.0</v>
@@ -11086,16 +11086,16 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B341" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C341" t="s">
         <v>266</v>
       </c>
       <c r="E341" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F341">
         <v>7.0</v>
@@ -11112,16 +11112,16 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B342" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C342" t="s">
         <v>224</v>
       </c>
       <c r="E342" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F342">
         <v>4.0</v>
@@ -11133,7 +11133,7 @@
         <v>37</v>
       </c>
       <c r="I342" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -11147,7 +11147,7 @@
         <v>346</v>
       </c>
       <c r="E343" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F343">
         <v>4.0</v>
@@ -11159,7 +11159,7 @@
         <v>37</v>
       </c>
       <c r="I343" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -11173,7 +11173,7 @@
         <v>266</v>
       </c>
       <c r="E344" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F344">
         <v>6.0</v>
@@ -11199,7 +11199,7 @@
         <v>224</v>
       </c>
       <c r="E345" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F345">
         <v>4.0</v>
@@ -11211,7 +11211,7 @@
         <v>37</v>
       </c>
       <c r="I345" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -11225,7 +11225,7 @@
         <v>296</v>
       </c>
       <c r="E346" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F346">
         <v>4.0</v>
@@ -11237,7 +11237,7 @@
         <v>37</v>
       </c>
       <c r="I346" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -11251,7 +11251,7 @@
         <v>312</v>
       </c>
       <c r="E347" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F347">
         <v>1.0</v>
@@ -11277,7 +11277,7 @@
         <v>266</v>
       </c>
       <c r="E348" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F348">
         <v>5.0</v>
@@ -11303,7 +11303,7 @@
         <v>224</v>
       </c>
       <c r="E349" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F349">
         <v>5.0</v>
@@ -11329,7 +11329,7 @@
         <v>296</v>
       </c>
       <c r="E350" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F350">
         <v>5.0</v>
@@ -11355,7 +11355,7 @@
         <v>312</v>
       </c>
       <c r="E351" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F351">
         <v>2.0</v>
@@ -11381,7 +11381,7 @@
         <v>346</v>
       </c>
       <c r="E352" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F352">
         <v>1.0</v>
@@ -11407,7 +11407,7 @@
         <v>224</v>
       </c>
       <c r="E353" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F353">
         <v>3.0</v>
@@ -11419,7 +11419,7 @@
         <v>37</v>
       </c>
       <c r="I353" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="354" spans="1:9">
@@ -11433,7 +11433,7 @@
         <v>312</v>
       </c>
       <c r="E354" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F354">
         <v>1.0</v>
@@ -11459,7 +11459,7 @@
         <v>346</v>
       </c>
       <c r="E355" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F355">
         <v>2.0</v>
@@ -11471,7 +11471,7 @@
         <v>37</v>
       </c>
       <c r="I355" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="356" spans="1:9">
@@ -11485,7 +11485,7 @@
         <v>266</v>
       </c>
       <c r="E356" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F356">
         <v>3.0</v>
@@ -11511,7 +11511,7 @@
         <v>224</v>
       </c>
       <c r="E357" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F357">
         <v>3.0</v>
@@ -11537,7 +11537,7 @@
         <v>296</v>
       </c>
       <c r="E358" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F358">
         <v>2.0</v>
@@ -11549,7 +11549,7 @@
         <v>37</v>
       </c>
       <c r="I358" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="359" spans="1:9">
@@ -11563,7 +11563,7 @@
         <v>346</v>
       </c>
       <c r="E359" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F359">
         <v>2.0</v>
@@ -11575,7 +11575,7 @@
         <v>37</v>
       </c>
       <c r="I359" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="360" spans="1:9">
@@ -11589,7 +11589,7 @@
         <v>266</v>
       </c>
       <c r="E360" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F360">
         <v>4.0</v>
@@ -11615,7 +11615,7 @@
         <v>224</v>
       </c>
       <c r="E361" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F361">
         <v>3.0</v>
@@ -11641,7 +11641,7 @@
         <v>296</v>
       </c>
       <c r="E362" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F362">
         <v>2.0</v>
@@ -11653,7 +11653,7 @@
         <v>37</v>
       </c>
       <c r="I362" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="363" spans="1:9">
@@ -11667,7 +11667,7 @@
         <v>312</v>
       </c>
       <c r="E363" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F363">
         <v>1.0</v>
@@ -11693,7 +11693,7 @@
         <v>346</v>
       </c>
       <c r="E364" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F364">
         <v>2.0</v>
@@ -11719,7 +11719,7 @@
         <v>266</v>
       </c>
       <c r="E365" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F365">
         <v>1.0</v>
@@ -11745,7 +11745,7 @@
         <v>224</v>
       </c>
       <c r="E366" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F366">
         <v>3.0</v>
@@ -11771,7 +11771,7 @@
         <v>296</v>
       </c>
       <c r="E367" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F367">
         <v>1.0</v>
@@ -11797,7 +11797,7 @@
         <v>266</v>
       </c>
       <c r="E368" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F368">
         <v>3.0</v>
@@ -11823,7 +11823,7 @@
         <v>296</v>
       </c>
       <c r="E369" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F369">
         <v>1.0</v>
@@ -11849,7 +11849,7 @@
         <v>346</v>
       </c>
       <c r="E370" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F370">
         <v>2.0</v>
@@ -11861,7 +11861,7 @@
         <v>37</v>
       </c>
       <c r="I370" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="371" spans="1:9">
@@ -11875,7 +11875,7 @@
         <v>266</v>
       </c>
       <c r="E371" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F371">
         <v>5.0</v>
@@ -11901,7 +11901,7 @@
         <v>224</v>
       </c>
       <c r="E372" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F372">
         <v>3.0</v>
@@ -11913,7 +11913,7 @@
         <v>37</v>
       </c>
       <c r="I372" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="373" spans="1:9">
@@ -11927,7 +11927,7 @@
         <v>296</v>
       </c>
       <c r="E373" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F373">
         <v>3.0</v>
@@ -11939,7 +11939,7 @@
         <v>37</v>
       </c>
       <c r="I373" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="374" spans="1:9">
@@ -11953,7 +11953,7 @@
         <v>312</v>
       </c>
       <c r="E374" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F374">
         <v>2.0</v>
@@ -11965,7 +11965,7 @@
         <v>37</v>
       </c>
       <c r="I374" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="375" spans="1:9">
@@ -12005,7 +12005,7 @@
         <v>266</v>
       </c>
       <c r="E376" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F376">
         <v>3.0</v>
@@ -12022,16 +12022,16 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B377" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C377" t="s">
         <v>312</v>
       </c>
       <c r="E377" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F377">
         <v>2.0</v>

--- a/src/inventory/Syl.xlsx
+++ b/src/inventory/Syl.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="665">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -584,7 +584,7 @@
     <t>৳303.57</t>
   </si>
   <si>
-    <t>৳1,214.29</t>
+    <t>৳607.14</t>
   </si>
   <si>
     <t>109-0402-036</t>
@@ -1154,6 +1154,18 @@
     <t>৳5,900.00</t>
   </si>
   <si>
+    <t>109-0303-004</t>
+  </si>
+  <si>
+    <t>Navy Blue Leather Passport Holder</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,PASSPORT HOLDER</t>
+  </si>
+  <si>
+    <t>৳880.00</t>
+  </si>
+  <si>
     <t>102-0302-008</t>
   </si>
   <si>
@@ -1169,18 +1181,6 @@
     <t>৳5,300.00</t>
   </si>
   <si>
-    <t>109-0303-004</t>
-  </si>
-  <si>
-    <t>Navy Blue Leather Passport Holder</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,PASSPORT HOLDER</t>
-  </si>
-  <si>
-    <t>৳880.00</t>
-  </si>
-  <si>
     <t>105-0301-009</t>
   </si>
   <si>
@@ -1214,9 +1214,6 @@
     <t>৳319.24</t>
   </si>
   <si>
-    <t>৳638.47</t>
-  </si>
-  <si>
     <t>105-0301-006</t>
   </si>
   <si>
@@ -1241,72 +1238,105 @@
     <t>৳3,990.00</t>
   </si>
   <si>
+    <t>105-0202-006</t>
+  </si>
+  <si>
+    <t>Lavender Full Sleeve Turtleneck T-shirt</t>
+  </si>
+  <si>
+    <t>৳1,396.00</t>
+  </si>
+  <si>
+    <t>109-0101-048</t>
+  </si>
+  <si>
+    <t>Long Leather Wallet 048</t>
+  </si>
+  <si>
+    <t>Men / WALLET,LONG</t>
+  </si>
+  <si>
+    <t>৳2,598.00</t>
+  </si>
+  <si>
+    <t>৳3,160.00</t>
+  </si>
+  <si>
+    <t>109-0104-005</t>
+  </si>
+  <si>
+    <t>Card Holder</t>
+  </si>
+  <si>
+    <t>Men / Card Holder</t>
+  </si>
+  <si>
+    <t>৳1,380.00</t>
+  </si>
+  <si>
+    <t>109-0104-006</t>
+  </si>
+  <si>
+    <t>Card Holder 06</t>
+  </si>
+  <si>
+    <t>105-0401-006</t>
+  </si>
+  <si>
+    <t>Burgundy Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳1,750.00</t>
+  </si>
+  <si>
+    <t>৳2,700.00</t>
+  </si>
+  <si>
     <t>৳1,950.00</t>
   </si>
   <si>
     <t>৳3,540.00</t>
   </si>
   <si>
-    <t>105-0202-006</t>
-  </si>
-  <si>
-    <t>Lavender Full Sleeve Turtleneck T-shirt</t>
-  </si>
-  <si>
-    <t>৳1,396.00</t>
-  </si>
-  <si>
-    <t>109-0101-048</t>
-  </si>
-  <si>
-    <t>Long Leather Wallet 048</t>
-  </si>
-  <si>
-    <t>Men / WALLET,LONG</t>
-  </si>
-  <si>
-    <t>৳2,598.00</t>
-  </si>
-  <si>
-    <t>৳3,160.00</t>
-  </si>
-  <si>
-    <t>109-0104-005</t>
-  </si>
-  <si>
-    <t>Card Holder</t>
-  </si>
-  <si>
-    <t>Men / Card Holder</t>
-  </si>
-  <si>
-    <t>৳1,380.00</t>
-  </si>
-  <si>
-    <t>109-0104-006</t>
-  </si>
-  <si>
-    <t>Card Holder 06</t>
-  </si>
-  <si>
-    <t>105-0401-006</t>
-  </si>
-  <si>
-    <t>Burgundy Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳1,750.00</t>
-  </si>
-  <si>
-    <t>৳2,700.00</t>
-  </si>
-  <si>
     <t>102-0402-034</t>
   </si>
   <si>
     <t>Mid Blue Denim Shirt</t>
   </si>
   <si>
+    <t>109-0401-223</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,BELT,Draft Items</t>
+  </si>
+  <si>
+    <t>৳949.00</t>
+  </si>
+  <si>
+    <t>105-0201-036</t>
+  </si>
+  <si>
+    <t>Full Sleeve Graphic T-shirt</t>
+  </si>
+  <si>
+    <t>৳728.00</t>
+  </si>
+  <si>
+    <t>৳2,950.00</t>
+  </si>
+  <si>
+    <t>৳540.00</t>
+  </si>
+  <si>
+    <t>৳207.17</t>
+  </si>
+  <si>
+    <t>৳828.66</t>
+  </si>
+  <si>
+    <t>৳2,792.00</t>
+  </si>
+  <si>
     <t>102-0302-006</t>
   </si>
   <si>
@@ -1316,25 +1346,10 @@
     <t>৳2,600.00</t>
   </si>
   <si>
-    <t>109-0401-223</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,BELT,Draft Items</t>
-  </si>
-  <si>
-    <t>৳949.00</t>
-  </si>
-  <si>
-    <t>105-0201-036</t>
-  </si>
-  <si>
-    <t>Full Sleeve Graphic T-shirt</t>
-  </si>
-  <si>
-    <t>৳728.00</t>
-  </si>
-  <si>
-    <t>৳2,950.00</t>
+    <t>109-0103-010</t>
+  </si>
+  <si>
+    <t>Black Perforated Leather Trifold Wallet</t>
   </si>
   <si>
     <t>৳1,000.00</t>
@@ -1343,22 +1358,52 @@
     <t>৳2,650.00</t>
   </si>
   <si>
-    <t>৳540.00</t>
-  </si>
-  <si>
-    <t>৳207.17</t>
-  </si>
-  <si>
-    <t>৳828.66</t>
-  </si>
-  <si>
-    <t>৳2,792.00</t>
-  </si>
-  <si>
-    <t>109-0103-010</t>
-  </si>
-  <si>
-    <t>Black Perforated Leather Trifold Wallet</t>
+    <t>102-0301-004</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 004</t>
+  </si>
+  <si>
+    <t>৳4,550.00</t>
+  </si>
+  <si>
+    <t>৳8,260.00</t>
+  </si>
+  <si>
+    <t>105-0401-005</t>
+  </si>
+  <si>
+    <t>Sable Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳2,160.00</t>
+  </si>
+  <si>
+    <t>105-0401-002</t>
+  </si>
+  <si>
+    <t>Glacier Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>105-0401-003</t>
+  </si>
+  <si>
+    <t>Tank Top 003</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Tank Top</t>
+  </si>
+  <si>
+    <t>৳83.33</t>
+  </si>
+  <si>
+    <t>৳416.67</t>
+  </si>
+  <si>
+    <t>৳3,200.00</t>
+  </si>
+  <si>
+    <t>৳1,080.00</t>
   </si>
   <si>
     <t>102-0301-002</t>
@@ -1367,57 +1412,9 @@
     <t>Half Sleeve shirt 002</t>
   </si>
   <si>
-    <t>৳4,550.00</t>
-  </si>
-  <si>
     <t>৳9,275.00</t>
   </si>
   <si>
-    <t>102-0301-004</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 004</t>
-  </si>
-  <si>
-    <t>৳8,260.00</t>
-  </si>
-  <si>
-    <t>105-0401-005</t>
-  </si>
-  <si>
-    <t>Sable Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳2,160.00</t>
-  </si>
-  <si>
-    <t>105-0401-002</t>
-  </si>
-  <si>
-    <t>Glacier Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>105-0401-003</t>
-  </si>
-  <si>
-    <t>Tank Top 003</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Tank Top</t>
-  </si>
-  <si>
-    <t>৳83.33</t>
-  </si>
-  <si>
-    <t>৳416.67</t>
-  </si>
-  <si>
-    <t>৳3,200.00</t>
-  </si>
-  <si>
-    <t>৳1,080.00</t>
-  </si>
-  <si>
     <t>109-0402-060</t>
   </si>
   <si>
@@ -1433,24 +1430,30 @@
     <t>Men / MEN,ACCESSORIES,WALLET,TRI-FOLD,Draft Items</t>
   </si>
   <si>
+    <t>105-0101-378</t>
+  </si>
+  <si>
+    <t>Mocha Rock T-shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
+  </si>
+  <si>
+    <t>৳640.00</t>
+  </si>
+  <si>
+    <t>103-0200-099</t>
+  </si>
+  <si>
+    <t>Black Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
     <t>৳1,300.00</t>
   </si>
   <si>
     <t>৳2,360.00</t>
   </si>
   <si>
-    <t>105-0101-378</t>
-  </si>
-  <si>
-    <t>Mocha Rock T-shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
-  </si>
-  <si>
-    <t>৳640.00</t>
-  </si>
-  <si>
     <t>102-0302-001</t>
   </si>
   <si>
@@ -1460,21 +1463,15 @@
     <t>৳1,450.00</t>
   </si>
   <si>
-    <t>103-0200-099</t>
-  </si>
-  <si>
-    <t>Black Polo Shirt in Cotton Pique</t>
+    <t>105-0101-373</t>
+  </si>
+  <si>
+    <t>Rust Bloom T-shirt</t>
   </si>
   <si>
     <t>৳3,975.00</t>
   </si>
   <si>
-    <t>105-0101-373</t>
-  </si>
-  <si>
-    <t>Rust Bloom T-shirt</t>
-  </si>
-  <si>
     <t>৳250.00</t>
   </si>
   <si>
@@ -1541,18 +1538,18 @@
     <t>৳1,620.00</t>
   </si>
   <si>
+    <t>102-0302-004</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 004</t>
+  </si>
+  <si>
     <t>102-0302-010</t>
   </si>
   <si>
     <t>Cuban Shirt 010</t>
   </si>
   <si>
-    <t>102-0302-004</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 004</t>
-  </si>
-  <si>
     <t>102-0302-007</t>
   </si>
   <si>
@@ -1745,34 +1742,34 @@
     <t>৳7,670.00</t>
   </si>
   <si>
+    <t>102-0301-005</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 005</t>
+  </si>
+  <si>
+    <t>102-0301-009</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 009</t>
+  </si>
+  <si>
+    <t>৳95.45</t>
+  </si>
+  <si>
+    <t>৳286.36</t>
+  </si>
+  <si>
+    <t>105-0201-032</t>
+  </si>
+  <si>
+    <t>Full Sleeve White Stripe T-shirt</t>
+  </si>
+  <si>
     <t>102-0301-003</t>
   </si>
   <si>
     <t>Half Sleeve shirt 003</t>
-  </si>
-  <si>
-    <t>102-0301-005</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 005</t>
-  </si>
-  <si>
-    <t>102-0301-009</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 009</t>
-  </si>
-  <si>
-    <t>৳95.45</t>
-  </si>
-  <si>
-    <t>৳286.36</t>
-  </si>
-  <si>
-    <t>105-0201-032</t>
-  </si>
-  <si>
-    <t>Full Sleeve White Stripe T-shirt</t>
   </si>
   <si>
     <t>৳210.00</t>
@@ -4194,7 +4191,7 @@
         <v>140</v>
       </c>
       <c r="F72">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G72" t="s">
         <v>188</v>
@@ -4203,7 +4200,7 @@
         <v>189</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -5769,152 +5766,152 @@
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>373</v>
+        <v>256</v>
       </c>
       <c r="B135" t="s">
-        <v>374</v>
+        <v>257</v>
       </c>
       <c r="C135" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="E135" t="s">
-        <v>375</v>
+        <v>259</v>
       </c>
       <c r="F135">
         <v>5.0</v>
       </c>
       <c r="G135" t="s">
-        <v>376</v>
+        <v>109</v>
       </c>
       <c r="H135" t="s">
-        <v>377</v>
+        <v>278</v>
       </c>
       <c r="I135" t="s">
-        <v>378</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
       <c r="B136" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="C136" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
       <c r="E136" t="s">
         <v>259</v>
       </c>
       <c r="F136">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G136" t="s">
         <v>109</v>
       </c>
       <c r="H136" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="I136" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>306</v>
+        <v>373</v>
       </c>
       <c r="B137" t="s">
-        <v>307</v>
+        <v>374</v>
       </c>
       <c r="C137" t="s">
-        <v>330</v>
+        <v>258</v>
       </c>
       <c r="E137" t="s">
-        <v>259</v>
+        <v>375</v>
       </c>
       <c r="F137">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G137" t="s">
-        <v>109</v>
+        <v>376</v>
       </c>
       <c r="H137" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="I137" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>379</v>
+        <v>280</v>
       </c>
       <c r="B138" t="s">
-        <v>380</v>
+        <v>281</v>
       </c>
       <c r="C138" t="s">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="E138" t="s">
-        <v>375</v>
+        <v>283</v>
       </c>
       <c r="F138">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G138" t="s">
-        <v>381</v>
+        <v>222</v>
       </c>
       <c r="H138" t="s">
-        <v>382</v>
+        <v>222</v>
       </c>
       <c r="I138" t="s">
-        <v>383</v>
+        <v>331</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>280</v>
+        <v>379</v>
       </c>
       <c r="B139" t="s">
-        <v>281</v>
-      </c>
-      <c r="C139" t="s">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="E139" t="s">
-        <v>283</v>
+        <v>381</v>
       </c>
       <c r="F139">
         <v>1.0</v>
       </c>
       <c r="G139" t="s">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="H139" t="s">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="I139" t="s">
-        <v>331</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
+        <v>383</v>
+      </c>
+      <c r="B140" t="s">
         <v>384</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
+        <v>258</v>
+      </c>
+      <c r="E140" t="s">
+        <v>375</v>
+      </c>
+      <c r="F140">
+        <v>4.0</v>
+      </c>
+      <c r="G140" t="s">
         <v>385</v>
       </c>
-      <c r="E140" t="s">
+      <c r="H140" t="s">
         <v>386</v>
-      </c>
-      <c r="F140">
-        <v>1.0</v>
-      </c>
-      <c r="G140" t="s">
-        <v>37</v>
-      </c>
-      <c r="H140" t="s">
-        <v>37</v>
       </c>
       <c r="I140" t="s">
         <v>387</v>
@@ -6009,24 +6006,24 @@
         <v>221</v>
       </c>
       <c r="F144">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="s">
         <v>398</v>
       </c>
       <c r="H144" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I144" t="s">
-        <v>301</v>
+        <v>223</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
+        <v>399</v>
+      </c>
+      <c r="B145" t="s">
         <v>400</v>
-      </c>
-      <c r="B145" t="s">
-        <v>401</v>
       </c>
       <c r="C145" t="s">
         <v>330</v>
@@ -6101,48 +6098,48 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
+        <v>401</v>
+      </c>
+      <c r="B148" t="s">
         <v>402</v>
       </c>
-      <c r="B148" t="s">
+      <c r="E148" t="s">
         <v>403</v>
-      </c>
-      <c r="E148" t="s">
-        <v>404</v>
       </c>
       <c r="F148">
         <v>10.0</v>
       </c>
       <c r="G148" t="s">
+        <v>404</v>
+      </c>
+      <c r="H148" t="s">
         <v>405</v>
       </c>
-      <c r="H148" t="s">
+      <c r="I148" t="s">
         <v>406</v>
-      </c>
-      <c r="I148" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="B149" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="C149" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E149" t="s">
-        <v>375</v>
+        <v>242</v>
       </c>
       <c r="F149">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G149" t="s">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="H149" t="s">
-        <v>408</v>
+        <v>37</v>
       </c>
       <c r="I149" t="s">
         <v>409</v>
@@ -6150,19 +6147,19 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>410</v>
+        <v>371</v>
       </c>
       <c r="B150" t="s">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="C150" t="s">
         <v>212</v>
       </c>
       <c r="E150" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F150">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G150" t="s">
         <v>37</v>
@@ -6171,93 +6168,90 @@
         <v>37</v>
       </c>
       <c r="I150" t="s">
-        <v>412</v>
+        <v>346</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="B151" t="s">
-        <v>372</v>
-      </c>
-      <c r="C151" t="s">
-        <v>212</v>
+        <v>411</v>
       </c>
       <c r="E151" t="s">
-        <v>236</v>
+        <v>412</v>
       </c>
       <c r="F151">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="H151" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="I151" t="s">
-        <v>346</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>413</v>
+        <v>298</v>
       </c>
       <c r="B152" t="s">
+        <v>299</v>
+      </c>
+      <c r="C152" t="s">
+        <v>258</v>
+      </c>
+      <c r="E152" t="s">
+        <v>221</v>
+      </c>
+      <c r="F152">
+        <v>4.0</v>
+      </c>
+      <c r="G152" t="s">
+        <v>222</v>
+      </c>
+      <c r="H152" t="s">
+        <v>335</v>
+      </c>
+      <c r="I152" t="s">
         <v>414</v>
-      </c>
-      <c r="E152" t="s">
-        <v>415</v>
-      </c>
-      <c r="F152">
-        <v>2.0</v>
-      </c>
-      <c r="G152" t="s">
-        <v>134</v>
-      </c>
-      <c r="H152" t="s">
-        <v>135</v>
-      </c>
-      <c r="I152" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>298</v>
+        <v>415</v>
       </c>
       <c r="B153" t="s">
-        <v>299</v>
-      </c>
-      <c r="C153" t="s">
-        <v>258</v>
+        <v>416</v>
       </c>
       <c r="E153" t="s">
-        <v>221</v>
+        <v>417</v>
       </c>
       <c r="F153">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G153" t="s">
         <v>222</v>
       </c>
       <c r="H153" t="s">
-        <v>335</v>
+        <v>273</v>
       </c>
       <c r="I153" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B154" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E154" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F154">
         <v>2.0</v>
@@ -6269,90 +6263,93 @@
         <v>273</v>
       </c>
       <c r="I154" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
+        <v>421</v>
+      </c>
+      <c r="B155" t="s">
         <v>422</v>
       </c>
-      <c r="B155" t="s">
-        <v>423</v>
+      <c r="C155" t="s">
+        <v>258</v>
       </c>
       <c r="E155" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="F155">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G155" t="s">
         <v>222</v>
       </c>
       <c r="H155" t="s">
-        <v>273</v>
+        <v>423</v>
       </c>
       <c r="I155" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="B156" t="s">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="C156" t="s">
-        <v>258</v>
+        <v>330</v>
       </c>
       <c r="E156" t="s">
-        <v>392</v>
+        <v>221</v>
       </c>
       <c r="F156">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="s">
         <v>222</v>
       </c>
       <c r="H156" t="s">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="I156" t="s">
-        <v>427</v>
+        <v>223</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="B157" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="C157" t="s">
-        <v>330</v>
+        <v>220</v>
       </c>
       <c r="E157" t="s">
-        <v>221</v>
+        <v>375</v>
       </c>
       <c r="F157">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G157" t="s">
-        <v>222</v>
+        <v>376</v>
       </c>
       <c r="H157" t="s">
-        <v>222</v>
+        <v>425</v>
       </c>
       <c r="I157" t="s">
-        <v>223</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
+        <v>427</v>
+      </c>
+      <c r="B158" t="s">
         <v>428</v>
-      </c>
-      <c r="B158" t="s">
-        <v>429</v>
       </c>
       <c r="C158" t="s">
         <v>212</v>
@@ -6375,212 +6372,212 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
+        <v>429</v>
+      </c>
+      <c r="B159" t="s">
+        <v>429</v>
+      </c>
+      <c r="E159" t="s">
         <v>430</v>
       </c>
-      <c r="B159" t="s">
+      <c r="F159">
+        <v>1.0</v>
+      </c>
+      <c r="G159" t="s">
+        <v>37</v>
+      </c>
+      <c r="H159" t="s">
+        <v>37</v>
+      </c>
+      <c r="I159" t="s">
         <v>431</v>
-      </c>
-      <c r="C159" t="s">
-        <v>258</v>
-      </c>
-      <c r="E159" t="s">
-        <v>375</v>
-      </c>
-      <c r="F159">
-        <v>4.0</v>
-      </c>
-      <c r="G159" t="s">
-        <v>376</v>
-      </c>
-      <c r="H159" t="s">
-        <v>432</v>
-      </c>
-      <c r="I159" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B160" t="s">
         <v>433</v>
       </c>
+      <c r="C160" t="s">
+        <v>175</v>
+      </c>
       <c r="E160" t="s">
+        <v>236</v>
+      </c>
+      <c r="F160">
+        <v>1.0</v>
+      </c>
+      <c r="G160" t="s">
+        <v>37</v>
+      </c>
+      <c r="H160" t="s">
+        <v>37</v>
+      </c>
+      <c r="I160" t="s">
         <v>434</v>
-      </c>
-      <c r="F160">
-        <v>1.0</v>
-      </c>
-      <c r="G160" t="s">
-        <v>37</v>
-      </c>
-      <c r="H160" t="s">
-        <v>37</v>
-      </c>
-      <c r="I160" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>436</v>
+        <v>390</v>
       </c>
       <c r="B161" t="s">
-        <v>437</v>
+        <v>391</v>
       </c>
       <c r="C161" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="E161" t="s">
-        <v>236</v>
+        <v>392</v>
       </c>
       <c r="F161">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G161" t="s">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="H161" t="s">
-        <v>37</v>
+        <v>423</v>
       </c>
       <c r="I161" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="B162" t="s">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="C162" t="s">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="E162" t="s">
         <v>392</v>
       </c>
       <c r="F162">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G162" t="s">
         <v>222</v>
       </c>
       <c r="H162" t="s">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="I162" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>379</v>
+        <v>240</v>
       </c>
       <c r="B163" t="s">
-        <v>380</v>
+        <v>241</v>
       </c>
       <c r="C163" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="E163" t="s">
-        <v>375</v>
+        <v>242</v>
       </c>
       <c r="F163">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G163" t="s">
-        <v>381</v>
+        <v>437</v>
       </c>
       <c r="H163" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I163" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="B164" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="C164" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="E164" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="F164">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G164" t="s">
-        <v>222</v>
+        <v>376</v>
       </c>
       <c r="H164" t="s">
-        <v>222</v>
+        <v>442</v>
       </c>
       <c r="I164" t="s">
-        <v>442</v>
+        <v>387</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>240</v>
+        <v>443</v>
       </c>
       <c r="B165" t="s">
-        <v>241</v>
-      </c>
-      <c r="C165" t="s">
-        <v>175</v>
+        <v>444</v>
       </c>
       <c r="E165" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="F165">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G165" t="s">
-        <v>443</v>
+        <v>37</v>
       </c>
       <c r="H165" t="s">
-        <v>444</v>
+        <v>37</v>
       </c>
       <c r="I165" t="s">
-        <v>445</v>
+        <v>382</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
+        <v>383</v>
+      </c>
+      <c r="B166" t="s">
+        <v>384</v>
+      </c>
+      <c r="C166" t="s">
+        <v>220</v>
+      </c>
+      <c r="E166" t="s">
+        <v>375</v>
+      </c>
+      <c r="F166">
+        <v>2.0</v>
+      </c>
+      <c r="G166" t="s">
+        <v>385</v>
+      </c>
+      <c r="H166" t="s">
+        <v>445</v>
+      </c>
+      <c r="I166" t="s">
         <v>446</v>
-      </c>
-      <c r="B166" t="s">
-        <v>447</v>
-      </c>
-      <c r="E166" t="s">
-        <v>164</v>
-      </c>
-      <c r="F166">
-        <v>1.0</v>
-      </c>
-      <c r="G166" t="s">
-        <v>37</v>
-      </c>
-      <c r="H166" t="s">
-        <v>37</v>
-      </c>
-      <c r="I166" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
+        <v>447</v>
+      </c>
+      <c r="B167" t="s">
         <v>448</v>
-      </c>
-      <c r="B167" t="s">
-        <v>449</v>
       </c>
       <c r="C167" t="s">
         <v>258</v>
@@ -6595,148 +6592,148 @@
         <v>376</v>
       </c>
       <c r="H167" t="s">
+        <v>449</v>
+      </c>
+      <c r="I167" t="s">
         <v>450</v>
-      </c>
-      <c r="I167" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
+        <v>451</v>
+      </c>
+      <c r="B168" t="s">
         <v>452</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
+        <v>282</v>
+      </c>
+      <c r="E168" t="s">
+        <v>392</v>
+      </c>
+      <c r="F168">
+        <v>4.0</v>
+      </c>
+      <c r="G168" t="s">
+        <v>222</v>
+      </c>
+      <c r="H168" t="s">
+        <v>335</v>
+      </c>
+      <c r="I168" t="s">
         <v>453</v>
-      </c>
-      <c r="C168" t="s">
-        <v>258</v>
-      </c>
-      <c r="E168" t="s">
-        <v>375</v>
-      </c>
-      <c r="F168">
-        <v>7.0</v>
-      </c>
-      <c r="G168" t="s">
-        <v>376</v>
-      </c>
-      <c r="H168" t="s">
-        <v>450</v>
-      </c>
-      <c r="I168" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
+        <v>454</v>
+      </c>
+      <c r="B169" t="s">
         <v>455</v>
       </c>
-      <c r="B169" t="s">
-        <v>456</v>
-      </c>
       <c r="C169" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="E169" t="s">
         <v>392</v>
       </c>
       <c r="F169">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G169" t="s">
         <v>222</v>
       </c>
       <c r="H169" t="s">
-        <v>335</v>
+        <v>222</v>
       </c>
       <c r="I169" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
+        <v>456</v>
+      </c>
+      <c r="B170" t="s">
+        <v>457</v>
+      </c>
+      <c r="C170" t="s">
+        <v>330</v>
+      </c>
+      <c r="E170" t="s">
         <v>458</v>
       </c>
-      <c r="B170" t="s">
+      <c r="F170">
+        <v>5.0</v>
+      </c>
+      <c r="G170" t="s">
         <v>459</v>
       </c>
-      <c r="C170" t="s">
-        <v>258</v>
-      </c>
-      <c r="E170" t="s">
-        <v>392</v>
-      </c>
-      <c r="F170">
-        <v>1.0</v>
-      </c>
-      <c r="G170" t="s">
-        <v>222</v>
-      </c>
       <c r="H170" t="s">
-        <v>222</v>
+        <v>460</v>
       </c>
       <c r="I170" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B171" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C171" t="s">
-        <v>330</v>
+        <v>220</v>
       </c>
       <c r="E171" t="s">
+        <v>392</v>
+      </c>
+      <c r="F171">
+        <v>2.0</v>
+      </c>
+      <c r="G171" t="s">
+        <v>222</v>
+      </c>
+      <c r="H171" t="s">
+        <v>273</v>
+      </c>
+      <c r="I171" t="s">
         <v>462</v>
-      </c>
-      <c r="F171">
-        <v>5.0</v>
-      </c>
-      <c r="G171" t="s">
-        <v>463</v>
-      </c>
-      <c r="H171" t="s">
-        <v>464</v>
-      </c>
-      <c r="I171" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B172" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C172" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="E172" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="F172">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G172" t="s">
-        <v>222</v>
+        <v>376</v>
       </c>
       <c r="H172" t="s">
-        <v>273</v>
+        <v>449</v>
       </c>
       <c r="I172" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
+        <v>466</v>
+      </c>
+      <c r="B173" t="s">
         <v>467</v>
-      </c>
-      <c r="B173" t="s">
-        <v>468</v>
       </c>
       <c r="E173" t="s">
         <v>172</v>
@@ -6756,62 +6753,62 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>379</v>
+        <v>468</v>
       </c>
       <c r="B174" t="s">
-        <v>380</v>
-      </c>
-      <c r="C174" t="s">
-        <v>330</v>
+        <v>469</v>
       </c>
       <c r="E174" t="s">
-        <v>375</v>
+        <v>470</v>
       </c>
       <c r="F174">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G174" t="s">
-        <v>381</v>
+        <v>37</v>
       </c>
       <c r="H174" t="s">
-        <v>440</v>
+        <v>37</v>
       </c>
       <c r="I174" t="s">
-        <v>441</v>
+        <v>382</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B175" t="s">
-        <v>470</v>
+        <v>472</v>
+      </c>
+      <c r="C175" t="s">
+        <v>139</v>
       </c>
       <c r="E175" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F175">
         <v>1.0</v>
       </c>
       <c r="G175" t="s">
-        <v>37</v>
+        <v>334</v>
       </c>
       <c r="H175" t="s">
-        <v>37</v>
+        <v>334</v>
       </c>
       <c r="I175" t="s">
-        <v>387</v>
+        <v>474</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B176" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C176" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
       <c r="E176" t="s">
         <v>375</v>
@@ -6820,255 +6817,255 @@
         <v>2.0</v>
       </c>
       <c r="G176" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="H176" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="I176" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B177" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C177" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="E177" t="s">
-        <v>476</v>
+        <v>292</v>
       </c>
       <c r="F177">
         <v>1.0</v>
       </c>
       <c r="G177" t="s">
-        <v>334</v>
+        <v>37</v>
       </c>
       <c r="H177" t="s">
-        <v>334</v>
+        <v>37</v>
       </c>
       <c r="I177" t="s">
-        <v>477</v>
+        <v>294</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>478</v>
+        <v>373</v>
       </c>
       <c r="B178" t="s">
-        <v>479</v>
+        <v>374</v>
       </c>
       <c r="C178" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="E178" t="s">
         <v>375</v>
       </c>
       <c r="F178">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G178" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="H178" t="s">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I178" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
+        <v>479</v>
+      </c>
+      <c r="B179" t="s">
+        <v>480</v>
+      </c>
+      <c r="C179" t="s">
+        <v>258</v>
+      </c>
+      <c r="E179" t="s">
+        <v>375</v>
+      </c>
+      <c r="F179">
+        <v>1.0</v>
+      </c>
+      <c r="G179" t="s">
+        <v>385</v>
+      </c>
+      <c r="H179" t="s">
+        <v>385</v>
+      </c>
+      <c r="I179" t="s">
         <v>481</v>
-      </c>
-      <c r="B179" t="s">
-        <v>482</v>
-      </c>
-      <c r="C179" t="s">
-        <v>175</v>
-      </c>
-      <c r="E179" t="s">
-        <v>292</v>
-      </c>
-      <c r="F179">
-        <v>1.0</v>
-      </c>
-      <c r="G179" t="s">
-        <v>37</v>
-      </c>
-      <c r="H179" t="s">
-        <v>37</v>
-      </c>
-      <c r="I179" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>430</v>
+        <v>482</v>
       </c>
       <c r="B180" t="s">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="C180" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="E180" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="F180">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G180" t="s">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="H180" t="s">
-        <v>408</v>
+        <v>37</v>
       </c>
       <c r="I180" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>379</v>
+        <v>451</v>
       </c>
       <c r="B181" t="s">
-        <v>380</v>
+        <v>452</v>
       </c>
       <c r="C181" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="E181" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F181">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G181" t="s">
-        <v>381</v>
+        <v>222</v>
       </c>
       <c r="H181" t="s">
-        <v>440</v>
+        <v>335</v>
       </c>
       <c r="I181" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
+        <v>440</v>
+      </c>
+      <c r="B182" t="s">
+        <v>441</v>
+      </c>
+      <c r="C182" t="s">
+        <v>220</v>
+      </c>
+      <c r="E182" t="s">
+        <v>375</v>
+      </c>
+      <c r="F182">
+        <v>3.0</v>
+      </c>
+      <c r="G182" t="s">
+        <v>376</v>
+      </c>
+      <c r="H182" t="s">
+        <v>425</v>
+      </c>
+      <c r="I182" t="s">
         <v>484</v>
-      </c>
-      <c r="B182" t="s">
-        <v>485</v>
-      </c>
-      <c r="C182" t="s">
-        <v>184</v>
-      </c>
-      <c r="E182" t="s">
-        <v>476</v>
-      </c>
-      <c r="F182">
-        <v>1.0</v>
-      </c>
-      <c r="G182" t="s">
-        <v>37</v>
-      </c>
-      <c r="H182" t="s">
-        <v>37</v>
-      </c>
-      <c r="I182" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B183" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C183" t="s">
         <v>258</v>
       </c>
       <c r="E183" t="s">
-        <v>392</v>
+        <v>458</v>
       </c>
       <c r="F183">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G183" t="s">
-        <v>222</v>
+        <v>485</v>
       </c>
       <c r="H183" t="s">
-        <v>335</v>
+        <v>423</v>
       </c>
       <c r="I183" t="s">
-        <v>457</v>
+        <v>486</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>460</v>
+        <v>383</v>
       </c>
       <c r="B184" t="s">
-        <v>461</v>
+        <v>384</v>
       </c>
       <c r="C184" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="E184" t="s">
-        <v>462</v>
+        <v>375</v>
       </c>
       <c r="F184">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G184" t="s">
-        <v>486</v>
+        <v>385</v>
       </c>
       <c r="H184" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="I184" t="s">
-        <v>487</v>
+        <v>446</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="B185" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C185" t="s">
-        <v>330</v>
+        <v>220</v>
       </c>
       <c r="E185" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F185">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G185" t="s">
-        <v>376</v>
+        <v>222</v>
       </c>
       <c r="H185" t="s">
-        <v>408</v>
+        <v>273</v>
       </c>
       <c r="I185" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="B186" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="C186" t="s">
         <v>220</v>
@@ -7077,76 +7074,76 @@
         <v>392</v>
       </c>
       <c r="F186">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G186" t="s">
         <v>222</v>
       </c>
       <c r="H186" t="s">
-        <v>273</v>
+        <v>335</v>
       </c>
       <c r="I186" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="B187" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="C187" t="s">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="E187" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="F187">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G187" t="s">
-        <v>222</v>
+        <v>376</v>
       </c>
       <c r="H187" t="s">
-        <v>335</v>
+        <v>425</v>
       </c>
       <c r="I187" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B188" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C188" t="s">
         <v>300</v>
       </c>
       <c r="E188" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F188">
         <v>1.0</v>
       </c>
       <c r="G188" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H188" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I188" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
+        <v>447</v>
+      </c>
+      <c r="B189" t="s">
         <v>448</v>
-      </c>
-      <c r="B189" t="s">
-        <v>449</v>
       </c>
       <c r="C189" t="s">
         <v>220</v>
@@ -7155,24 +7152,24 @@
         <v>375</v>
       </c>
       <c r="F189">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G189" t="s">
         <v>376</v>
       </c>
       <c r="H189" t="s">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="I189" t="s">
-        <v>488</v>
+        <v>450</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B190" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="C190" t="s">
         <v>220</v>
@@ -7181,47 +7178,47 @@
         <v>375</v>
       </c>
       <c r="F190">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G190" t="s">
         <v>376</v>
       </c>
       <c r="H190" t="s">
-        <v>450</v>
+        <v>377</v>
       </c>
       <c r="I190" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
+        <v>488</v>
+      </c>
+      <c r="B191" t="s">
         <v>489</v>
       </c>
-      <c r="B191" t="s">
+      <c r="E191" t="s">
         <v>490</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191">
+        <v>1.0</v>
+      </c>
+      <c r="G191" t="s">
+        <v>37</v>
+      </c>
+      <c r="H191" t="s">
+        <v>37</v>
+      </c>
+      <c r="I191" t="s">
         <v>491</v>
-      </c>
-      <c r="F191">
-        <v>1.0</v>
-      </c>
-      <c r="G191" t="s">
-        <v>37</v>
-      </c>
-      <c r="H191" t="s">
-        <v>37</v>
-      </c>
-      <c r="I191" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B192" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C192" t="s">
         <v>220</v>
@@ -7233,21 +7230,21 @@
         <v>2.0</v>
       </c>
       <c r="G192" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H192" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="I192" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
+        <v>493</v>
+      </c>
+      <c r="B193" t="s">
         <v>494</v>
-      </c>
-      <c r="B193" t="s">
-        <v>495</v>
       </c>
       <c r="C193" t="s">
         <v>184</v>
@@ -7270,28 +7267,28 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B194" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C194" t="s">
         <v>139</v>
       </c>
       <c r="E194" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F194">
         <v>5.0</v>
       </c>
       <c r="G194" t="s">
+        <v>495</v>
+      </c>
+      <c r="H194" t="s">
         <v>496</v>
       </c>
-      <c r="H194" t="s">
-        <v>497</v>
-      </c>
       <c r="I194" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -7317,59 +7314,59 @@
         <v>37</v>
       </c>
       <c r="I195" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
+        <v>498</v>
+      </c>
+      <c r="B196" t="s">
         <v>499</v>
-      </c>
-      <c r="B196" t="s">
-        <v>500</v>
       </c>
       <c r="C196" t="s">
         <v>282</v>
       </c>
       <c r="E196" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F196">
         <v>2.0</v>
       </c>
       <c r="G196" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H196" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I196" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B197" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C197" t="s">
         <v>282</v>
       </c>
       <c r="E197" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F197">
         <v>2.0</v>
       </c>
       <c r="G197" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H197" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I197" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -7392,44 +7389,44 @@
         <v>376</v>
       </c>
       <c r="H198" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I198" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
+        <v>501</v>
+      </c>
+      <c r="B199" t="s">
         <v>502</v>
-      </c>
-      <c r="B199" t="s">
-        <v>503</v>
       </c>
       <c r="C199" t="s">
         <v>282</v>
       </c>
       <c r="E199" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F199">
         <v>1.0</v>
       </c>
       <c r="G199" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H199" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I199" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B200" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C200" t="s">
         <v>330</v>
@@ -7441,21 +7438,21 @@
         <v>3.0</v>
       </c>
       <c r="G200" t="s">
+        <v>504</v>
+      </c>
+      <c r="H200" t="s">
         <v>505</v>
       </c>
-      <c r="H200" t="s">
+      <c r="I200" t="s">
         <v>506</v>
-      </c>
-      <c r="I200" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
+        <v>507</v>
+      </c>
+      <c r="B201" t="s">
         <v>508</v>
-      </c>
-      <c r="B201" t="s">
-        <v>509</v>
       </c>
       <c r="C201" t="s">
         <v>258</v>
@@ -7464,50 +7461,50 @@
         <v>375</v>
       </c>
       <c r="F201">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G201" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H201" t="s">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="I201" t="s">
-        <v>274</v>
+        <v>492</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>430</v>
+        <v>509</v>
       </c>
       <c r="B202" t="s">
-        <v>431</v>
+        <v>510</v>
       </c>
       <c r="C202" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="E202" t="s">
         <v>375</v>
       </c>
       <c r="F202">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G202" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="H202" t="s">
-        <v>472</v>
+        <v>385</v>
       </c>
       <c r="I202" t="s">
-        <v>441</v>
+        <v>274</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B203" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C203" t="s">
         <v>258</v>
@@ -7519,65 +7516,65 @@
         <v>2.0</v>
       </c>
       <c r="G203" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H203" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="I203" t="s">
-        <v>493</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B204" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C204" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="E204" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="F204">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G204" t="s">
-        <v>381</v>
+        <v>37</v>
       </c>
       <c r="H204" t="s">
-        <v>440</v>
+        <v>37</v>
       </c>
       <c r="I204" t="s">
-        <v>441</v>
+        <v>503</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>514</v>
+        <v>440</v>
       </c>
       <c r="B205" t="s">
-        <v>515</v>
+        <v>441</v>
       </c>
       <c r="C205" t="s">
-        <v>184</v>
+        <v>282</v>
       </c>
       <c r="E205" t="s">
-        <v>476</v>
+        <v>375</v>
       </c>
       <c r="F205">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G205" t="s">
-        <v>37</v>
+        <v>376</v>
       </c>
       <c r="H205" t="s">
-        <v>37</v>
+        <v>477</v>
       </c>
       <c r="I205" t="s">
-        <v>504</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -7608,10 +7605,10 @@
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B207" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C207" t="s">
         <v>282</v>
@@ -7629,15 +7626,15 @@
         <v>273</v>
       </c>
       <c r="I207" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B208" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C208" t="s">
         <v>220</v>
@@ -7649,21 +7646,21 @@
         <v>2.0</v>
       </c>
       <c r="G208" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H208" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="I208" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="B209" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="C209" t="s">
         <v>330</v>
@@ -7672,27 +7669,27 @@
         <v>375</v>
       </c>
       <c r="F209">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G209" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="H209" t="s">
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="I209" t="s">
-        <v>378</v>
+        <v>492</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B210" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C210" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="E210" t="s">
         <v>375</v>
@@ -7701,53 +7698,53 @@
         <v>2.0</v>
       </c>
       <c r="G210" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H210" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="I210" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="B211" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="C211" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
       <c r="E211" t="s">
         <v>375</v>
       </c>
       <c r="F211">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G211" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="H211" t="s">
-        <v>440</v>
+        <v>377</v>
       </c>
       <c r="I211" t="s">
-        <v>493</v>
+        <v>378</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
+        <v>515</v>
+      </c>
+      <c r="B212" t="s">
         <v>516</v>
-      </c>
-      <c r="B212" t="s">
-        <v>517</v>
       </c>
       <c r="C212" t="s">
         <v>212</v>
       </c>
       <c r="E212" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F212">
         <v>4.0</v>
@@ -7759,47 +7756,47 @@
         <v>37</v>
       </c>
       <c r="I212" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
+        <v>498</v>
+      </c>
+      <c r="B213" t="s">
         <v>499</v>
-      </c>
-      <c r="B213" t="s">
-        <v>500</v>
       </c>
       <c r="C213" t="s">
         <v>330</v>
       </c>
       <c r="E213" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F213">
         <v>1.0</v>
       </c>
       <c r="G213" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H213" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I213" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
+        <v>513</v>
+      </c>
+      <c r="B214" t="s">
         <v>514</v>
-      </c>
-      <c r="B214" t="s">
-        <v>515</v>
       </c>
       <c r="C214" t="s">
         <v>212</v>
       </c>
       <c r="E214" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F214">
         <v>5.0</v>
@@ -7811,93 +7808,93 @@
         <v>37</v>
       </c>
       <c r="I214" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B215" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C215" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E215" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F215">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G215" t="s">
-        <v>381</v>
+        <v>222</v>
       </c>
       <c r="H215" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="I215" t="s">
-        <v>519</v>
+        <v>394</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B216" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C216" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="E216" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="F216">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G216" t="s">
-        <v>222</v>
+        <v>385</v>
       </c>
       <c r="H216" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="I216" t="s">
-        <v>394</v>
+        <v>518</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B217" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C217" t="s">
         <v>220</v>
       </c>
       <c r="E217" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F217">
         <v>4.0</v>
       </c>
       <c r="G217" t="s">
+        <v>519</v>
+      </c>
+      <c r="H217" t="s">
         <v>520</v>
       </c>
-      <c r="H217" t="s">
-        <v>521</v>
-      </c>
       <c r="I217" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
+        <v>511</v>
+      </c>
+      <c r="B218" t="s">
         <v>512</v>
-      </c>
-      <c r="B218" t="s">
-        <v>513</v>
       </c>
       <c r="C218" t="s">
         <v>330</v>
@@ -7909,148 +7906,148 @@
         <v>1.0</v>
       </c>
       <c r="G218" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H218" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I218" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>448</v>
+        <v>521</v>
       </c>
       <c r="B219" t="s">
-        <v>449</v>
-      </c>
-      <c r="C219" t="s">
-        <v>282</v>
+        <v>522</v>
       </c>
       <c r="E219" t="s">
-        <v>375</v>
+        <v>523</v>
       </c>
       <c r="F219">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G219" t="s">
-        <v>376</v>
+        <v>524</v>
       </c>
       <c r="H219" t="s">
-        <v>432</v>
+        <v>109</v>
       </c>
       <c r="I219" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>452</v>
+        <v>525</v>
       </c>
       <c r="B220" t="s">
-        <v>453</v>
+        <v>526</v>
       </c>
       <c r="C220" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="E220" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="F220">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G220" t="s">
-        <v>376</v>
+        <v>527</v>
       </c>
       <c r="H220" t="s">
-        <v>408</v>
+        <v>528</v>
       </c>
       <c r="I220" t="s">
-        <v>409</v>
+        <v>517</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="B221" t="s">
-        <v>523</v>
+        <v>530</v>
+      </c>
+      <c r="C221" t="s">
+        <v>212</v>
       </c>
       <c r="E221" t="s">
-        <v>524</v>
+        <v>473</v>
       </c>
       <c r="F221">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G221" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="H221" t="s">
-        <v>109</v>
+        <v>532</v>
       </c>
       <c r="I221" t="s">
-        <v>416</v>
+        <v>517</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>526</v>
+        <v>447</v>
       </c>
       <c r="B222" t="s">
-        <v>527</v>
+        <v>448</v>
       </c>
       <c r="C222" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="E222" t="s">
-        <v>476</v>
+        <v>375</v>
       </c>
       <c r="F222">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G222" t="s">
-        <v>528</v>
+        <v>376</v>
       </c>
       <c r="H222" t="s">
-        <v>529</v>
+        <v>425</v>
       </c>
       <c r="I222" t="s">
-        <v>518</v>
+        <v>426</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>530</v>
+        <v>463</v>
       </c>
       <c r="B223" t="s">
-        <v>531</v>
+        <v>464</v>
       </c>
       <c r="C223" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="E223" t="s">
-        <v>476</v>
+        <v>375</v>
       </c>
       <c r="F223">
         <v>4.0</v>
       </c>
       <c r="G223" t="s">
-        <v>532</v>
+        <v>376</v>
       </c>
       <c r="H223" t="s">
-        <v>533</v>
+        <v>442</v>
       </c>
       <c r="I223" t="s">
-        <v>518</v>
+        <v>387</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
+        <v>533</v>
+      </c>
+      <c r="B224" t="s">
         <v>534</v>
-      </c>
-      <c r="B224" t="s">
-        <v>535</v>
       </c>
       <c r="C224" t="s">
         <v>184</v>
@@ -8068,21 +8065,21 @@
         <v>37</v>
       </c>
       <c r="I224" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
+        <v>535</v>
+      </c>
+      <c r="B225" t="s">
         <v>536</v>
-      </c>
-      <c r="B225" t="s">
-        <v>537</v>
       </c>
       <c r="C225" t="s">
         <v>282</v>
       </c>
       <c r="E225" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F225">
         <v>4.0</v>
@@ -8094,21 +8091,21 @@
         <v>37</v>
       </c>
       <c r="I225" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
+        <v>539</v>
+      </c>
+      <c r="B226" t="s">
         <v>540</v>
-      </c>
-      <c r="B226" t="s">
-        <v>541</v>
       </c>
       <c r="C226" t="s">
         <v>175</v>
       </c>
       <c r="E226" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F226">
         <v>3.0</v>
@@ -8125,91 +8122,91 @@
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
+        <v>541</v>
+      </c>
+      <c r="B227" t="s">
         <v>542</v>
-      </c>
-      <c r="B227" t="s">
-        <v>543</v>
       </c>
       <c r="C227" t="s">
         <v>212</v>
       </c>
       <c r="E227" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F227">
         <v>8.0</v>
       </c>
       <c r="G227" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H227" t="s">
         <v>335</v>
       </c>
       <c r="I227" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
+        <v>498</v>
+      </c>
+      <c r="B228" t="s">
         <v>499</v>
-      </c>
-      <c r="B228" t="s">
-        <v>500</v>
       </c>
       <c r="C228" t="s">
         <v>258</v>
       </c>
       <c r="E228" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F228">
         <v>3.0</v>
       </c>
       <c r="G228" t="s">
+        <v>544</v>
+      </c>
+      <c r="H228" t="s">
         <v>545</v>
       </c>
-      <c r="H228" t="s">
+      <c r="I228" t="s">
         <v>546</v>
-      </c>
-      <c r="I228" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
+        <v>547</v>
+      </c>
+      <c r="B229" t="s">
         <v>548</v>
-      </c>
-      <c r="B229" t="s">
-        <v>549</v>
       </c>
       <c r="C229" t="s">
         <v>282</v>
       </c>
       <c r="E229" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F229">
         <v>3.0</v>
       </c>
       <c r="G229" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H229" t="s">
         <v>78</v>
       </c>
       <c r="I229" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>448</v>
+        <v>549</v>
       </c>
       <c r="B230" t="s">
-        <v>449</v>
+        <v>550</v>
       </c>
       <c r="C230" t="s">
-        <v>330</v>
+        <v>258</v>
       </c>
       <c r="E230" t="s">
         <v>375</v>
@@ -8221,128 +8218,128 @@
         <v>376</v>
       </c>
       <c r="H230" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I230" t="s">
-        <v>483</v>
+        <v>551</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>550</v>
+        <v>371</v>
       </c>
       <c r="B231" t="s">
-        <v>551</v>
+        <v>372</v>
       </c>
       <c r="C231" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="E231" t="s">
-        <v>375</v>
+        <v>236</v>
       </c>
       <c r="F231">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G231" t="s">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="H231" t="s">
-        <v>408</v>
+        <v>37</v>
       </c>
       <c r="I231" t="s">
-        <v>552</v>
+        <v>434</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>371</v>
+        <v>463</v>
       </c>
       <c r="B232" t="s">
-        <v>372</v>
+        <v>464</v>
       </c>
       <c r="C232" t="s">
-        <v>184</v>
+        <v>330</v>
       </c>
       <c r="E232" t="s">
-        <v>236</v>
+        <v>375</v>
       </c>
       <c r="F232">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G232" t="s">
-        <v>37</v>
+        <v>376</v>
       </c>
       <c r="H232" t="s">
-        <v>37</v>
+        <v>425</v>
       </c>
       <c r="I232" t="s">
-        <v>438</v>
+        <v>484</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
+        <v>552</v>
+      </c>
+      <c r="B233" t="s">
         <v>553</v>
-      </c>
-      <c r="B233" t="s">
-        <v>554</v>
       </c>
       <c r="C233" t="s">
         <v>212</v>
       </c>
       <c r="E233" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F233">
         <v>4.0</v>
       </c>
       <c r="G233" t="s">
+        <v>527</v>
+      </c>
+      <c r="H233" t="s">
         <v>528</v>
       </c>
-      <c r="H233" t="s">
-        <v>529</v>
-      </c>
       <c r="I233" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
+        <v>547</v>
+      </c>
+      <c r="B234" t="s">
         <v>548</v>
-      </c>
-      <c r="B234" t="s">
-        <v>549</v>
       </c>
       <c r="C234" t="s">
         <v>258</v>
       </c>
       <c r="E234" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F234">
         <v>5.0</v>
       </c>
       <c r="G234" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H234" t="s">
         <v>53</v>
       </c>
       <c r="I234" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
+        <v>515</v>
+      </c>
+      <c r="B235" t="s">
         <v>516</v>
-      </c>
-      <c r="B235" t="s">
-        <v>517</v>
       </c>
       <c r="C235" t="s">
         <v>184</v>
       </c>
       <c r="E235" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F235">
         <v>3.0</v>
@@ -8354,30 +8351,30 @@
         <v>37</v>
       </c>
       <c r="I235" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
+        <v>501</v>
+      </c>
+      <c r="B236" t="s">
         <v>502</v>
-      </c>
-      <c r="B236" t="s">
-        <v>503</v>
       </c>
       <c r="C236" t="s">
         <v>330</v>
       </c>
       <c r="E236" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F236">
         <v>2.0</v>
       </c>
       <c r="G236" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H236" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I236" t="s">
         <v>274</v>
@@ -8403,128 +8400,128 @@
         <v>376</v>
       </c>
       <c r="H237" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I237" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="B238" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C238" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="E238" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="F238">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G238" t="s">
-        <v>381</v>
+        <v>37</v>
       </c>
       <c r="H238" t="s">
-        <v>381</v>
+        <v>37</v>
       </c>
       <c r="I238" t="s">
-        <v>274</v>
+        <v>517</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>484</v>
+        <v>547</v>
       </c>
       <c r="B239" t="s">
+        <v>548</v>
+      </c>
+      <c r="C239" t="s">
+        <v>220</v>
+      </c>
+      <c r="E239" t="s">
+        <v>458</v>
+      </c>
+      <c r="F239">
+        <v>3.0</v>
+      </c>
+      <c r="G239" t="s">
         <v>485</v>
       </c>
-      <c r="C239" t="s">
-        <v>212</v>
-      </c>
-      <c r="E239" t="s">
-        <v>476</v>
-      </c>
-      <c r="F239">
-        <v>4.0</v>
-      </c>
-      <c r="G239" t="s">
-        <v>37</v>
-      </c>
       <c r="H239" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="I239" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>548</v>
+        <v>509</v>
       </c>
       <c r="B240" t="s">
-        <v>549</v>
+        <v>510</v>
       </c>
       <c r="C240" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="E240" t="s">
-        <v>462</v>
+        <v>375</v>
       </c>
       <c r="F240">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G240" t="s">
-        <v>486</v>
+        <v>385</v>
       </c>
       <c r="H240" t="s">
-        <v>78</v>
+        <v>385</v>
       </c>
       <c r="I240" t="s">
-        <v>507</v>
+        <v>274</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
+        <v>501</v>
+      </c>
+      <c r="B241" t="s">
         <v>502</v>
-      </c>
-      <c r="B241" t="s">
-        <v>503</v>
       </c>
       <c r="C241" t="s">
         <v>258</v>
       </c>
       <c r="E241" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F241">
         <v>5.0</v>
       </c>
       <c r="G241" t="s">
+        <v>555</v>
+      </c>
+      <c r="H241" t="s">
         <v>556</v>
       </c>
-      <c r="H241" t="s">
-        <v>557</v>
-      </c>
       <c r="I241" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
+        <v>539</v>
+      </c>
+      <c r="B242" t="s">
         <v>540</v>
-      </c>
-      <c r="B242" t="s">
-        <v>541</v>
       </c>
       <c r="C242" t="s">
         <v>212</v>
       </c>
       <c r="E242" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F242">
         <v>4.0</v>
@@ -8536,67 +8533,67 @@
         <v>37</v>
       </c>
       <c r="I242" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="B243" t="s">
-        <v>513</v>
+        <v>542</v>
       </c>
       <c r="C243" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="E243" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="F243">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G243" t="s">
-        <v>381</v>
+        <v>554</v>
       </c>
       <c r="H243" t="s">
-        <v>381</v>
+        <v>557</v>
       </c>
       <c r="I243" t="s">
-        <v>519</v>
+        <v>394</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>542</v>
+        <v>511</v>
       </c>
       <c r="B244" t="s">
-        <v>543</v>
+        <v>512</v>
       </c>
       <c r="C244" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="E244" t="s">
-        <v>476</v>
+        <v>375</v>
       </c>
       <c r="F244">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G244" t="s">
-        <v>555</v>
+        <v>385</v>
       </c>
       <c r="H244" t="s">
-        <v>558</v>
+        <v>385</v>
       </c>
       <c r="I244" t="s">
-        <v>394</v>
+        <v>518</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
+        <v>558</v>
+      </c>
+      <c r="B245" t="s">
         <v>559</v>
-      </c>
-      <c r="B245" t="s">
-        <v>560</v>
       </c>
       <c r="C245" t="s">
         <v>139</v>
@@ -8614,41 +8611,41 @@
         <v>37</v>
       </c>
       <c r="I245" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
+        <v>529</v>
+      </c>
+      <c r="B246" t="s">
         <v>530</v>
-      </c>
-      <c r="B246" t="s">
-        <v>531</v>
       </c>
       <c r="C246" t="s">
         <v>139</v>
       </c>
       <c r="E246" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F246">
         <v>5.0</v>
       </c>
       <c r="G246" t="s">
+        <v>560</v>
+      </c>
+      <c r="H246" t="s">
         <v>561</v>
       </c>
-      <c r="H246" t="s">
-        <v>562</v>
-      </c>
       <c r="I246" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
+        <v>562</v>
+      </c>
+      <c r="B247" t="s">
         <v>563</v>
-      </c>
-      <c r="B247" t="s">
-        <v>564</v>
       </c>
       <c r="C247" t="s">
         <v>258</v>
@@ -8663,24 +8660,24 @@
         <v>376</v>
       </c>
       <c r="H247" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I247" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
+        <v>552</v>
+      </c>
+      <c r="B248" t="s">
         <v>553</v>
-      </c>
-      <c r="B248" t="s">
-        <v>554</v>
       </c>
       <c r="C248" t="s">
         <v>139</v>
       </c>
       <c r="E248" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F248">
         <v>14.0</v>
@@ -8689,18 +8686,18 @@
         <v>230</v>
       </c>
       <c r="H248" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I248" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
+        <v>533</v>
+      </c>
+      <c r="B249" t="s">
         <v>534</v>
-      </c>
-      <c r="B249" t="s">
-        <v>535</v>
       </c>
       <c r="C249" t="s">
         <v>139</v>
@@ -8718,15 +8715,15 @@
         <v>37</v>
       </c>
       <c r="I249" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B250" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C250" t="s">
         <v>330</v>
@@ -8738,21 +8735,21 @@
         <v>1.0</v>
       </c>
       <c r="G250" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H250" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I250" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
+        <v>511</v>
+      </c>
+      <c r="B251" t="s">
         <v>512</v>
-      </c>
-      <c r="B251" t="s">
-        <v>513</v>
       </c>
       <c r="C251" t="s">
         <v>282</v>
@@ -8764,21 +8761,21 @@
         <v>1.0</v>
       </c>
       <c r="G251" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H251" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I251" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B252" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="C252" t="s">
         <v>220</v>
@@ -8787,24 +8784,24 @@
         <v>375</v>
       </c>
       <c r="F252">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G252" t="s">
         <v>376</v>
       </c>
       <c r="H252" t="s">
-        <v>376</v>
+        <v>477</v>
       </c>
       <c r="I252" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="B253" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="C253" t="s">
         <v>220</v>
@@ -8813,56 +8810,56 @@
         <v>375</v>
       </c>
       <c r="F253">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G253" t="s">
         <v>376</v>
       </c>
       <c r="H253" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="I253" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B254" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C254" t="s">
         <v>212</v>
       </c>
       <c r="E254" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F254">
         <v>1.0</v>
       </c>
       <c r="G254" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H254" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I254" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
+        <v>568</v>
+      </c>
+      <c r="B255" t="s">
         <v>569</v>
-      </c>
-      <c r="B255" t="s">
-        <v>570</v>
       </c>
       <c r="C255" t="s">
         <v>212</v>
       </c>
       <c r="E255" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F255">
         <v>4.0</v>
@@ -8874,67 +8871,67 @@
         <v>37</v>
       </c>
       <c r="I255" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
+        <v>513</v>
+      </c>
+      <c r="B256" t="s">
         <v>514</v>
-      </c>
-      <c r="B256" t="s">
-        <v>515</v>
       </c>
       <c r="C256" t="s">
         <v>139</v>
       </c>
       <c r="E256" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F256">
         <v>11.0</v>
       </c>
       <c r="G256" t="s">
+        <v>570</v>
+      </c>
+      <c r="H256" t="s">
         <v>571</v>
       </c>
-      <c r="H256" t="s">
+      <c r="I256" t="s">
         <v>572</v>
-      </c>
-      <c r="I256" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
+        <v>541</v>
+      </c>
+      <c r="B257" t="s">
         <v>542</v>
-      </c>
-      <c r="B257" t="s">
-        <v>543</v>
       </c>
       <c r="C257" t="s">
         <v>149</v>
       </c>
       <c r="E257" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F257">
         <v>13.0</v>
       </c>
       <c r="G257" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H257" t="s">
+        <v>573</v>
+      </c>
+      <c r="I257" t="s">
         <v>574</v>
-      </c>
-      <c r="I257" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B258" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C258" t="s">
         <v>300</v>
@@ -8949,21 +8946,21 @@
         <v>376</v>
       </c>
       <c r="H258" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I258" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
+        <v>575</v>
+      </c>
+      <c r="B259" t="s">
         <v>576</v>
       </c>
-      <c r="B259" t="s">
-        <v>577</v>
-      </c>
       <c r="C259" t="s">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="E259" t="s">
         <v>375</v>
@@ -8975,18 +8972,18 @@
         <v>376</v>
       </c>
       <c r="H259" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I259" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
+        <v>577</v>
+      </c>
+      <c r="B260" t="s">
         <v>578</v>
-      </c>
-      <c r="B260" t="s">
-        <v>579</v>
       </c>
       <c r="C260" t="s">
         <v>258</v>
@@ -9001,21 +8998,21 @@
         <v>376</v>
       </c>
       <c r="H260" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I260" t="s">
-        <v>441</v>
+        <v>564</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B261" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C261" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="E261" t="s">
         <v>375</v>
@@ -9027,79 +9024,79 @@
         <v>376</v>
       </c>
       <c r="H261" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I261" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
+        <v>513</v>
+      </c>
+      <c r="B262" t="s">
+        <v>514</v>
+      </c>
+      <c r="C262" t="s">
+        <v>149</v>
+      </c>
+      <c r="E262" t="s">
+        <v>473</v>
+      </c>
+      <c r="F262">
+        <v>3.0</v>
+      </c>
+      <c r="G262" t="s">
+        <v>579</v>
+      </c>
+      <c r="H262" t="s">
         <v>580</v>
       </c>
-      <c r="B262" t="s">
-        <v>581</v>
-      </c>
-      <c r="C262" t="s">
-        <v>258</v>
-      </c>
-      <c r="E262" t="s">
-        <v>375</v>
-      </c>
-      <c r="F262">
-        <v>2.0</v>
-      </c>
-      <c r="G262" t="s">
-        <v>376</v>
-      </c>
-      <c r="H262" t="s">
-        <v>472</v>
-      </c>
       <c r="I262" t="s">
-        <v>565</v>
+        <v>394</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>514</v>
+        <v>581</v>
       </c>
       <c r="B263" t="s">
-        <v>515</v>
+        <v>582</v>
       </c>
       <c r="C263" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="E263" t="s">
-        <v>476</v>
+        <v>236</v>
       </c>
       <c r="F263">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G263" t="s">
-        <v>582</v>
+        <v>37</v>
       </c>
       <c r="H263" t="s">
-        <v>583</v>
+        <v>37</v>
       </c>
       <c r="I263" t="s">
-        <v>394</v>
+        <v>434</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>584</v>
+        <v>539</v>
       </c>
       <c r="B264" t="s">
-        <v>585</v>
+        <v>540</v>
       </c>
       <c r="C264" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E264" t="s">
-        <v>236</v>
+        <v>473</v>
       </c>
       <c r="F264">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G264" t="s">
         <v>37</v>
@@ -9108,56 +9105,56 @@
         <v>37</v>
       </c>
       <c r="I264" t="s">
-        <v>438</v>
+        <v>478</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>540</v>
+        <v>583</v>
       </c>
       <c r="B265" t="s">
-        <v>541</v>
+        <v>584</v>
       </c>
       <c r="C265" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="E265" t="s">
-        <v>476</v>
+        <v>375</v>
       </c>
       <c r="F265">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G265" t="s">
-        <v>37</v>
+        <v>376</v>
       </c>
       <c r="H265" t="s">
-        <v>37</v>
+        <v>477</v>
       </c>
       <c r="I265" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
+        <v>552</v>
+      </c>
+      <c r="B266" t="s">
         <v>553</v>
-      </c>
-      <c r="B266" t="s">
-        <v>554</v>
       </c>
       <c r="C266" t="s">
         <v>175</v>
       </c>
       <c r="E266" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F266">
         <v>3.0</v>
       </c>
       <c r="G266" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H266" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I266" t="s">
         <v>394</v>
@@ -9191,10 +9188,10 @@
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
+        <v>533</v>
+      </c>
+      <c r="B268" t="s">
         <v>534</v>
-      </c>
-      <c r="B268" t="s">
-        <v>535</v>
       </c>
       <c r="C268" t="s">
         <v>149</v>
@@ -9212,21 +9209,21 @@
         <v>37</v>
       </c>
       <c r="I268" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
+        <v>541</v>
+      </c>
+      <c r="B269" t="s">
         <v>542</v>
-      </c>
-      <c r="B269" t="s">
-        <v>543</v>
       </c>
       <c r="C269" t="s">
         <v>175</v>
       </c>
       <c r="E269" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F269">
         <v>5.0</v>
@@ -9238,122 +9235,122 @@
         <v>37</v>
       </c>
       <c r="I269" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
+        <v>541</v>
+      </c>
+      <c r="B270" t="s">
         <v>542</v>
-      </c>
-      <c r="B270" t="s">
-        <v>543</v>
       </c>
       <c r="C270" t="s">
         <v>139</v>
       </c>
       <c r="E270" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F270">
         <v>14.0</v>
       </c>
       <c r="G270" t="s">
+        <v>587</v>
+      </c>
+      <c r="H270" t="s">
         <v>588</v>
       </c>
-      <c r="H270" t="s">
-        <v>589</v>
-      </c>
       <c r="I270" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
+        <v>525</v>
+      </c>
+      <c r="B271" t="s">
         <v>526</v>
-      </c>
-      <c r="B271" t="s">
-        <v>527</v>
       </c>
       <c r="C271" t="s">
         <v>139</v>
       </c>
       <c r="E271" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F271">
         <v>4.0</v>
       </c>
       <c r="G271" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H271" t="s">
         <v>129</v>
       </c>
       <c r="I271" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>591</v>
+        <v>562</v>
       </c>
       <c r="B272" t="s">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="C272" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="E272" t="s">
         <v>375</v>
       </c>
       <c r="F272">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G272" t="s">
         <v>376</v>
       </c>
       <c r="H272" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="I272" t="s">
-        <v>493</v>
+        <v>567</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>448</v>
+        <v>590</v>
       </c>
       <c r="B273" t="s">
-        <v>449</v>
+        <v>591</v>
       </c>
       <c r="C273" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="E273" t="s">
         <v>375</v>
       </c>
       <c r="F273">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G273" t="s">
         <v>376</v>
       </c>
       <c r="H273" t="s">
-        <v>376</v>
+        <v>477</v>
       </c>
       <c r="I273" t="s">
-        <v>519</v>
+        <v>492</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>563</v>
+        <v>463</v>
       </c>
       <c r="B274" t="s">
-        <v>564</v>
+        <v>464</v>
       </c>
       <c r="C274" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="E274" t="s">
         <v>375</v>
@@ -9368,7 +9365,7 @@
         <v>376</v>
       </c>
       <c r="I274" t="s">
-        <v>568</v>
+        <v>518</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -9399,10 +9396,10 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
+        <v>493</v>
+      </c>
+      <c r="B276" t="s">
         <v>494</v>
-      </c>
-      <c r="B276" t="s">
-        <v>495</v>
       </c>
       <c r="C276" t="s">
         <v>212</v>
@@ -9425,10 +9422,10 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
+        <v>558</v>
+      </c>
+      <c r="B277" t="s">
         <v>559</v>
-      </c>
-      <c r="B277" t="s">
-        <v>560</v>
       </c>
       <c r="C277" t="s">
         <v>149</v>
@@ -9451,36 +9448,36 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
+        <v>552</v>
+      </c>
+      <c r="B278" t="s">
         <v>553</v>
-      </c>
-      <c r="B278" t="s">
-        <v>554</v>
       </c>
       <c r="C278" t="s">
         <v>149</v>
       </c>
       <c r="E278" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F278">
         <v>5.0</v>
       </c>
       <c r="G278" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H278" t="s">
         <v>320</v>
       </c>
       <c r="I278" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
+        <v>533</v>
+      </c>
+      <c r="B279" t="s">
         <v>534</v>
-      </c>
-      <c r="B279" t="s">
-        <v>535</v>
       </c>
       <c r="C279" t="s">
         <v>175</v>
@@ -9503,10 +9500,10 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
+        <v>549</v>
+      </c>
+      <c r="B280" t="s">
         <v>550</v>
-      </c>
-      <c r="B280" t="s">
-        <v>551</v>
       </c>
       <c r="C280" t="s">
         <v>330</v>
@@ -9524,15 +9521,15 @@
         <v>376</v>
       </c>
       <c r="I280" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
+        <v>549</v>
+      </c>
+      <c r="B281" t="s">
         <v>550</v>
-      </c>
-      <c r="B281" t="s">
-        <v>551</v>
       </c>
       <c r="C281" t="s">
         <v>282</v>
@@ -9550,18 +9547,18 @@
         <v>376</v>
       </c>
       <c r="I281" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B282" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C282" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="E282" t="s">
         <v>375</v>
@@ -9576,18 +9573,18 @@
         <v>376</v>
       </c>
       <c r="I282" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B283" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C283" t="s">
-        <v>282</v>
+        <v>220</v>
       </c>
       <c r="E283" t="s">
         <v>375</v>
@@ -9602,15 +9599,15 @@
         <v>376</v>
       </c>
       <c r="I283" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
+        <v>558</v>
+      </c>
+      <c r="B284" t="s">
         <v>559</v>
-      </c>
-      <c r="B284" t="s">
-        <v>560</v>
       </c>
       <c r="C284" t="s">
         <v>212</v>
@@ -9628,7 +9625,7 @@
         <v>37</v>
       </c>
       <c r="I284" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="285" spans="1:9">
@@ -9659,10 +9656,10 @@
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
+        <v>592</v>
+      </c>
+      <c r="B286" t="s">
         <v>593</v>
-      </c>
-      <c r="B286" t="s">
-        <v>594</v>
       </c>
       <c r="C286" t="s">
         <v>184</v>
@@ -9706,15 +9703,15 @@
         <v>37</v>
       </c>
       <c r="I287" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
+        <v>590</v>
+      </c>
+      <c r="B288" t="s">
         <v>591</v>
-      </c>
-      <c r="B288" t="s">
-        <v>592</v>
       </c>
       <c r="C288" t="s">
         <v>282</v>
@@ -9732,18 +9729,18 @@
         <v>376</v>
       </c>
       <c r="I288" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="B289" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="C289" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="E289" t="s">
         <v>375</v>
@@ -9758,18 +9755,18 @@
         <v>376</v>
       </c>
       <c r="I289" t="s">
-        <v>519</v>
+        <v>567</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B290" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="C290" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E290" t="s">
         <v>375</v>
@@ -9784,15 +9781,15 @@
         <v>376</v>
       </c>
       <c r="I290" t="s">
-        <v>568</v>
+        <v>518</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
+        <v>592</v>
+      </c>
+      <c r="B291" t="s">
         <v>593</v>
-      </c>
-      <c r="B291" t="s">
-        <v>594</v>
       </c>
       <c r="C291" t="s">
         <v>149</v>
@@ -9836,21 +9833,21 @@
         <v>37</v>
       </c>
       <c r="I292" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
+        <v>539</v>
+      </c>
+      <c r="B293" t="s">
         <v>540</v>
-      </c>
-      <c r="B293" t="s">
-        <v>541</v>
       </c>
       <c r="C293" t="s">
         <v>149</v>
       </c>
       <c r="E293" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F293">
         <v>8.0</v>
@@ -9862,21 +9859,21 @@
         <v>37</v>
       </c>
       <c r="I293" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
+        <v>594</v>
+      </c>
+      <c r="B294" t="s">
         <v>595</v>
-      </c>
-      <c r="B294" t="s">
-        <v>596</v>
       </c>
       <c r="C294" t="s">
         <v>175</v>
       </c>
       <c r="E294" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F294">
         <v>1.0</v>
@@ -9893,16 +9890,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
+        <v>597</v>
+      </c>
+      <c r="B295" t="s">
         <v>598</v>
-      </c>
-      <c r="B295" t="s">
-        <v>599</v>
       </c>
       <c r="C295" t="s">
         <v>184</v>
       </c>
       <c r="E295" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F295">
         <v>1.0</v>
@@ -9919,13 +9916,13 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
+        <v>600</v>
+      </c>
+      <c r="B296" t="s">
         <v>601</v>
       </c>
-      <c r="B296" t="s">
+      <c r="E296" t="s">
         <v>602</v>
-      </c>
-      <c r="E296" t="s">
-        <v>603</v>
       </c>
       <c r="F296">
         <v>2.0</v>
@@ -9937,15 +9934,15 @@
         <v>37</v>
       </c>
       <c r="I296" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
+        <v>604</v>
+      </c>
+      <c r="B297" t="s">
         <v>605</v>
-      </c>
-      <c r="B297" t="s">
-        <v>606</v>
       </c>
       <c r="E297" t="s">
         <v>108</v>
@@ -9965,13 +9962,13 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
+        <v>606</v>
+      </c>
+      <c r="B298" t="s">
         <v>607</v>
       </c>
-      <c r="B298" t="s">
-        <v>608</v>
-      </c>
       <c r="E298" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F298">
         <v>1.0</v>
@@ -9983,12 +9980,12 @@
         <v>37</v>
       </c>
       <c r="I298" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B299" t="s">
         <v>107</v>
@@ -10011,10 +10008,10 @@
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
+        <v>609</v>
+      </c>
+      <c r="B300" t="s">
         <v>610</v>
-      </c>
-      <c r="B300" t="s">
-        <v>611</v>
       </c>
       <c r="C300" t="s">
         <v>149</v>
@@ -10037,10 +10034,10 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
+        <v>609</v>
+      </c>
+      <c r="B301" t="s">
         <v>610</v>
-      </c>
-      <c r="B301" t="s">
-        <v>611</v>
       </c>
       <c r="C301" t="s">
         <v>139</v>
@@ -10063,10 +10060,10 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
+        <v>493</v>
+      </c>
+      <c r="B302" t="s">
         <v>494</v>
-      </c>
-      <c r="B302" t="s">
-        <v>495</v>
       </c>
       <c r="C302" t="s">
         <v>175</v>
@@ -10089,36 +10086,36 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
+        <v>611</v>
+      </c>
+      <c r="B303" t="s">
         <v>612</v>
-      </c>
-      <c r="B303" t="s">
-        <v>613</v>
       </c>
       <c r="C303" t="s">
         <v>175</v>
       </c>
       <c r="E303" t="s">
+        <v>613</v>
+      </c>
+      <c r="F303">
+        <v>1.0</v>
+      </c>
+      <c r="G303" t="s">
+        <v>37</v>
+      </c>
+      <c r="H303" t="s">
+        <v>37</v>
+      </c>
+      <c r="I303" t="s">
         <v>614</v>
-      </c>
-      <c r="F303">
-        <v>1.0</v>
-      </c>
-      <c r="G303" t="s">
-        <v>37</v>
-      </c>
-      <c r="H303" t="s">
-        <v>37</v>
-      </c>
-      <c r="I303" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B304" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C304" t="s">
         <v>175</v>
@@ -10141,10 +10138,10 @@
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
+        <v>558</v>
+      </c>
+      <c r="B305" t="s">
         <v>559</v>
-      </c>
-      <c r="B305" t="s">
-        <v>560</v>
       </c>
       <c r="C305" t="s">
         <v>175</v>
@@ -10162,7 +10159,7 @@
         <v>37</v>
       </c>
       <c r="I305" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="306" spans="1:9">
@@ -10188,7 +10185,7 @@
         <v>37</v>
       </c>
       <c r="I306" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -10219,10 +10216,10 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
+        <v>533</v>
+      </c>
+      <c r="B308" t="s">
         <v>534</v>
-      </c>
-      <c r="B308" t="s">
-        <v>535</v>
       </c>
       <c r="C308" t="s">
         <v>212</v>
@@ -10245,16 +10242,16 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
+        <v>539</v>
+      </c>
+      <c r="B309" t="s">
         <v>540</v>
-      </c>
-      <c r="B309" t="s">
-        <v>541</v>
       </c>
       <c r="C309" t="s">
         <v>139</v>
       </c>
       <c r="E309" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F309">
         <v>9.0</v>
@@ -10266,21 +10263,21 @@
         <v>37</v>
       </c>
       <c r="I309" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
+        <v>515</v>
+      </c>
+      <c r="B310" t="s">
         <v>516</v>
-      </c>
-      <c r="B310" t="s">
-        <v>517</v>
       </c>
       <c r="C310" t="s">
         <v>149</v>
       </c>
       <c r="E310" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F310">
         <v>4.0</v>
@@ -10292,21 +10289,21 @@
         <v>37</v>
       </c>
       <c r="I310" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
+        <v>513</v>
+      </c>
+      <c r="B311" t="s">
         <v>514</v>
-      </c>
-      <c r="B311" t="s">
-        <v>515</v>
       </c>
       <c r="C311" t="s">
         <v>175</v>
       </c>
       <c r="E311" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F311">
         <v>3.0</v>
@@ -10323,16 +10320,16 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
+        <v>568</v>
+      </c>
+      <c r="B312" t="s">
         <v>569</v>
-      </c>
-      <c r="B312" t="s">
-        <v>570</v>
       </c>
       <c r="C312" t="s">
         <v>139</v>
       </c>
       <c r="E312" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F312">
         <v>1.0</v>
@@ -10344,18 +10341,18 @@
         <v>37</v>
       </c>
       <c r="I312" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
+        <v>616</v>
+      </c>
+      <c r="B313" t="s">
         <v>617</v>
       </c>
-      <c r="B313" t="s">
-        <v>618</v>
-      </c>
       <c r="E313" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F313">
         <v>2.0</v>
@@ -10372,13 +10369,13 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
+        <v>618</v>
+      </c>
+      <c r="B314" t="s">
         <v>619</v>
       </c>
-      <c r="B314" t="s">
-        <v>620</v>
-      </c>
       <c r="E314" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F314">
         <v>1.0</v>
@@ -10395,13 +10392,13 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
+        <v>620</v>
+      </c>
+      <c r="B315" t="s">
         <v>621</v>
       </c>
-      <c r="B315" t="s">
-        <v>622</v>
-      </c>
       <c r="E315" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F315">
         <v>2.0</v>
@@ -10418,13 +10415,13 @@
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
+        <v>622</v>
+      </c>
+      <c r="B316" t="s">
         <v>623</v>
       </c>
-      <c r="B316" t="s">
-        <v>624</v>
-      </c>
       <c r="E316" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F316">
         <v>1.0</v>
@@ -10441,13 +10438,13 @@
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
+        <v>624</v>
+      </c>
+      <c r="B317" t="s">
         <v>625</v>
       </c>
-      <c r="B317" t="s">
-        <v>626</v>
-      </c>
       <c r="E317" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F317">
         <v>1.0</v>
@@ -10464,13 +10461,13 @@
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
+        <v>626</v>
+      </c>
+      <c r="B318" t="s">
         <v>627</v>
       </c>
-      <c r="B318" t="s">
-        <v>628</v>
-      </c>
       <c r="E318" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F318">
         <v>2.0</v>
@@ -10482,18 +10479,18 @@
         <v>37</v>
       </c>
       <c r="I318" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
+        <v>629</v>
+      </c>
+      <c r="B319" t="s">
         <v>630</v>
       </c>
-      <c r="B319" t="s">
-        <v>631</v>
-      </c>
       <c r="E319" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F319">
         <v>1.0</v>
@@ -10510,39 +10507,39 @@
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
+        <v>631</v>
+      </c>
+      <c r="B320" t="s">
         <v>632</v>
       </c>
-      <c r="B320" t="s">
-        <v>633</v>
-      </c>
       <c r="E320" t="s">
+        <v>490</v>
+      </c>
+      <c r="F320">
+        <v>1.0</v>
+      </c>
+      <c r="G320" t="s">
+        <v>37</v>
+      </c>
+      <c r="H320" t="s">
+        <v>37</v>
+      </c>
+      <c r="I320" t="s">
         <v>491</v>
-      </c>
-      <c r="F320">
-        <v>1.0</v>
-      </c>
-      <c r="G320" t="s">
-        <v>37</v>
-      </c>
-      <c r="H320" t="s">
-        <v>37</v>
-      </c>
-      <c r="I320" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
+        <v>535</v>
+      </c>
+      <c r="B321" t="s">
         <v>536</v>
-      </c>
-      <c r="B321" t="s">
-        <v>537</v>
       </c>
       <c r="C321" t="s">
         <v>330</v>
       </c>
       <c r="E321" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F321">
         <v>3.0</v>
@@ -10554,21 +10551,21 @@
         <v>37</v>
       </c>
       <c r="I321" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
+        <v>535</v>
+      </c>
+      <c r="B322" t="s">
         <v>536</v>
-      </c>
-      <c r="B322" t="s">
-        <v>537</v>
       </c>
       <c r="C322" t="s">
         <v>258</v>
       </c>
       <c r="E322" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F322">
         <v>7.0</v>
@@ -10580,21 +10577,21 @@
         <v>37</v>
       </c>
       <c r="I322" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
+        <v>535</v>
+      </c>
+      <c r="B323" t="s">
         <v>536</v>
-      </c>
-      <c r="B323" t="s">
-        <v>537</v>
       </c>
       <c r="C323" t="s">
         <v>220</v>
       </c>
       <c r="E323" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F323">
         <v>4.0</v>
@@ -10606,21 +10603,21 @@
         <v>37</v>
       </c>
       <c r="I323" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
+        <v>635</v>
+      </c>
+      <c r="B324" t="s">
         <v>636</v>
-      </c>
-      <c r="B324" t="s">
-        <v>637</v>
       </c>
       <c r="C324" t="s">
         <v>330</v>
       </c>
       <c r="E324" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F324">
         <v>4.0</v>
@@ -10632,21 +10629,21 @@
         <v>37</v>
       </c>
       <c r="I324" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
+        <v>635</v>
+      </c>
+      <c r="B325" t="s">
         <v>636</v>
-      </c>
-      <c r="B325" t="s">
-        <v>637</v>
       </c>
       <c r="C325" t="s">
         <v>258</v>
       </c>
       <c r="E325" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F325">
         <v>6.0</v>
@@ -10658,21 +10655,21 @@
         <v>37</v>
       </c>
       <c r="I325" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="326" spans="1:9">
       <c r="A326" t="s">
+        <v>635</v>
+      </c>
+      <c r="B326" t="s">
         <v>636</v>
-      </c>
-      <c r="B326" t="s">
-        <v>637</v>
       </c>
       <c r="C326" t="s">
         <v>220</v>
       </c>
       <c r="E326" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F326">
         <v>4.0</v>
@@ -10684,21 +10681,21 @@
         <v>37</v>
       </c>
       <c r="I326" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
+        <v>635</v>
+      </c>
+      <c r="B327" t="s">
         <v>636</v>
-      </c>
-      <c r="B327" t="s">
-        <v>637</v>
       </c>
       <c r="C327" t="s">
         <v>282</v>
       </c>
       <c r="E327" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F327">
         <v>4.0</v>
@@ -10710,21 +10707,21 @@
         <v>37</v>
       </c>
       <c r="I327" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="328" spans="1:9">
       <c r="A328" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B328" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C328" t="s">
         <v>300</v>
       </c>
       <c r="E328" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F328">
         <v>1.0</v>
@@ -10736,21 +10733,21 @@
         <v>37</v>
       </c>
       <c r="I328" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
+        <v>640</v>
+      </c>
+      <c r="B329" t="s">
         <v>641</v>
-      </c>
-      <c r="B329" t="s">
-        <v>642</v>
       </c>
       <c r="C329" t="s">
         <v>258</v>
       </c>
       <c r="E329" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F329">
         <v>5.0</v>
@@ -10762,21 +10759,21 @@
         <v>37</v>
       </c>
       <c r="I329" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="330" spans="1:9">
       <c r="A330" t="s">
+        <v>640</v>
+      </c>
+      <c r="B330" t="s">
         <v>641</v>
-      </c>
-      <c r="B330" t="s">
-        <v>642</v>
       </c>
       <c r="C330" t="s">
         <v>220</v>
       </c>
       <c r="E330" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F330">
         <v>5.0</v>
@@ -10788,21 +10785,21 @@
         <v>37</v>
       </c>
       <c r="I330" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
+        <v>640</v>
+      </c>
+      <c r="B331" t="s">
         <v>641</v>
-      </c>
-      <c r="B331" t="s">
-        <v>642</v>
       </c>
       <c r="C331" t="s">
         <v>282</v>
       </c>
       <c r="E331" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F331">
         <v>5.0</v>
@@ -10814,21 +10811,21 @@
         <v>37</v>
       </c>
       <c r="I331" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
+        <v>640</v>
+      </c>
+      <c r="B332" t="s">
         <v>641</v>
-      </c>
-      <c r="B332" t="s">
-        <v>642</v>
       </c>
       <c r="C332" t="s">
         <v>300</v>
       </c>
       <c r="E332" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F332">
         <v>2.0</v>
@@ -10840,21 +10837,21 @@
         <v>37</v>
       </c>
       <c r="I332" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="333" spans="1:9">
       <c r="A333" t="s">
+        <v>644</v>
+      </c>
+      <c r="B333" t="s">
         <v>645</v>
-      </c>
-      <c r="B333" t="s">
-        <v>646</v>
       </c>
       <c r="C333" t="s">
         <v>330</v>
       </c>
       <c r="E333" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F333">
         <v>1.0</v>
@@ -10866,21 +10863,21 @@
         <v>37</v>
       </c>
       <c r="I333" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="334" spans="1:9">
       <c r="A334" t="s">
+        <v>644</v>
+      </c>
+      <c r="B334" t="s">
         <v>645</v>
-      </c>
-      <c r="B334" t="s">
-        <v>646</v>
       </c>
       <c r="C334" t="s">
         <v>220</v>
       </c>
       <c r="E334" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F334">
         <v>3.0</v>
@@ -10892,21 +10889,21 @@
         <v>37</v>
       </c>
       <c r="I334" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="335" spans="1:9">
       <c r="A335" t="s">
+        <v>644</v>
+      </c>
+      <c r="B335" t="s">
         <v>645</v>
-      </c>
-      <c r="B335" t="s">
-        <v>646</v>
       </c>
       <c r="C335" t="s">
         <v>300</v>
       </c>
       <c r="E335" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F335">
         <v>1.0</v>
@@ -10918,21 +10915,21 @@
         <v>37</v>
       </c>
       <c r="I335" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="336" spans="1:9">
       <c r="A336" t="s">
+        <v>646</v>
+      </c>
+      <c r="B336" t="s">
         <v>647</v>
-      </c>
-      <c r="B336" t="s">
-        <v>648</v>
       </c>
       <c r="C336" t="s">
         <v>330</v>
       </c>
       <c r="E336" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F336">
         <v>2.0</v>
@@ -10944,21 +10941,21 @@
         <v>37</v>
       </c>
       <c r="I336" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="337" spans="1:9">
       <c r="A337" t="s">
+        <v>646</v>
+      </c>
+      <c r="B337" t="s">
         <v>647</v>
-      </c>
-      <c r="B337" t="s">
-        <v>648</v>
       </c>
       <c r="C337" t="s">
         <v>258</v>
       </c>
       <c r="E337" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F337">
         <v>3.0</v>
@@ -10970,21 +10967,21 @@
         <v>37</v>
       </c>
       <c r="I337" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="338" spans="1:9">
       <c r="A338" t="s">
+        <v>646</v>
+      </c>
+      <c r="B338" t="s">
         <v>647</v>
-      </c>
-      <c r="B338" t="s">
-        <v>648</v>
       </c>
       <c r="C338" t="s">
         <v>220</v>
       </c>
       <c r="E338" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F338">
         <v>3.0</v>
@@ -10996,21 +10993,21 @@
         <v>37</v>
       </c>
       <c r="I338" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="339" spans="1:9">
       <c r="A339" t="s">
+        <v>646</v>
+      </c>
+      <c r="B339" t="s">
         <v>647</v>
-      </c>
-      <c r="B339" t="s">
-        <v>648</v>
       </c>
       <c r="C339" t="s">
         <v>282</v>
       </c>
       <c r="E339" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F339">
         <v>2.0</v>
@@ -11022,21 +11019,21 @@
         <v>37</v>
       </c>
       <c r="I339" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="340" spans="1:9">
       <c r="A340" t="s">
+        <v>649</v>
+      </c>
+      <c r="B340" t="s">
         <v>650</v>
-      </c>
-      <c r="B340" t="s">
-        <v>651</v>
       </c>
       <c r="C340" t="s">
         <v>330</v>
       </c>
       <c r="E340" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F340">
         <v>2.0</v>
@@ -11048,21 +11045,21 @@
         <v>37</v>
       </c>
       <c r="I340" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="341" spans="1:9">
       <c r="A341" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B341" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C341" t="s">
         <v>258</v>
       </c>
       <c r="E341" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F341">
         <v>4.0</v>
@@ -11074,21 +11071,21 @@
         <v>37</v>
       </c>
       <c r="I341" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="342" spans="1:9">
       <c r="A342" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B342" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C342" t="s">
         <v>220</v>
       </c>
       <c r="E342" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F342">
         <v>3.0</v>
@@ -11100,21 +11097,21 @@
         <v>37</v>
       </c>
       <c r="I342" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="343" spans="1:9">
       <c r="A343" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B343" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C343" t="s">
         <v>282</v>
       </c>
       <c r="E343" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F343">
         <v>2.0</v>
@@ -11126,21 +11123,21 @@
         <v>37</v>
       </c>
       <c r="I343" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="344" spans="1:9">
       <c r="A344" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B344" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C344" t="s">
         <v>300</v>
       </c>
       <c r="E344" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F344">
         <v>1.0</v>
@@ -11157,16 +11154,16 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" t="s">
+        <v>653</v>
+      </c>
+      <c r="B345" t="s">
         <v>654</v>
-      </c>
-      <c r="B345" t="s">
-        <v>655</v>
       </c>
       <c r="C345" t="s">
         <v>330</v>
       </c>
       <c r="E345" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F345">
         <v>2.0</v>
@@ -11178,21 +11175,21 @@
         <v>37</v>
       </c>
       <c r="I345" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="346" spans="1:9">
       <c r="A346" t="s">
+        <v>653</v>
+      </c>
+      <c r="B346" t="s">
         <v>654</v>
-      </c>
-      <c r="B346" t="s">
-        <v>655</v>
       </c>
       <c r="C346" t="s">
         <v>258</v>
       </c>
       <c r="E346" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F346">
         <v>1.0</v>
@@ -11204,21 +11201,21 @@
         <v>37</v>
       </c>
       <c r="I346" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="347" spans="1:9">
       <c r="A347" t="s">
+        <v>653</v>
+      </c>
+      <c r="B347" t="s">
         <v>654</v>
-      </c>
-      <c r="B347" t="s">
-        <v>655</v>
       </c>
       <c r="C347" t="s">
         <v>220</v>
       </c>
       <c r="E347" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F347">
         <v>3.0</v>
@@ -11230,21 +11227,21 @@
         <v>37</v>
       </c>
       <c r="I347" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="348" spans="1:9">
       <c r="A348" t="s">
+        <v>653</v>
+      </c>
+      <c r="B348" t="s">
         <v>654</v>
-      </c>
-      <c r="B348" t="s">
-        <v>655</v>
       </c>
       <c r="C348" t="s">
         <v>282</v>
       </c>
       <c r="E348" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F348">
         <v>1.0</v>
@@ -11256,21 +11253,21 @@
         <v>37</v>
       </c>
       <c r="I348" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="349" spans="1:9">
       <c r="A349" t="s">
+        <v>657</v>
+      </c>
+      <c r="B349" t="s">
         <v>658</v>
-      </c>
-      <c r="B349" t="s">
-        <v>659</v>
       </c>
       <c r="C349" t="s">
         <v>258</v>
       </c>
       <c r="E349" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F349">
         <v>3.0</v>
@@ -11282,21 +11279,21 @@
         <v>37</v>
       </c>
       <c r="I349" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="350" spans="1:9">
       <c r="A350" t="s">
+        <v>657</v>
+      </c>
+      <c r="B350" t="s">
         <v>658</v>
-      </c>
-      <c r="B350" t="s">
-        <v>659</v>
       </c>
       <c r="C350" t="s">
         <v>282</v>
       </c>
       <c r="E350" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F350">
         <v>1.0</v>
@@ -11313,16 +11310,16 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" t="s">
+        <v>659</v>
+      </c>
+      <c r="B351" t="s">
         <v>660</v>
-      </c>
-      <c r="B351" t="s">
-        <v>661</v>
       </c>
       <c r="C351" t="s">
         <v>330</v>
       </c>
       <c r="E351" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F351">
         <v>2.0</v>
@@ -11334,21 +11331,21 @@
         <v>37</v>
       </c>
       <c r="I351" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="352" spans="1:9">
       <c r="A352" t="s">
+        <v>659</v>
+      </c>
+      <c r="B352" t="s">
         <v>660</v>
-      </c>
-      <c r="B352" t="s">
-        <v>661</v>
       </c>
       <c r="C352" t="s">
         <v>258</v>
       </c>
       <c r="E352" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F352">
         <v>5.0</v>
@@ -11360,21 +11357,21 @@
         <v>37</v>
       </c>
       <c r="I352" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="353" spans="1:9">
       <c r="A353" t="s">
+        <v>659</v>
+      </c>
+      <c r="B353" t="s">
         <v>660</v>
-      </c>
-      <c r="B353" t="s">
-        <v>661</v>
       </c>
       <c r="C353" t="s">
         <v>220</v>
       </c>
       <c r="E353" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F353">
         <v>3.0</v>
@@ -11386,21 +11383,21 @@
         <v>37</v>
       </c>
       <c r="I353" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="354" spans="1:9">
       <c r="A354" t="s">
+        <v>659</v>
+      </c>
+      <c r="B354" t="s">
         <v>660</v>
-      </c>
-      <c r="B354" t="s">
-        <v>661</v>
       </c>
       <c r="C354" t="s">
         <v>282</v>
       </c>
       <c r="E354" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F354">
         <v>2.0</v>
@@ -11412,21 +11409,21 @@
         <v>37</v>
       </c>
       <c r="I354" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="355" spans="1:9">
       <c r="A355" t="s">
+        <v>659</v>
+      </c>
+      <c r="B355" t="s">
         <v>660</v>
-      </c>
-      <c r="B355" t="s">
-        <v>661</v>
       </c>
       <c r="C355" t="s">
         <v>300</v>
       </c>
       <c r="E355" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F355">
         <v>2.0</v>
@@ -11438,15 +11435,15 @@
         <v>37</v>
       </c>
       <c r="I355" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="356" spans="1:9">
       <c r="A356" t="s">
+        <v>609</v>
+      </c>
+      <c r="B356" t="s">
         <v>610</v>
-      </c>
-      <c r="B356" t="s">
-        <v>611</v>
       </c>
       <c r="C356" t="s">
         <v>175</v>
@@ -11469,16 +11466,16 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" t="s">
+        <v>662</v>
+      </c>
+      <c r="B357" t="s">
         <v>663</v>
-      </c>
-      <c r="B357" t="s">
-        <v>664</v>
       </c>
       <c r="C357" t="s">
         <v>258</v>
       </c>
       <c r="E357" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F357">
         <v>3.0</v>
@@ -11490,21 +11487,21 @@
         <v>37</v>
       </c>
       <c r="I357" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="358" spans="1:9">
       <c r="A358" t="s">
+        <v>535</v>
+      </c>
+      <c r="B358" t="s">
         <v>536</v>
-      </c>
-      <c r="B358" t="s">
-        <v>537</v>
       </c>
       <c r="C358" t="s">
         <v>300</v>
       </c>
       <c r="E358" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F358">
         <v>2.0</v>
@@ -11516,7 +11513,7 @@
         <v>37</v>
       </c>
       <c r="I358" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>

--- a/src/inventory/Syl.xlsx
+++ b/src/inventory/Syl.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="613">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -578,9 +578,6 @@
     <t>৳303.57</t>
   </si>
   <si>
-    <t>৳607.14</t>
-  </si>
-  <si>
     <t>109-0402-041</t>
   </si>
   <si>
@@ -671,12 +668,6 @@
     <t>৳7,984.00</t>
   </si>
   <si>
-    <t>109-0102-071</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 071</t>
-  </si>
-  <si>
     <t>৳194.44</t>
   </si>
   <si>
@@ -749,10 +740,7 @@
     <t>৳228.76</t>
   </si>
   <si>
-    <t>৳1,372.55</t>
-  </si>
-  <si>
-    <t>৳5,988.00</t>
+    <t>৳1,143.79</t>
   </si>
   <si>
     <t>105-0301-007</t>
@@ -887,51 +875,48 @@
     <t>Drop Shoulder T-Shirt 05</t>
   </si>
   <si>
+    <t>৳258.06</t>
+  </si>
+  <si>
+    <t>103-0100-115</t>
+  </si>
+  <si>
+    <t>Premium Jade Green Polo Shirt</t>
+  </si>
+  <si>
+    <t>Men / POLO SHIRT,15% OFF,SALE,MEN,POLO,BASIC,PIQUE,PRINTED</t>
+  </si>
+  <si>
+    <t>৳256.63</t>
+  </si>
+  <si>
+    <t>৳522.28</t>
+  </si>
+  <si>
+    <t>106-0101-109</t>
+  </si>
+  <si>
+    <t>Grey Semi Formal Panjabi - Regular Fit</t>
+  </si>
+  <si>
+    <t>৳625.00</t>
+  </si>
+  <si>
+    <t>109-0402-054</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 54</t>
+  </si>
+  <si>
+    <t>109-0402-057</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 57</t>
+  </si>
+  <si>
     <t>৳1,650.00</t>
   </si>
   <si>
-    <t>৳2,370.00</t>
-  </si>
-  <si>
-    <t>৳258.06</t>
-  </si>
-  <si>
-    <t>103-0100-115</t>
-  </si>
-  <si>
-    <t>Premium Jade Green Polo Shirt</t>
-  </si>
-  <si>
-    <t>Men / POLO SHIRT,15% OFF,SALE,MEN,POLO,BASIC,PIQUE,PRINTED</t>
-  </si>
-  <si>
-    <t>৳256.63</t>
-  </si>
-  <si>
-    <t>৳522.28</t>
-  </si>
-  <si>
-    <t>106-0101-109</t>
-  </si>
-  <si>
-    <t>Grey Semi Formal Panjabi - Regular Fit</t>
-  </si>
-  <si>
-    <t>৳625.00</t>
-  </si>
-  <si>
-    <t>109-0402-054</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 54</t>
-  </si>
-  <si>
-    <t>109-0402-057</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 57</t>
-  </si>
-  <si>
     <t>৳2,850.00</t>
   </si>
   <si>
@@ -1064,6 +1049,42 @@
     <t>M</t>
   </si>
   <si>
+    <t>109-0303-004</t>
+  </si>
+  <si>
+    <t>Navy Blue Leather Passport Holder</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,PASSPORT HOLDER</t>
+  </si>
+  <si>
+    <t>৳880.00</t>
+  </si>
+  <si>
+    <t>105-0401-007</t>
+  </si>
+  <si>
+    <t>Cabbage Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>Men / Tank Top</t>
+  </si>
+  <si>
+    <t>৳1,050.00</t>
+  </si>
+  <si>
+    <t>৳1,770.00</t>
+  </si>
+  <si>
+    <t>109-0402-061</t>
+  </si>
+  <si>
+    <t>Premium Leather Belt 061</t>
+  </si>
+  <si>
+    <t>৳2,970.00</t>
+  </si>
+  <si>
     <t>102-0302-005</t>
   </si>
   <si>
@@ -1082,16 +1103,25 @@
     <t>৳5,900.00</t>
   </si>
   <si>
-    <t>109-0303-004</t>
-  </si>
-  <si>
-    <t>Navy Blue Leather Passport Holder</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,PASSPORT HOLDER</t>
-  </si>
-  <si>
-    <t>৳880.00</t>
+    <t>105-0301-006</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 06</t>
+  </si>
+  <si>
+    <t>102-0302-008</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 008</t>
+  </si>
+  <si>
+    <t>৳500.00</t>
+  </si>
+  <si>
+    <t>৳2,000.00</t>
+  </si>
+  <si>
+    <t>৳5,300.00</t>
   </si>
   <si>
     <t>105-0301-009</t>
@@ -1100,51 +1130,6 @@
     <t>Deep Violet Drop Shoulder T-Shirt</t>
   </si>
   <si>
-    <t>105-0401-007</t>
-  </si>
-  <si>
-    <t>Cabbage Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>Men / Tank Top</t>
-  </si>
-  <si>
-    <t>৳1,050.00</t>
-  </si>
-  <si>
-    <t>৳1,770.00</t>
-  </si>
-  <si>
-    <t>109-0402-061</t>
-  </si>
-  <si>
-    <t>Premium Leather Belt 061</t>
-  </si>
-  <si>
-    <t>৳2,970.00</t>
-  </si>
-  <si>
-    <t>102-0302-008</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 008</t>
-  </si>
-  <si>
-    <t>৳500.00</t>
-  </si>
-  <si>
-    <t>৳2,000.00</t>
-  </si>
-  <si>
-    <t>৳5,300.00</t>
-  </si>
-  <si>
-    <t>105-0301-006</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 06</t>
-  </si>
-  <si>
     <t>109-0501-001</t>
   </si>
   <si>
@@ -1223,21 +1208,21 @@
     <t>৳2,950.00</t>
   </si>
   <si>
+    <t>105-0201-036</t>
+  </si>
+  <si>
+    <t>Full Sleeve Graphic T-shirt</t>
+  </si>
+  <si>
+    <t>৳728.00</t>
+  </si>
+  <si>
     <t>৳1,950.00</t>
   </si>
   <si>
     <t>৳3,540.00</t>
   </si>
   <si>
-    <t>105-0201-036</t>
-  </si>
-  <si>
-    <t>Full Sleeve Graphic T-shirt</t>
-  </si>
-  <si>
-    <t>৳728.00</t>
-  </si>
-  <si>
     <t>৳540.00</t>
   </si>
   <si>
@@ -1262,6 +1247,42 @@
     <t>Sable Relaxed Graphic Tank Top</t>
   </si>
   <si>
+    <t>105-0401-003</t>
+  </si>
+  <si>
+    <t>Tank Top 003</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Tank Top</t>
+  </si>
+  <si>
+    <t>৳83.33</t>
+  </si>
+  <si>
+    <t>৳416.67</t>
+  </si>
+  <si>
+    <t>৳3,200.00</t>
+  </si>
+  <si>
+    <t>৳1,080.00</t>
+  </si>
+  <si>
+    <t>109-0402-060</t>
+  </si>
+  <si>
+    <t>Premium Leather Belt 060</t>
+  </si>
+  <si>
+    <t>109-0103-008</t>
+  </si>
+  <si>
+    <t>Auburn Luxe Trifold Leather Wallet</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,WALLET,TRI-FOLD,Draft Items</t>
+  </si>
+  <si>
     <t>102-0301-004</t>
   </si>
   <si>
@@ -1274,31 +1295,16 @@
     <t>৳8,260.00</t>
   </si>
   <si>
-    <t>105-0401-003</t>
-  </si>
-  <si>
-    <t>Tank Top 003</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Tank Top</t>
-  </si>
-  <si>
-    <t>৳83.33</t>
-  </si>
-  <si>
-    <t>৳416.67</t>
-  </si>
-  <si>
-    <t>৳3,200.00</t>
-  </si>
-  <si>
-    <t>৳1,080.00</t>
-  </si>
-  <si>
-    <t>109-0402-060</t>
-  </si>
-  <si>
-    <t>Premium Leather Belt 060</t>
+    <t>103-0200-099</t>
+  </si>
+  <si>
+    <t>Black Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
+    <t>৳1,300.00</t>
+  </si>
+  <si>
+    <t>৳2,360.00</t>
   </si>
   <si>
     <t>৳1,000.00</t>
@@ -1307,13 +1313,16 @@
     <t>৳2,650.00</t>
   </si>
   <si>
-    <t>109-0103-008</t>
-  </si>
-  <si>
-    <t>Auburn Luxe Trifold Leather Wallet</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,WALLET,TRI-FOLD,Draft Items</t>
+    <t>105-0101-373</t>
+  </si>
+  <si>
+    <t>Rust Bloom T-shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
+  </si>
+  <si>
+    <t>৳640.00</t>
   </si>
   <si>
     <t>102-0302-006</t>
@@ -1325,16 +1334,13 @@
     <t>৳2,600.00</t>
   </si>
   <si>
-    <t>103-0200-099</t>
-  </si>
-  <si>
-    <t>Black Polo Shirt in Cotton Pique</t>
-  </si>
-  <si>
-    <t>৳1,300.00</t>
-  </si>
-  <si>
-    <t>৳2,360.00</t>
+    <t>৳250.00</t>
+  </si>
+  <si>
+    <t>৳1,500.00</t>
+  </si>
+  <si>
+    <t>৳3,840.00</t>
   </si>
   <si>
     <t>102-0301-002</t>
@@ -1346,27 +1352,6 @@
     <t>৳9,275.00</t>
   </si>
   <si>
-    <t>105-0101-373</t>
-  </si>
-  <si>
-    <t>Rust Bloom T-shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
-  </si>
-  <si>
-    <t>৳640.00</t>
-  </si>
-  <si>
-    <t>৳250.00</t>
-  </si>
-  <si>
-    <t>৳1,500.00</t>
-  </si>
-  <si>
-    <t>৳3,840.00</t>
-  </si>
-  <si>
     <t>102-0302-001</t>
   </si>
   <si>
@@ -1382,24 +1367,24 @@
     <t>৳2,900.00</t>
   </si>
   <si>
+    <t>108-0101-013</t>
+  </si>
+  <si>
+    <t>Brown Sweatshirt in French-Terry</t>
+  </si>
+  <si>
+    <t>৳159.09</t>
+  </si>
+  <si>
+    <t>৳636.36</t>
+  </si>
+  <si>
+    <t>৳2,560.00</t>
+  </si>
+  <si>
     <t>৳6,625.00</t>
   </si>
   <si>
-    <t>108-0101-013</t>
-  </si>
-  <si>
-    <t>Brown Sweatshirt in French-Terry</t>
-  </si>
-  <si>
-    <t>৳159.09</t>
-  </si>
-  <si>
-    <t>৳636.36</t>
-  </si>
-  <si>
-    <t>৳2,560.00</t>
-  </si>
-  <si>
     <t>৳2,394.00</t>
   </si>
   <si>
@@ -1442,27 +1427,27 @@
     <t>Cuban Shirt 007</t>
   </si>
   <si>
+    <t>105-0101-372</t>
+  </si>
+  <si>
+    <t>Deep Harbor T-shirt</t>
+  </si>
+  <si>
     <t>102-0302-010</t>
   </si>
   <si>
     <t>Cuban Shirt 010</t>
   </si>
   <si>
-    <t>105-0101-372</t>
-  </si>
-  <si>
-    <t>Deep Harbor T-shirt</t>
+    <t>৳41.67</t>
+  </si>
+  <si>
+    <t>৳166.67</t>
   </si>
   <si>
     <t>৳1,325.00</t>
   </si>
   <si>
-    <t>৳41.67</t>
-  </si>
-  <si>
-    <t>৳166.67</t>
-  </si>
-  <si>
     <t>109-0101-045</t>
   </si>
   <si>
@@ -1535,9 +1520,6 @@
     <t>৳202.55</t>
   </si>
   <si>
-    <t>৳405.11</t>
-  </si>
-  <si>
     <t>105-0401-008</t>
   </si>
   <si>
@@ -1574,7 +1556,7 @@
     <t>৳209.53</t>
   </si>
   <si>
-    <t>৳1,047.64</t>
+    <t>৳838.11</t>
   </si>
   <si>
     <t>৳420.00</t>
@@ -1619,6 +1601,18 @@
     <t>৳1,625.00</t>
   </si>
   <si>
+    <t>৳95.45</t>
+  </si>
+  <si>
+    <t>৳190.91</t>
+  </si>
+  <si>
+    <t>105-0201-032</t>
+  </si>
+  <si>
+    <t>Full Sleeve White Stripe T-shirt</t>
+  </si>
+  <si>
     <t>102-0301-005</t>
   </si>
   <si>
@@ -1631,34 +1625,22 @@
     <t>Half Sleeve shirt 009</t>
   </si>
   <si>
-    <t>৳95.45</t>
-  </si>
-  <si>
-    <t>৳190.91</t>
-  </si>
-  <si>
-    <t>105-0201-032</t>
-  </si>
-  <si>
-    <t>Full Sleeve White Stripe T-shirt</t>
-  </si>
-  <si>
     <t>৳210.00</t>
   </si>
   <si>
     <t>৳2,912.00</t>
   </si>
   <si>
+    <t>৳116.67</t>
+  </si>
+  <si>
+    <t>৳1,633.33</t>
+  </si>
+  <si>
     <t>102-0301-003</t>
   </si>
   <si>
     <t>Half Sleeve shirt 003</t>
-  </si>
-  <si>
-    <t>৳116.67</t>
-  </si>
-  <si>
-    <t>৳1,633.33</t>
   </si>
   <si>
     <t>102-0301-001</t>
@@ -2211,7 +2193,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I328"/>
+  <dimension ref="A1:I325"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4027,24 +4009,24 @@
         <v>139</v>
       </c>
       <c r="F71">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G71" t="s">
         <v>186</v>
       </c>
       <c r="H71" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I71" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
+        <v>187</v>
+      </c>
+      <c r="B72" t="s">
         <v>188</v>
-      </c>
-      <c r="B72" t="s">
-        <v>189</v>
       </c>
       <c r="E72" t="s">
         <v>171</v>
@@ -4056,10 +4038,10 @@
         <v>108</v>
       </c>
       <c r="H72" t="s">
+        <v>189</v>
+      </c>
+      <c r="I72" t="s">
         <v>190</v>
-      </c>
-      <c r="I72" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -4079,13 +4061,13 @@
         <v>5.0</v>
       </c>
       <c r="G73" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H73" t="s">
         <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -4105,21 +4087,21 @@
         <v>15.0</v>
       </c>
       <c r="G74" t="s">
+        <v>193</v>
+      </c>
+      <c r="H74" t="s">
         <v>194</v>
       </c>
-      <c r="H74" t="s">
+      <c r="I74" t="s">
         <v>195</v>
-      </c>
-      <c r="I74" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
+        <v>196</v>
+      </c>
+      <c r="B75" t="s">
         <v>197</v>
-      </c>
-      <c r="B75" t="s">
-        <v>198</v>
       </c>
       <c r="C75" t="s">
         <v>148</v>
@@ -4131,76 +4113,76 @@
         <v>1.0</v>
       </c>
       <c r="G75" t="s">
+        <v>198</v>
+      </c>
+      <c r="H75" t="s">
+        <v>198</v>
+      </c>
+      <c r="I75" t="s">
         <v>199</v>
-      </c>
-      <c r="H75" t="s">
-        <v>199</v>
-      </c>
-      <c r="I75" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76" t="s">
         <v>201</v>
-      </c>
-      <c r="B76" t="s">
-        <v>202</v>
       </c>
       <c r="C76" t="s">
         <v>182</v>
       </c>
       <c r="E76" t="s">
+        <v>202</v>
+      </c>
+      <c r="F76">
+        <v>1.0</v>
+      </c>
+      <c r="G76" t="s">
         <v>203</v>
       </c>
-      <c r="F76">
-        <v>1.0</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
+        <v>203</v>
+      </c>
+      <c r="I76" t="s">
         <v>204</v>
-      </c>
-      <c r="H76" t="s">
-        <v>204</v>
-      </c>
-      <c r="I76" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
+        <v>200</v>
+      </c>
+      <c r="B77" t="s">
         <v>201</v>
-      </c>
-      <c r="B77" t="s">
-        <v>202</v>
       </c>
       <c r="C77" t="s">
         <v>138</v>
       </c>
       <c r="E77" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F77">
         <v>1.0</v>
       </c>
       <c r="G77" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H77" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I77" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
+        <v>196</v>
+      </c>
+      <c r="B78" t="s">
         <v>197</v>
       </c>
-      <c r="B78" t="s">
-        <v>198</v>
-      </c>
       <c r="C78" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E78" t="s">
         <v>177</v>
@@ -4209,27 +4191,27 @@
         <v>1.0</v>
       </c>
       <c r="G78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I78" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
+        <v>208</v>
+      </c>
+      <c r="B79" t="s">
         <v>209</v>
-      </c>
-      <c r="B79" t="s">
-        <v>210</v>
       </c>
       <c r="C79" t="s">
         <v>173</v>
       </c>
       <c r="E79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F79">
         <v>2.0</v>
@@ -4241,7 +4223,7 @@
         <v>36</v>
       </c>
       <c r="I79" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4272,10 +4254,10 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
+        <v>212</v>
+      </c>
+      <c r="B81" t="s">
         <v>213</v>
-      </c>
-      <c r="B81" t="s">
-        <v>214</v>
       </c>
       <c r="C81" t="s">
         <v>138</v>
@@ -4287,131 +4269,134 @@
         <v>8.0</v>
       </c>
       <c r="G81" t="s">
+        <v>214</v>
+      </c>
+      <c r="H81" t="s">
         <v>215</v>
       </c>
-      <c r="H81" t="s">
+      <c r="I81" t="s">
         <v>216</v>
-      </c>
-      <c r="I81" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
+        <v>212</v>
+      </c>
+      <c r="B82" t="s">
+        <v>213</v>
+      </c>
+      <c r="C82" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" t="s">
+        <v>139</v>
+      </c>
+      <c r="F82">
+        <v>3.0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>217</v>
+      </c>
+      <c r="H82" t="s">
+        <v>128</v>
+      </c>
+      <c r="I82" t="s">
         <v>218</v>
-      </c>
-      <c r="B82" t="s">
-        <v>219</v>
-      </c>
-      <c r="E82" t="s">
-        <v>132</v>
-      </c>
-      <c r="F82">
-        <v>1.0</v>
-      </c>
-      <c r="G82" t="s">
-        <v>133</v>
-      </c>
-      <c r="H82" t="s">
-        <v>133</v>
-      </c>
-      <c r="I82" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B83" t="s">
-        <v>214</v>
-      </c>
-      <c r="C83" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E83" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F83">
         <v>3.0</v>
       </c>
       <c r="G83" t="s">
+        <v>36</v>
+      </c>
+      <c r="H83" t="s">
+        <v>36</v>
+      </c>
+      <c r="I83" t="s">
         <v>220</v>
-      </c>
-      <c r="H83" t="s">
-        <v>128</v>
-      </c>
-      <c r="I83" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
+        <v>221</v>
+      </c>
+      <c r="B84" t="s">
         <v>222</v>
       </c>
-      <c r="B84" t="s">
-        <v>162</v>
+      <c r="C84" t="s">
+        <v>173</v>
       </c>
       <c r="E84" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="F84">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G84" t="s">
-        <v>36</v>
+        <v>224</v>
       </c>
       <c r="H84" t="s">
-        <v>36</v>
+        <v>225</v>
       </c>
       <c r="I84" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B85" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="E85" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F85">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G85" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H85" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I85" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B86" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C86" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="E86" t="s">
+        <v>223</v>
+      </c>
+      <c r="F86">
+        <v>5.0</v>
+      </c>
+      <c r="G86" t="s">
         <v>232</v>
-      </c>
-      <c r="F86">
-        <v>1.0</v>
-      </c>
-      <c r="G86" t="s">
-        <v>233</v>
       </c>
       <c r="H86" t="s">
         <v>233</v>
@@ -4422,120 +4407,120 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B87" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C87" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="E87" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
       <c r="F87">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G87" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="H87" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="I87" t="s">
-        <v>237</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="B88" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C88" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E88" t="s">
-        <v>139</v>
+        <v>237</v>
       </c>
       <c r="F88">
         <v>1.0</v>
       </c>
       <c r="G88" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="H88" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="I88" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="B89" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="C89" t="s">
         <v>173</v>
       </c>
       <c r="E89" t="s">
+        <v>139</v>
+      </c>
+      <c r="F89">
+        <v>5.0</v>
+      </c>
+      <c r="G89" t="s">
         <v>240</v>
-      </c>
-      <c r="F89">
-        <v>1.0</v>
-      </c>
-      <c r="G89" t="s">
-        <v>241</v>
       </c>
       <c r="H89" t="s">
         <v>241</v>
       </c>
       <c r="I89" t="s">
-        <v>242</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="B90" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="C90" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E90" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="F90">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G90" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H90" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I90" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B91" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C91" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="E91" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
       <c r="F91">
         <v>1.0</v>
@@ -4547,33 +4532,33 @@
         <v>250</v>
       </c>
       <c r="I91" t="s">
-        <v>251</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
+        <v>251</v>
+      </c>
+      <c r="B92" t="s">
         <v>252</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
+        <v>244</v>
+      </c>
+      <c r="E92" t="s">
+        <v>245</v>
+      </c>
+      <c r="F92">
+        <v>7.0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>108</v>
+      </c>
+      <c r="H92" t="s">
         <v>253</v>
       </c>
-      <c r="C92" t="s">
-        <v>182</v>
-      </c>
-      <c r="E92" t="s">
-        <v>203</v>
-      </c>
-      <c r="F92">
-        <v>1.0</v>
-      </c>
-      <c r="G92" t="s">
+      <c r="I92" t="s">
         <v>254</v>
-      </c>
-      <c r="H92" t="s">
-        <v>254</v>
-      </c>
-      <c r="I92" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4583,17 +4568,14 @@
       <c r="B93" t="s">
         <v>256</v>
       </c>
-      <c r="C93" t="s">
-        <v>248</v>
-      </c>
       <c r="E93" t="s">
-        <v>249</v>
+        <v>132</v>
       </c>
       <c r="F93">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G93" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="H93" t="s">
         <v>257</v>
@@ -4604,178 +4586,181 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" t="s">
+        <v>201</v>
+      </c>
+      <c r="C94" t="s">
+        <v>173</v>
+      </c>
+      <c r="E94" t="s">
+        <v>202</v>
+      </c>
+      <c r="F94">
+        <v>16.0</v>
+      </c>
+      <c r="G94" t="s">
         <v>259</v>
       </c>
-      <c r="B94" t="s">
+      <c r="H94" t="s">
         <v>260</v>
       </c>
-      <c r="E94" t="s">
-        <v>132</v>
-      </c>
-      <c r="F94">
-        <v>2.0</v>
-      </c>
-      <c r="G94" t="s">
-        <v>215</v>
-      </c>
-      <c r="H94" t="s">
+      <c r="I94" t="s">
         <v>261</v>
-      </c>
-      <c r="I94" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="B95" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="C95" t="s">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="E95" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="F95">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="G95" t="s">
+        <v>108</v>
+      </c>
+      <c r="H95" t="s">
+        <v>189</v>
+      </c>
+      <c r="I95" t="s">
         <v>263</v>
-      </c>
-      <c r="H95" t="s">
-        <v>264</v>
-      </c>
-      <c r="I95" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="C96" t="s">
+        <v>173</v>
+      </c>
+      <c r="E96" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96">
+        <v>3.0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>264</v>
+      </c>
+      <c r="H96" t="s">
+        <v>265</v>
+      </c>
+      <c r="I96" t="s">
         <v>266</v>
-      </c>
-      <c r="E96" t="s">
-        <v>249</v>
-      </c>
-      <c r="F96">
-        <v>2.0</v>
-      </c>
-      <c r="G96" t="s">
-        <v>108</v>
-      </c>
-      <c r="H96" t="s">
-        <v>190</v>
-      </c>
-      <c r="I96" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="B97" t="s">
-        <v>176</v>
+        <v>268</v>
       </c>
       <c r="C97" t="s">
         <v>173</v>
       </c>
       <c r="E97" t="s">
-        <v>177</v>
+        <v>269</v>
       </c>
       <c r="F97">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G97" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H97" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I97" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>271</v>
+        <v>49</v>
       </c>
       <c r="B98" t="s">
+        <v>50</v>
+      </c>
+      <c r="C98">
+        <v>40</v>
+      </c>
+      <c r="E98" t="s">
+        <v>51</v>
+      </c>
+      <c r="F98">
+        <v>1.0</v>
+      </c>
+      <c r="G98" t="s">
         <v>272</v>
       </c>
-      <c r="C98" t="s">
-        <v>173</v>
-      </c>
-      <c r="E98" t="s">
-        <v>273</v>
-      </c>
-      <c r="F98">
-        <v>1.0</v>
-      </c>
-      <c r="G98" t="s">
-        <v>274</v>
-      </c>
       <c r="H98" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I98" t="s">
-        <v>275</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>49</v>
+        <v>273</v>
       </c>
       <c r="B99" t="s">
-        <v>50</v>
-      </c>
-      <c r="C99">
-        <v>40</v>
+        <v>274</v>
       </c>
       <c r="E99" t="s">
-        <v>51</v>
+        <v>171</v>
       </c>
       <c r="F99">
         <v>1.0</v>
       </c>
       <c r="G99" t="s">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="H99" t="s">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="I99" t="s">
-        <v>53</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
+        <v>276</v>
+      </c>
+      <c r="B100" t="s">
         <v>277</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>278</v>
       </c>
       <c r="E100" t="s">
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="F100">
         <v>1.0</v>
       </c>
       <c r="G100" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="H100" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="I100" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -4786,22 +4771,22 @@
         <v>281</v>
       </c>
       <c r="C101" t="s">
+        <v>173</v>
+      </c>
+      <c r="E101" t="s">
+        <v>177</v>
+      </c>
+      <c r="F101">
+        <v>3.0</v>
+      </c>
+      <c r="G101" t="s">
         <v>282</v>
       </c>
-      <c r="E101" t="s">
+      <c r="H101" t="s">
         <v>283</v>
       </c>
-      <c r="F101">
-        <v>1.0</v>
-      </c>
-      <c r="G101" t="s">
-        <v>215</v>
-      </c>
-      <c r="H101" t="s">
-        <v>215</v>
-      </c>
       <c r="I101" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -4812,195 +4797,195 @@
         <v>285</v>
       </c>
       <c r="C102" t="s">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="E102" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="F102">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G102" t="s">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="H102" t="s">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="I102" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>288</v>
+        <v>180</v>
       </c>
       <c r="B103" t="s">
-        <v>289</v>
+        <v>181</v>
       </c>
       <c r="C103" t="s">
-        <v>266</v>
+        <v>173</v>
       </c>
       <c r="E103" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
       <c r="F103">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G103" t="s">
-        <v>108</v>
+        <v>286</v>
       </c>
       <c r="H103" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I103" t="s">
-        <v>291</v>
+        <v>199</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="B104" t="s">
-        <v>181</v>
+        <v>288</v>
       </c>
       <c r="C104" t="s">
         <v>173</v>
       </c>
       <c r="E104" t="s">
-        <v>177</v>
+        <v>289</v>
       </c>
       <c r="F104">
         <v>1.0</v>
       </c>
       <c r="G104" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H104" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I104" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B105" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C105" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E105" t="s">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="F105">
         <v>1.0</v>
       </c>
       <c r="G105" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="H105" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I105" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B106" t="s">
-        <v>289</v>
-      </c>
-      <c r="C106" t="s">
-        <v>248</v>
+        <v>293</v>
+      </c>
+      <c r="C106">
+        <v>44</v>
       </c>
       <c r="E106" t="s">
-        <v>249</v>
+        <v>51</v>
       </c>
       <c r="F106">
         <v>1.0</v>
       </c>
       <c r="G106" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H106" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I106" t="s">
-        <v>251</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B107" t="s">
-        <v>299</v>
-      </c>
-      <c r="C107">
-        <v>44</v>
+        <v>296</v>
       </c>
       <c r="E107" t="s">
-        <v>51</v>
+        <v>171</v>
       </c>
       <c r="F107">
         <v>1.0</v>
       </c>
       <c r="G107" t="s">
-        <v>300</v>
+        <v>108</v>
       </c>
       <c r="H107" t="s">
-        <v>300</v>
+        <v>108</v>
       </c>
       <c r="I107" t="s">
-        <v>53</v>
+        <v>275</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B108" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E108" t="s">
         <v>171</v>
       </c>
       <c r="F108">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G108" t="s">
         <v>108</v>
       </c>
       <c r="H108" t="s">
-        <v>108</v>
+        <v>299</v>
       </c>
       <c r="I108" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
+        <v>301</v>
+      </c>
+      <c r="B109" t="s">
+        <v>302</v>
+      </c>
+      <c r="C109" t="s">
+        <v>173</v>
+      </c>
+      <c r="E109" t="s">
+        <v>229</v>
+      </c>
+      <c r="F109">
+        <v>6.0</v>
+      </c>
+      <c r="G109" t="s">
         <v>303</v>
       </c>
-      <c r="B109" t="s">
+      <c r="H109" t="s">
         <v>304</v>
-      </c>
-      <c r="E109" t="s">
-        <v>171</v>
-      </c>
-      <c r="F109">
-        <v>3.0</v>
-      </c>
-      <c r="G109" t="s">
-        <v>108</v>
-      </c>
-      <c r="H109" t="s">
-        <v>290</v>
       </c>
       <c r="I109" t="s">
         <v>305</v>
@@ -5013,31 +4998,28 @@
       <c r="B110" t="s">
         <v>307</v>
       </c>
-      <c r="C110" t="s">
-        <v>173</v>
-      </c>
       <c r="E110" t="s">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="F110">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G110" t="s">
-        <v>308</v>
+        <v>214</v>
       </c>
       <c r="H110" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="I110" t="s">
-        <v>310</v>
+        <v>258</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B111" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E111" t="s">
         <v>132</v>
@@ -5046,21 +5028,21 @@
         <v>2.0</v>
       </c>
       <c r="G111" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H111" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I111" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B112" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E112" t="s">
         <v>132</v>
@@ -5069,137 +5051,137 @@
         <v>2.0</v>
       </c>
       <c r="G112" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H112" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I112" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B113" t="s">
-        <v>316</v>
+        <v>252</v>
+      </c>
+      <c r="C113" t="s">
+        <v>262</v>
       </c>
       <c r="E113" t="s">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="F113">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G113" t="s">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="H113" t="s">
-        <v>261</v>
+        <v>108</v>
       </c>
       <c r="I113" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B114" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="C114" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="E114" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="F114">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G114" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="H114" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="I114" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
+        <v>317</v>
+      </c>
+      <c r="B115" t="s">
+        <v>318</v>
+      </c>
+      <c r="E115" t="s">
+        <v>171</v>
+      </c>
+      <c r="F115">
+        <v>2.0</v>
+      </c>
+      <c r="G115" t="s">
+        <v>108</v>
+      </c>
+      <c r="H115" t="s">
+        <v>189</v>
+      </c>
+      <c r="I115" t="s">
         <v>319</v>
-      </c>
-      <c r="B115" t="s">
-        <v>320</v>
-      </c>
-      <c r="C115" t="s">
-        <v>207</v>
-      </c>
-      <c r="E115" t="s">
-        <v>226</v>
-      </c>
-      <c r="F115">
-        <v>3.0</v>
-      </c>
-      <c r="G115" t="s">
-        <v>36</v>
-      </c>
-      <c r="H115" t="s">
-        <v>36</v>
-      </c>
-      <c r="I115" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B116" t="s">
-        <v>323</v>
+        <v>321</v>
+      </c>
+      <c r="C116" t="s">
+        <v>182</v>
       </c>
       <c r="E116" t="s">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="F116">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G116" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="H116" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="I116" t="s">
-        <v>324</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
+        <v>322</v>
+      </c>
+      <c r="B117" t="s">
+        <v>323</v>
+      </c>
+      <c r="E117" t="s">
+        <v>324</v>
+      </c>
+      <c r="F117">
+        <v>3.0</v>
+      </c>
+      <c r="G117" t="s">
+        <v>133</v>
+      </c>
+      <c r="H117" t="s">
         <v>325</v>
       </c>
-      <c r="B117" t="s">
+      <c r="I117" t="s">
         <v>326</v>
-      </c>
-      <c r="C117" t="s">
-        <v>182</v>
-      </c>
-      <c r="E117" t="s">
-        <v>226</v>
-      </c>
-      <c r="F117">
-        <v>5.0</v>
-      </c>
-      <c r="G117" t="s">
-        <v>36</v>
-      </c>
-      <c r="H117" t="s">
-        <v>36</v>
-      </c>
-      <c r="I117" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5210,316 +5192,319 @@
         <v>328</v>
       </c>
       <c r="E118" t="s">
-        <v>329</v>
+        <v>171</v>
       </c>
       <c r="F118">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G118" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="H118" t="s">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="I118" t="s">
-        <v>331</v>
+        <v>172</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B119" t="s">
-        <v>333</v>
+        <v>330</v>
+      </c>
+      <c r="C119" t="s">
+        <v>173</v>
       </c>
       <c r="E119" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="F119">
         <v>1.0</v>
       </c>
       <c r="G119" t="s">
-        <v>108</v>
+        <v>331</v>
       </c>
       <c r="H119" t="s">
-        <v>108</v>
+        <v>331</v>
       </c>
       <c r="I119" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="B120" t="s">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="C120" t="s">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="E120" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="F120">
         <v>1.0</v>
       </c>
       <c r="G120" t="s">
-        <v>336</v>
+        <v>108</v>
       </c>
       <c r="H120" t="s">
-        <v>336</v>
+        <v>108</v>
       </c>
       <c r="I120" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="B121" t="s">
-        <v>289</v>
-      </c>
-      <c r="C121" t="s">
+        <v>334</v>
+      </c>
+      <c r="E121" t="s">
+        <v>335</v>
+      </c>
+      <c r="F121">
+        <v>24.0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>336</v>
+      </c>
+      <c r="H121" t="s">
         <v>337</v>
       </c>
-      <c r="E121" t="s">
-        <v>249</v>
-      </c>
-      <c r="F121">
-        <v>1.0</v>
-      </c>
-      <c r="G121" t="s">
-        <v>108</v>
-      </c>
-      <c r="H121" t="s">
-        <v>108</v>
-      </c>
       <c r="I121" t="s">
-        <v>251</v>
+        <v>338</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B122" t="s">
-        <v>339</v>
+        <v>340</v>
+      </c>
+      <c r="C122" t="s">
+        <v>173</v>
       </c>
       <c r="E122" t="s">
-        <v>340</v>
+        <v>223</v>
       </c>
       <c r="F122">
-        <v>24.0</v>
+        <v>2.0</v>
       </c>
       <c r="G122" t="s">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="H122" t="s">
-        <v>342</v>
+        <v>36</v>
       </c>
       <c r="I122" t="s">
-        <v>343</v>
+        <v>226</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>344</v>
+        <v>242</v>
       </c>
       <c r="B123" t="s">
-        <v>345</v>
+        <v>243</v>
       </c>
       <c r="C123" t="s">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="E123" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="F123">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G123" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="H123" t="s">
-        <v>36</v>
+        <v>341</v>
       </c>
       <c r="I123" t="s">
-        <v>229</v>
+        <v>342</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="B124" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="C124" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E124" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F124">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G124" t="s">
         <v>108</v>
       </c>
       <c r="H124" t="s">
-        <v>346</v>
+        <v>108</v>
       </c>
       <c r="I124" t="s">
-        <v>347</v>
+        <v>247</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="B125" t="s">
-        <v>289</v>
-      </c>
-      <c r="C125" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E125" t="s">
-        <v>249</v>
+        <v>346</v>
       </c>
       <c r="F125">
         <v>1.0</v>
       </c>
       <c r="G125" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="H125" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="I125" t="s">
-        <v>251</v>
+        <v>347</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
+        <v>348</v>
+      </c>
+      <c r="B126" t="s">
         <v>349</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
+        <v>278</v>
+      </c>
+      <c r="E126" t="s">
         <v>350</v>
       </c>
-      <c r="C126" t="s">
-        <v>248</v>
-      </c>
-      <c r="E126" t="s">
+      <c r="F126">
+        <v>3.0</v>
+      </c>
+      <c r="G126" t="s">
+        <v>214</v>
+      </c>
+      <c r="H126" t="s">
         <v>351</v>
       </c>
-      <c r="F126">
-        <v>5.0</v>
-      </c>
-      <c r="G126" t="s">
+      <c r="I126" t="s">
         <v>352</v>
-      </c>
-      <c r="H126" t="s">
-        <v>353</v>
-      </c>
-      <c r="I126" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
+        <v>353</v>
+      </c>
+      <c r="B127" t="s">
+        <v>354</v>
+      </c>
+      <c r="E127" t="s">
+        <v>171</v>
+      </c>
+      <c r="F127">
+        <v>3.0</v>
+      </c>
+      <c r="G127" t="s">
+        <v>133</v>
+      </c>
+      <c r="H127" t="s">
+        <v>325</v>
+      </c>
+      <c r="I127" t="s">
         <v>355</v>
-      </c>
-      <c r="B127" t="s">
-        <v>356</v>
-      </c>
-      <c r="E127" t="s">
-        <v>357</v>
-      </c>
-      <c r="F127">
-        <v>1.0</v>
-      </c>
-      <c r="G127" t="s">
-        <v>36</v>
-      </c>
-      <c r="H127" t="s">
-        <v>36</v>
-      </c>
-      <c r="I127" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
+        <v>356</v>
+      </c>
+      <c r="B128" t="s">
+        <v>357</v>
+      </c>
+      <c r="C128" t="s">
+        <v>244</v>
+      </c>
+      <c r="E128" t="s">
+        <v>358</v>
+      </c>
+      <c r="F128">
+        <v>5.0</v>
+      </c>
+      <c r="G128" t="s">
         <v>359</v>
       </c>
-      <c r="B128" t="s">
+      <c r="H128" t="s">
         <v>360</v>
       </c>
-      <c r="C128" t="s">
-        <v>266</v>
-      </c>
-      <c r="E128" t="s">
-        <v>283</v>
-      </c>
-      <c r="F128">
-        <v>1.0</v>
-      </c>
-      <c r="G128" t="s">
-        <v>215</v>
-      </c>
-      <c r="H128" t="s">
-        <v>215</v>
-      </c>
       <c r="I128" t="s">
-        <v>251</v>
+        <v>361</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B129" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C129" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="E129" t="s">
-        <v>363</v>
+        <v>245</v>
       </c>
       <c r="F129">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G129" t="s">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="H129" t="s">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="I129" t="s">
-        <v>365</v>
+        <v>313</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
+        <v>364</v>
+      </c>
+      <c r="B130" t="s">
+        <v>365</v>
+      </c>
+      <c r="C130" t="s">
+        <v>244</v>
+      </c>
+      <c r="E130" t="s">
+        <v>358</v>
+      </c>
+      <c r="F130">
+        <v>4.0</v>
+      </c>
+      <c r="G130" t="s">
         <v>366</v>
       </c>
-      <c r="B130" t="s">
+      <c r="H130" t="s">
         <v>367</v>
-      </c>
-      <c r="E130" t="s">
-        <v>171</v>
-      </c>
-      <c r="F130">
-        <v>3.0</v>
-      </c>
-      <c r="G130" t="s">
-        <v>133</v>
-      </c>
-      <c r="H130" t="s">
-        <v>330</v>
       </c>
       <c r="I130" t="s">
         <v>368</v>
@@ -5533,218 +5518,215 @@
         <v>370</v>
       </c>
       <c r="C131" t="s">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="E131" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="F131">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G131" t="s">
-        <v>371</v>
+        <v>214</v>
       </c>
       <c r="H131" t="s">
-        <v>372</v>
+        <v>214</v>
       </c>
       <c r="I131" t="s">
-        <v>373</v>
+        <v>247</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
+        <v>371</v>
+      </c>
+      <c r="B132" t="s">
+        <v>372</v>
+      </c>
+      <c r="E132" t="s">
+        <v>373</v>
+      </c>
+      <c r="F132">
+        <v>8.0</v>
+      </c>
+      <c r="G132" t="s">
         <v>374</v>
       </c>
-      <c r="B132" t="s">
+      <c r="H132" t="s">
         <v>375</v>
       </c>
-      <c r="C132" t="s">
-        <v>348</v>
-      </c>
-      <c r="E132" t="s">
-        <v>249</v>
-      </c>
-      <c r="F132">
-        <v>1.0</v>
-      </c>
-      <c r="G132" t="s">
-        <v>108</v>
-      </c>
-      <c r="H132" t="s">
-        <v>108</v>
-      </c>
       <c r="I132" t="s">
-        <v>318</v>
+        <v>376</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="B133" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="C133" t="s">
-        <v>337</v>
+        <v>206</v>
       </c>
       <c r="E133" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="F133">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G133" t="s">
-        <v>215</v>
+        <v>36</v>
       </c>
       <c r="H133" t="s">
-        <v>215</v>
+        <v>36</v>
       </c>
       <c r="I133" t="s">
-        <v>251</v>
+        <v>379</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>376</v>
+        <v>339</v>
       </c>
       <c r="B134" t="s">
-        <v>377</v>
+        <v>340</v>
+      </c>
+      <c r="C134" t="s">
+        <v>206</v>
       </c>
       <c r="E134" t="s">
-        <v>378</v>
+        <v>223</v>
       </c>
       <c r="F134">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G134" t="s">
-        <v>379</v>
+        <v>36</v>
       </c>
       <c r="H134" t="s">
-        <v>380</v>
+        <v>36</v>
       </c>
       <c r="I134" t="s">
-        <v>381</v>
+        <v>316</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
+        <v>380</v>
+      </c>
+      <c r="B135" t="s">
+        <v>381</v>
+      </c>
+      <c r="E135" t="s">
         <v>382</v>
-      </c>
-      <c r="B135" t="s">
-        <v>383</v>
-      </c>
-      <c r="C135" t="s">
-        <v>207</v>
-      </c>
-      <c r="E135" t="s">
-        <v>232</v>
       </c>
       <c r="F135">
         <v>2.0</v>
       </c>
       <c r="G135" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="H135" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="I135" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>344</v>
+        <v>276</v>
       </c>
       <c r="B136" t="s">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="C136" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="E136" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="F136">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G136" t="s">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="H136" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="I136" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
+        <v>384</v>
+      </c>
+      <c r="B137" t="s">
         <v>385</v>
       </c>
-      <c r="B137" t="s">
+      <c r="E137" t="s">
         <v>386</v>
-      </c>
-      <c r="E137" t="s">
-        <v>387</v>
       </c>
       <c r="F137">
         <v>2.0</v>
       </c>
       <c r="G137" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="H137" t="s">
-        <v>134</v>
+        <v>257</v>
       </c>
       <c r="I137" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>280</v>
+        <v>388</v>
       </c>
       <c r="B138" t="s">
-        <v>281</v>
-      </c>
-      <c r="C138" t="s">
-        <v>248</v>
+        <v>389</v>
       </c>
       <c r="E138" t="s">
-        <v>283</v>
+        <v>386</v>
       </c>
       <c r="F138">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G138" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H138" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="I138" t="s">
-        <v>347</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B139" t="s">
-        <v>390</v>
+        <v>391</v>
+      </c>
+      <c r="C139" t="s">
+        <v>244</v>
       </c>
       <c r="E139" t="s">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="F139">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G139" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H139" t="s">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="I139" t="s">
         <v>392</v>
@@ -5752,123 +5734,126 @@
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="B140" t="s">
-        <v>394</v>
+        <v>370</v>
+      </c>
+      <c r="C140" t="s">
+        <v>343</v>
       </c>
       <c r="E140" t="s">
-        <v>391</v>
+        <v>279</v>
       </c>
       <c r="F140">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G140" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H140" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="I140" t="s">
-        <v>392</v>
+        <v>247</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B141" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C141" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="E141" t="s">
-        <v>363</v>
+        <v>237</v>
       </c>
       <c r="F141">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G141" t="s">
-        <v>215</v>
+        <v>36</v>
       </c>
       <c r="H141" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="I141" t="s">
-        <v>397</v>
+        <v>168</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="B142" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="C142" t="s">
-        <v>348</v>
+        <v>244</v>
       </c>
       <c r="E142" t="s">
-        <v>283</v>
+        <v>350</v>
       </c>
       <c r="F142">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G142" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H142" t="s">
-        <v>215</v>
+        <v>395</v>
       </c>
       <c r="I142" t="s">
-        <v>251</v>
+        <v>396</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
+        <v>397</v>
+      </c>
+      <c r="B143" t="s">
         <v>398</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
+        <v>173</v>
+      </c>
+      <c r="E143" t="s">
+        <v>223</v>
+      </c>
+      <c r="F143">
+        <v>1.0</v>
+      </c>
+      <c r="G143" t="s">
+        <v>36</v>
+      </c>
+      <c r="H143" t="s">
+        <v>36</v>
+      </c>
+      <c r="I143" t="s">
         <v>399</v>
-      </c>
-      <c r="C143" t="s">
-        <v>207</v>
-      </c>
-      <c r="E143" t="s">
-        <v>240</v>
-      </c>
-      <c r="F143">
-        <v>1.0</v>
-      </c>
-      <c r="G143" t="s">
-        <v>36</v>
-      </c>
-      <c r="H143" t="s">
-        <v>36</v>
-      </c>
-      <c r="I143" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B144" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C144" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E144" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F144">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G144" t="s">
-        <v>215</v>
+        <v>359</v>
       </c>
       <c r="H144" t="s">
         <v>400</v>
@@ -5879,181 +5864,178 @@
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>349</v>
+        <v>390</v>
       </c>
       <c r="B145" t="s">
+        <v>391</v>
+      </c>
+      <c r="C145" t="s">
+        <v>278</v>
+      </c>
+      <c r="E145" t="s">
         <v>350</v>
       </c>
-      <c r="C145" t="s">
-        <v>266</v>
-      </c>
-      <c r="E145" t="s">
-        <v>351</v>
-      </c>
       <c r="F145">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="s">
-        <v>352</v>
+        <v>214</v>
       </c>
       <c r="H145" t="s">
+        <v>214</v>
+      </c>
+      <c r="I145" t="s">
         <v>402</v>
-      </c>
-      <c r="I145" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>404</v>
+        <v>227</v>
       </c>
       <c r="B146" t="s">
-        <v>405</v>
+        <v>228</v>
       </c>
       <c r="C146" t="s">
         <v>173</v>
       </c>
       <c r="E146" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F146">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G146" t="s">
-        <v>36</v>
+        <v>403</v>
       </c>
       <c r="H146" t="s">
-        <v>36</v>
+        <v>404</v>
       </c>
       <c r="I146" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B147" t="s">
-        <v>396</v>
-      </c>
-      <c r="C147" t="s">
-        <v>282</v>
+        <v>407</v>
       </c>
       <c r="E147" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="F147">
         <v>1.0</v>
       </c>
       <c r="G147" t="s">
-        <v>215</v>
+        <v>36</v>
       </c>
       <c r="H147" t="s">
-        <v>215</v>
+        <v>36</v>
       </c>
       <c r="I147" t="s">
-        <v>407</v>
+        <v>347</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>230</v>
+        <v>408</v>
       </c>
       <c r="B148" t="s">
-        <v>231</v>
+        <v>409</v>
       </c>
       <c r="C148" t="s">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="E148" t="s">
-        <v>232</v>
+        <v>350</v>
       </c>
       <c r="F148">
         <v>4.0</v>
       </c>
       <c r="G148" t="s">
-        <v>408</v>
+        <v>214</v>
       </c>
       <c r="H148" t="s">
-        <v>409</v>
+        <v>304</v>
       </c>
       <c r="I148" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
+        <v>410</v>
+      </c>
+      <c r="B149" t="s">
         <v>411</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
+        <v>343</v>
+      </c>
+      <c r="E149" t="s">
         <v>412</v>
       </c>
-      <c r="E149" t="s">
-        <v>163</v>
-      </c>
       <c r="F149">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G149" t="s">
-        <v>36</v>
+        <v>413</v>
       </c>
       <c r="H149" t="s">
-        <v>36</v>
+        <v>414</v>
       </c>
       <c r="I149" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B150" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C150" t="s">
-        <v>337</v>
+        <v>262</v>
       </c>
       <c r="E150" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="F150">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G150" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H150" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="I150" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B151" t="s">
-        <v>416</v>
-      </c>
-      <c r="C151" t="s">
-        <v>248</v>
+        <v>418</v>
       </c>
       <c r="E151" t="s">
-        <v>351</v>
+        <v>171</v>
       </c>
       <c r="F151">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G151" t="s">
-        <v>352</v>
+        <v>133</v>
       </c>
       <c r="H151" t="s">
-        <v>417</v>
+        <v>325</v>
       </c>
       <c r="I151" t="s">
-        <v>418</v>
+        <v>355</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -6063,46 +6045,43 @@
       <c r="B152" t="s">
         <v>420</v>
       </c>
-      <c r="C152" t="s">
-        <v>348</v>
-      </c>
       <c r="E152" t="s">
         <v>421</v>
       </c>
       <c r="F152">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="s">
-        <v>422</v>
+        <v>36</v>
       </c>
       <c r="H152" t="s">
-        <v>423</v>
+        <v>36</v>
       </c>
       <c r="I152" t="s">
-        <v>424</v>
+        <v>347</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B153" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C153" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E153" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F153">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G153" t="s">
-        <v>215</v>
+        <v>359</v>
       </c>
       <c r="H153" t="s">
-        <v>261</v>
+        <v>424</v>
       </c>
       <c r="I153" t="s">
         <v>425</v>
@@ -6115,40 +6094,43 @@
       <c r="B154" t="s">
         <v>427</v>
       </c>
+      <c r="C154" t="s">
+        <v>173</v>
+      </c>
       <c r="E154" t="s">
-        <v>171</v>
+        <v>269</v>
       </c>
       <c r="F154">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G154" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="H154" t="s">
-        <v>330</v>
+        <v>36</v>
       </c>
       <c r="I154" t="s">
-        <v>368</v>
+        <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="B155" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>332</v>
       </c>
       <c r="E155" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F155">
         <v>2.0</v>
       </c>
       <c r="G155" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="H155" t="s">
         <v>428</v>
@@ -6159,464 +6141,467 @@
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
+        <v>364</v>
+      </c>
+      <c r="B156" t="s">
+        <v>365</v>
+      </c>
+      <c r="C156" t="s">
+        <v>262</v>
+      </c>
+      <c r="E156" t="s">
+        <v>358</v>
+      </c>
+      <c r="F156">
+        <v>2.0</v>
+      </c>
+      <c r="G156" t="s">
+        <v>366</v>
+      </c>
+      <c r="H156" t="s">
         <v>430</v>
       </c>
-      <c r="B156" t="s">
+      <c r="I156" t="s">
         <v>431</v>
-      </c>
-      <c r="E156" t="s">
-        <v>432</v>
-      </c>
-      <c r="F156">
-        <v>1.0</v>
-      </c>
-      <c r="G156" t="s">
-        <v>36</v>
-      </c>
-      <c r="H156" t="s">
-        <v>36</v>
-      </c>
-      <c r="I156" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
+        <v>432</v>
+      </c>
+      <c r="B157" t="s">
         <v>433</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
+        <v>182</v>
+      </c>
+      <c r="E157" t="s">
         <v>434</v>
       </c>
-      <c r="C157" t="s">
-        <v>248</v>
-      </c>
-      <c r="E157" t="s">
-        <v>351</v>
-      </c>
       <c r="F157">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G157" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H157" t="s">
+        <v>36</v>
+      </c>
+      <c r="I157" t="s">
         <v>435</v>
-      </c>
-      <c r="I157" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="B158" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="C158" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E158" t="s">
-        <v>273</v>
+        <v>350</v>
       </c>
       <c r="F158">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G158" t="s">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="H158" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="I158" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="B159" t="s">
-        <v>350</v>
+        <v>437</v>
       </c>
       <c r="C159" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="E159" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F159">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G159" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H159" t="s">
         <v>438</v>
       </c>
       <c r="I159" t="s">
-        <v>439</v>
+        <v>368</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
+        <v>410</v>
+      </c>
+      <c r="B160" t="s">
+        <v>411</v>
+      </c>
+      <c r="C160" t="s">
+        <v>244</v>
+      </c>
+      <c r="E160" t="s">
+        <v>412</v>
+      </c>
+      <c r="F160">
+        <v>6.0</v>
+      </c>
+      <c r="G160" t="s">
+        <v>439</v>
+      </c>
+      <c r="H160" t="s">
         <v>440</v>
       </c>
-      <c r="B160" t="s">
+      <c r="I160" t="s">
         <v>441</v>
-      </c>
-      <c r="C160" t="s">
-        <v>248</v>
-      </c>
-      <c r="E160" t="s">
-        <v>351</v>
-      </c>
-      <c r="F160">
-        <v>7.0</v>
-      </c>
-      <c r="G160" t="s">
-        <v>352</v>
-      </c>
-      <c r="H160" t="s">
-        <v>417</v>
-      </c>
-      <c r="I160" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>443</v>
+        <v>364</v>
       </c>
       <c r="B161" t="s">
-        <v>444</v>
+        <v>365</v>
       </c>
       <c r="C161" t="s">
-        <v>182</v>
+        <v>343</v>
       </c>
       <c r="E161" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F161">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G161" t="s">
-        <v>36</v>
+        <v>366</v>
       </c>
       <c r="H161" t="s">
-        <v>36</v>
+        <v>430</v>
       </c>
       <c r="I161" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="B162" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C162" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="E162" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F162">
         <v>2.0</v>
       </c>
       <c r="G162" t="s">
-        <v>371</v>
+        <v>214</v>
       </c>
       <c r="H162" t="s">
-        <v>428</v>
+        <v>257</v>
       </c>
       <c r="I162" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>413</v>
+        <v>348</v>
       </c>
       <c r="B163" t="s">
-        <v>414</v>
+        <v>349</v>
       </c>
       <c r="C163" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E163" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="F163">
         <v>4.0</v>
       </c>
       <c r="G163" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H163" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I163" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="B164" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C164" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E164" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="F164">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G164" t="s">
-        <v>447</v>
+        <v>359</v>
       </c>
       <c r="H164" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="I164" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B165" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C165" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E165" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F165">
         <v>1.0</v>
       </c>
       <c r="G165" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H165" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I165" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="B166" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C166" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="E166" t="s">
-        <v>363</v>
+        <v>412</v>
       </c>
       <c r="F166">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166" t="s">
-        <v>215</v>
+        <v>439</v>
       </c>
       <c r="H166" t="s">
-        <v>261</v>
+        <v>439</v>
       </c>
       <c r="I166" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B167" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C167" t="s">
-        <v>266</v>
+        <v>332</v>
       </c>
       <c r="E167" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F167">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G167" t="s">
-        <v>215</v>
+        <v>366</v>
       </c>
       <c r="H167" t="s">
-        <v>309</v>
+        <v>430</v>
       </c>
       <c r="I167" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>369</v>
+        <v>436</v>
       </c>
       <c r="B168" t="s">
-        <v>370</v>
+        <v>437</v>
       </c>
       <c r="C168" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E168" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F168">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G168" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="H168" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="I168" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="B169" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="C169" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E169" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="F169">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G169" t="s">
-        <v>447</v>
+        <v>366</v>
       </c>
       <c r="H169" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="I169" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B170" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C170" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E170" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F170">
         <v>3.0</v>
       </c>
       <c r="G170" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H170" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I170" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B171" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="C171" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="E171" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F171">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G171" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H171" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="I171" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="B172" t="s">
-        <v>416</v>
+        <v>451</v>
       </c>
       <c r="C172" t="s">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="E172" t="s">
-        <v>351</v>
+        <v>177</v>
       </c>
       <c r="F172">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G172" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H172" t="s">
-        <v>417</v>
+        <v>36</v>
       </c>
       <c r="I172" t="s">
-        <v>418</v>
+        <v>179</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="B173" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="C173" t="s">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="E173" t="s">
-        <v>351</v>
+        <v>434</v>
       </c>
       <c r="F173">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G173" t="s">
-        <v>371</v>
+        <v>452</v>
       </c>
       <c r="H173" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="I173" t="s">
         <v>454</v>
@@ -6624,25 +6609,25 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C174" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E174" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F174">
         <v>5.0</v>
       </c>
       <c r="G174" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H174" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="I174" t="s">
         <v>455</v>
@@ -6650,770 +6635,770 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
+        <v>267</v>
+      </c>
+      <c r="B175" t="s">
+        <v>268</v>
+      </c>
+      <c r="C175" t="s">
+        <v>206</v>
+      </c>
+      <c r="E175" t="s">
+        <v>269</v>
+      </c>
+      <c r="F175">
+        <v>3.0</v>
+      </c>
+      <c r="G175" t="s">
+        <v>36</v>
+      </c>
+      <c r="H175" t="s">
+        <v>36</v>
+      </c>
+      <c r="I175" t="s">
         <v>456</v>
-      </c>
-      <c r="B175" t="s">
-        <v>457</v>
-      </c>
-      <c r="C175" t="s">
-        <v>182</v>
-      </c>
-      <c r="E175" t="s">
-        <v>177</v>
-      </c>
-      <c r="F175">
-        <v>4.0</v>
-      </c>
-      <c r="G175" t="s">
-        <v>36</v>
-      </c>
-      <c r="H175" t="s">
-        <v>36</v>
-      </c>
-      <c r="I175" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="B176" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="C176" t="s">
-        <v>138</v>
+        <v>332</v>
       </c>
       <c r="E176" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="F176">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G176" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="H176" t="s">
+        <v>366</v>
+      </c>
+      <c r="I176" t="s">
         <v>459</v>
-      </c>
-      <c r="I176" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>271</v>
+        <v>410</v>
       </c>
       <c r="B177" t="s">
-        <v>272</v>
+        <v>411</v>
       </c>
       <c r="C177" t="s">
-        <v>207</v>
+        <v>332</v>
       </c>
       <c r="E177" t="s">
-        <v>273</v>
+        <v>412</v>
       </c>
       <c r="F177">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G177" t="s">
-        <v>36</v>
+        <v>439</v>
       </c>
       <c r="H177" t="s">
-        <v>36</v>
+        <v>366</v>
       </c>
       <c r="I177" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>462</v>
+        <v>356</v>
       </c>
       <c r="B178" t="s">
-        <v>463</v>
+        <v>357</v>
       </c>
       <c r="C178" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E178" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="F178">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G178" t="s">
-        <v>447</v>
+        <v>359</v>
       </c>
       <c r="H178" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="I178" t="s">
-        <v>464</v>
+        <v>401</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="B179" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="C179" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E179" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F179">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G179" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="H179" t="s">
-        <v>371</v>
+        <v>439</v>
       </c>
       <c r="I179" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="B180" t="s">
+        <v>409</v>
+      </c>
+      <c r="C180" t="s">
+        <v>343</v>
+      </c>
+      <c r="E180" t="s">
         <v>350</v>
       </c>
-      <c r="C180" t="s">
-        <v>348</v>
-      </c>
-      <c r="E180" t="s">
-        <v>351</v>
-      </c>
       <c r="F180">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G180" t="s">
-        <v>352</v>
+        <v>463</v>
       </c>
       <c r="H180" t="s">
-        <v>402</v>
+        <v>214</v>
       </c>
       <c r="I180" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
+        <v>464</v>
+      </c>
+      <c r="B181" t="s">
         <v>465</v>
       </c>
-      <c r="B181" t="s">
-        <v>466</v>
-      </c>
       <c r="C181" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="E181" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="F181">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G181" t="s">
-        <v>447</v>
+        <v>366</v>
       </c>
       <c r="H181" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="I181" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="B182" t="s">
-        <v>414</v>
+        <v>467</v>
       </c>
       <c r="C182" t="s">
-        <v>348</v>
+        <v>182</v>
       </c>
       <c r="E182" t="s">
-        <v>363</v>
+        <v>434</v>
       </c>
       <c r="F182">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G182" t="s">
-        <v>468</v>
+        <v>36</v>
       </c>
       <c r="H182" t="s">
-        <v>215</v>
+        <v>36</v>
       </c>
       <c r="I182" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>469</v>
+        <v>314</v>
       </c>
       <c r="B183" t="s">
-        <v>470</v>
+        <v>315</v>
       </c>
       <c r="C183" t="s">
-        <v>248</v>
+        <v>173</v>
       </c>
       <c r="E183" t="s">
-        <v>351</v>
+        <v>223</v>
       </c>
       <c r="F183">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G183" t="s">
-        <v>371</v>
+        <v>36</v>
       </c>
       <c r="H183" t="s">
-        <v>428</v>
+        <v>36</v>
       </c>
       <c r="I183" t="s">
-        <v>454</v>
+        <v>316</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="B184" t="s">
-        <v>472</v>
+        <v>391</v>
       </c>
       <c r="C184" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E184" t="s">
-        <v>445</v>
+        <v>350</v>
       </c>
       <c r="F184">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G184" t="s">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="H184" t="s">
-        <v>36</v>
+        <v>257</v>
       </c>
       <c r="I184" t="s">
-        <v>467</v>
+        <v>416</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B185" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C185" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E185" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F185">
         <v>2.0</v>
       </c>
       <c r="G185" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H185" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I185" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>319</v>
+        <v>445</v>
       </c>
       <c r="B186" t="s">
-        <v>320</v>
+        <v>446</v>
       </c>
       <c r="C186" t="s">
-        <v>173</v>
+        <v>343</v>
       </c>
       <c r="E186" t="s">
-        <v>226</v>
+        <v>358</v>
       </c>
       <c r="F186">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G186" t="s">
-        <v>36</v>
+        <v>366</v>
       </c>
       <c r="H186" t="s">
-        <v>36</v>
+        <v>430</v>
       </c>
       <c r="I186" t="s">
-        <v>321</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>395</v>
+        <v>445</v>
       </c>
       <c r="B187" t="s">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="C187" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E187" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F187">
         <v>2.0</v>
       </c>
       <c r="G187" t="s">
-        <v>215</v>
+        <v>366</v>
       </c>
       <c r="H187" t="s">
-        <v>261</v>
+        <v>430</v>
       </c>
       <c r="I187" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B188" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C188" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="E188" t="s">
-        <v>351</v>
+        <v>434</v>
       </c>
       <c r="F188">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G188" t="s">
-        <v>371</v>
+        <v>36</v>
       </c>
       <c r="H188" t="s">
-        <v>371</v>
+        <v>36</v>
       </c>
       <c r="I188" t="s">
-        <v>262</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B189" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C189" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E189" t="s">
-        <v>351</v>
+        <v>412</v>
       </c>
       <c r="F189">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G189" t="s">
-        <v>371</v>
+        <v>439</v>
       </c>
       <c r="H189" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="I189" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="B190" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="C190" t="s">
-        <v>337</v>
+        <v>206</v>
       </c>
       <c r="E190" t="s">
-        <v>351</v>
+        <v>434</v>
       </c>
       <c r="F190">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G190" t="s">
-        <v>371</v>
+        <v>36</v>
       </c>
       <c r="H190" t="s">
-        <v>428</v>
+        <v>36</v>
       </c>
       <c r="I190" t="s">
-        <v>454</v>
+        <v>396</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>433</v>
+        <v>348</v>
       </c>
       <c r="B191" t="s">
-        <v>434</v>
+        <v>349</v>
       </c>
       <c r="C191" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E191" t="s">
+        <v>350</v>
+      </c>
+      <c r="F191">
+        <v>3.0</v>
+      </c>
+      <c r="G191" t="s">
+        <v>214</v>
+      </c>
+      <c r="H191" t="s">
         <v>351</v>
       </c>
-      <c r="F191">
-        <v>2.0</v>
-      </c>
-      <c r="G191" t="s">
+      <c r="I191" t="s">
         <v>352</v>
-      </c>
-      <c r="H191" t="s">
-        <v>438</v>
-      </c>
-      <c r="I191" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B192" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C192" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="E192" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F192">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G192" t="s">
-        <v>36</v>
+        <v>366</v>
       </c>
       <c r="H192" t="s">
-        <v>36</v>
+        <v>366</v>
       </c>
       <c r="I192" t="s">
-        <v>460</v>
+        <v>258</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="B193" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="C193" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="E193" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="F193">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G193" t="s">
-        <v>447</v>
+        <v>359</v>
       </c>
       <c r="H193" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="I193" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>471</v>
+        <v>422</v>
       </c>
       <c r="B194" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="C194" t="s">
-        <v>207</v>
+        <v>343</v>
       </c>
       <c r="E194" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F194">
         <v>5.0</v>
       </c>
       <c r="G194" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="H194" t="s">
-        <v>36</v>
+        <v>360</v>
       </c>
       <c r="I194" t="s">
-        <v>401</v>
+        <v>361</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>361</v>
+        <v>410</v>
       </c>
       <c r="B195" t="s">
-        <v>362</v>
+        <v>411</v>
       </c>
       <c r="C195" t="s">
-        <v>337</v>
+        <v>262</v>
       </c>
       <c r="E195" t="s">
-        <v>363</v>
+        <v>412</v>
       </c>
       <c r="F195">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G195" t="s">
-        <v>215</v>
+        <v>474</v>
       </c>
       <c r="H195" t="s">
-        <v>364</v>
+        <v>475</v>
       </c>
       <c r="I195" t="s">
-        <v>365</v>
+        <v>454</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>415</v>
+        <v>364</v>
       </c>
       <c r="B196" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="C196" t="s">
-        <v>348</v>
+        <v>278</v>
       </c>
       <c r="E196" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F196">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G196" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="H196" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="I196" t="s">
-        <v>354</v>
+        <v>476</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="B197" t="s">
+        <v>469</v>
+      </c>
+      <c r="C197" t="s">
+        <v>343</v>
+      </c>
+      <c r="E197" t="s">
+        <v>358</v>
+      </c>
+      <c r="F197">
+        <v>1.0</v>
+      </c>
+      <c r="G197" t="s">
+        <v>366</v>
+      </c>
+      <c r="H197" t="s">
+        <v>366</v>
+      </c>
+      <c r="I197" t="s">
         <v>476</v>
-      </c>
-      <c r="C197" t="s">
-        <v>266</v>
-      </c>
-      <c r="E197" t="s">
-        <v>351</v>
-      </c>
-      <c r="F197">
-        <v>2.0</v>
-      </c>
-      <c r="G197" t="s">
-        <v>371</v>
-      </c>
-      <c r="H197" t="s">
-        <v>428</v>
-      </c>
-      <c r="I197" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
       <c r="B198" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
       <c r="C198" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E198" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F198">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G198" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H198" t="s">
-        <v>371</v>
+        <v>430</v>
       </c>
       <c r="I198" t="s">
-        <v>479</v>
+        <v>429</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>419</v>
+        <v>477</v>
       </c>
       <c r="B199" t="s">
-        <v>420</v>
-      </c>
-      <c r="C199" t="s">
-        <v>266</v>
+        <v>478</v>
       </c>
       <c r="E199" t="s">
-        <v>421</v>
+        <v>479</v>
       </c>
       <c r="F199">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G199" t="s">
         <v>480</v>
       </c>
       <c r="H199" t="s">
-        <v>481</v>
+        <v>108</v>
       </c>
       <c r="I199" t="s">
-        <v>460</v>
+        <v>383</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B200" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C200" t="s">
-        <v>348</v>
+        <v>206</v>
       </c>
       <c r="E200" t="s">
-        <v>351</v>
+        <v>434</v>
       </c>
       <c r="F200">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G200" t="s">
-        <v>371</v>
+        <v>483</v>
       </c>
       <c r="H200" t="s">
-        <v>371</v>
+        <v>484</v>
       </c>
       <c r="I200" t="s">
-        <v>479</v>
+        <v>454</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B201" t="s">
-        <v>483</v>
+        <v>486</v>
+      </c>
+      <c r="C201" t="s">
+        <v>206</v>
       </c>
       <c r="E201" t="s">
-        <v>484</v>
+        <v>434</v>
       </c>
       <c r="F201">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G201" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H201" t="s">
-        <v>108</v>
+        <v>488</v>
       </c>
       <c r="I201" t="s">
-        <v>388</v>
+        <v>454</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B202" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C202" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="E202" t="s">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="F202">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G202" t="s">
-        <v>488</v>
+        <v>36</v>
       </c>
       <c r="H202" t="s">
-        <v>489</v>
+        <v>36</v>
       </c>
       <c r="I202" t="s">
-        <v>460</v>
+        <v>399</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B203" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C203" t="s">
-        <v>207</v>
+        <v>332</v>
       </c>
       <c r="E203" t="s">
-        <v>445</v>
+        <v>493</v>
       </c>
       <c r="F203">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G203" t="s">
-        <v>492</v>
+        <v>36</v>
       </c>
       <c r="H203" t="s">
-        <v>493</v>
+        <v>36</v>
       </c>
       <c r="I203" t="s">
-        <v>460</v>
+        <v>494</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B204" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C204" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E204" t="s">
-        <v>226</v>
+        <v>434</v>
       </c>
       <c r="F204">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G204" t="s">
         <v>36</v>
@@ -7422,30 +7407,30 @@
         <v>36</v>
       </c>
       <c r="I204" t="s">
-        <v>406</v>
+        <v>352</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B205" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C205" t="s">
-        <v>337</v>
+        <v>206</v>
       </c>
       <c r="E205" t="s">
-        <v>498</v>
+        <v>434</v>
       </c>
       <c r="F205">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G205" t="s">
-        <v>36</v>
+        <v>463</v>
       </c>
       <c r="H205" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="I205" t="s">
         <v>499</v>
@@ -7453,461 +7438,461 @@
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
+        <v>457</v>
+      </c>
+      <c r="B206" t="s">
+        <v>458</v>
+      </c>
+      <c r="C206" t="s">
+        <v>244</v>
+      </c>
+      <c r="E206" t="s">
+        <v>412</v>
+      </c>
+      <c r="F206">
+        <v>1.0</v>
+      </c>
+      <c r="G206" t="s">
         <v>500</v>
       </c>
-      <c r="B206" t="s">
-        <v>501</v>
-      </c>
-      <c r="C206" t="s">
-        <v>173</v>
-      </c>
-      <c r="E206" t="s">
-        <v>445</v>
-      </c>
-      <c r="F206">
-        <v>3.0</v>
-      </c>
-      <c r="G206" t="s">
-        <v>36</v>
-      </c>
       <c r="H206" t="s">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="I206" t="s">
-        <v>365</v>
+        <v>435</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>415</v>
+        <v>501</v>
       </c>
       <c r="B207" t="s">
-        <v>416</v>
+        <v>502</v>
       </c>
       <c r="C207" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E207" t="s">
-        <v>351</v>
+        <v>412</v>
       </c>
       <c r="F207">
         <v>3.0</v>
       </c>
       <c r="G207" t="s">
-        <v>352</v>
+        <v>439</v>
       </c>
       <c r="H207" t="s">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="I207" t="s">
-        <v>403</v>
+        <v>503</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>502</v>
+        <v>422</v>
       </c>
       <c r="B208" t="s">
-        <v>503</v>
+        <v>423</v>
       </c>
       <c r="C208" t="s">
-        <v>207</v>
+        <v>332</v>
       </c>
       <c r="E208" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F208">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G208" t="s">
-        <v>468</v>
+        <v>359</v>
       </c>
       <c r="H208" t="s">
-        <v>309</v>
+        <v>400</v>
       </c>
       <c r="I208" t="s">
-        <v>504</v>
+        <v>401</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="B209" t="s">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="C209" t="s">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="E209" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="F209">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G209" t="s">
-        <v>505</v>
+        <v>359</v>
       </c>
       <c r="H209" t="s">
-        <v>506</v>
+        <v>438</v>
       </c>
       <c r="I209" t="s">
-        <v>464</v>
+        <v>368</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>507</v>
+        <v>339</v>
       </c>
       <c r="B210" t="s">
-        <v>508</v>
+        <v>340</v>
       </c>
       <c r="C210" t="s">
-        <v>337</v>
+        <v>182</v>
       </c>
       <c r="E210" t="s">
-        <v>421</v>
+        <v>223</v>
       </c>
       <c r="F210">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G210" t="s">
-        <v>447</v>
+        <v>36</v>
       </c>
       <c r="H210" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="I210" t="s">
-        <v>509</v>
+        <v>399</v>
       </c>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>440</v>
+        <v>504</v>
       </c>
       <c r="B211" t="s">
-        <v>441</v>
+        <v>505</v>
       </c>
       <c r="C211" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="E211" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F211">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G211" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H211" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="I211" t="s">
-        <v>373</v>
+        <v>506</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B212" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C212" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="E212" t="s">
-        <v>351</v>
+        <v>434</v>
       </c>
       <c r="F212">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G212" t="s">
-        <v>352</v>
+        <v>483</v>
       </c>
       <c r="H212" t="s">
-        <v>402</v>
+        <v>484</v>
       </c>
       <c r="I212" t="s">
-        <v>512</v>
+        <v>429</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>344</v>
+        <v>501</v>
       </c>
       <c r="B213" t="s">
-        <v>345</v>
+        <v>502</v>
       </c>
       <c r="C213" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="E213" t="s">
-        <v>226</v>
+        <v>412</v>
       </c>
       <c r="F213">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G213" t="s">
-        <v>36</v>
+        <v>439</v>
       </c>
       <c r="H213" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I213" t="s">
-        <v>406</v>
+        <v>509</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>513</v>
+        <v>470</v>
       </c>
       <c r="B214" t="s">
-        <v>514</v>
+        <v>471</v>
       </c>
       <c r="C214" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="E214" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="F214">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G214" t="s">
-        <v>488</v>
+        <v>36</v>
       </c>
       <c r="H214" t="s">
-        <v>489</v>
+        <v>36</v>
       </c>
       <c r="I214" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>507</v>
+        <v>460</v>
       </c>
       <c r="B215" t="s">
-        <v>508</v>
+        <v>461</v>
       </c>
       <c r="C215" t="s">
-        <v>248</v>
+        <v>343</v>
       </c>
       <c r="E215" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F215">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G215" t="s">
-        <v>447</v>
+        <v>510</v>
       </c>
       <c r="H215" t="s">
-        <v>52</v>
+        <v>484</v>
       </c>
       <c r="I215" t="s">
-        <v>515</v>
+        <v>258</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="B216" t="s">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="C216" t="s">
-        <v>182</v>
+        <v>343</v>
       </c>
       <c r="E216" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F216">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G216" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="H216" t="s">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="I216" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="B217" t="s">
-        <v>466</v>
+        <v>433</v>
       </c>
       <c r="C217" t="s">
-        <v>348</v>
+        <v>206</v>
       </c>
       <c r="E217" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F217">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G217" t="s">
-        <v>516</v>
+        <v>36</v>
       </c>
       <c r="H217" t="s">
-        <v>489</v>
+        <v>36</v>
       </c>
       <c r="I217" t="s">
-        <v>262</v>
+        <v>511</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="B218" t="s">
-        <v>441</v>
+        <v>502</v>
       </c>
       <c r="C218" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="E218" t="s">
-        <v>351</v>
+        <v>412</v>
       </c>
       <c r="F218">
         <v>3.0</v>
       </c>
       <c r="G218" t="s">
-        <v>352</v>
+        <v>439</v>
       </c>
       <c r="H218" t="s">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="I218" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="B219" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="C219" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="E219" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="F219">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G219" t="s">
-        <v>36</v>
+        <v>512</v>
       </c>
       <c r="H219" t="s">
-        <v>36</v>
+        <v>513</v>
       </c>
       <c r="I219" t="s">
-        <v>517</v>
+        <v>429</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="B220" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C220" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="E220" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F220">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G220" t="s">
-        <v>447</v>
+        <v>36</v>
       </c>
       <c r="H220" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="I220" t="s">
-        <v>509</v>
+        <v>429</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="B221" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="C221" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="E221" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F221">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G221" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="H221" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="I221" t="s">
-        <v>401</v>
+        <v>352</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B222" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C222" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E222" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F222">
         <v>2.0</v>
       </c>
       <c r="G222" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H222" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="I222" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="B223" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="C223" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="E223" t="s">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="F223">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G223" t="s">
         <v>36</v>
@@ -7916,544 +7901,544 @@
         <v>36</v>
       </c>
       <c r="I223" t="s">
-        <v>439</v>
+        <v>399</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="B224" t="s">
-        <v>503</v>
+        <v>469</v>
       </c>
       <c r="C224" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="E224" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F224">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G224" t="s">
-        <v>516</v>
+        <v>366</v>
       </c>
       <c r="H224" t="s">
-        <v>520</v>
+        <v>366</v>
       </c>
       <c r="I224" t="s">
-        <v>365</v>
+        <v>476</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B225" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C225" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E225" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F225">
         <v>1.0</v>
       </c>
       <c r="G225" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H225" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I225" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>473</v>
+        <v>517</v>
       </c>
       <c r="B226" t="s">
-        <v>474</v>
+        <v>518</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E226" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F226">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G226" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="H226" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="I226" t="s">
-        <v>479</v>
+        <v>519</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="B227" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="C227" t="s">
         <v>138</v>
       </c>
       <c r="E227" t="s">
-        <v>226</v>
+        <v>434</v>
       </c>
       <c r="F227">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="G227" t="s">
-        <v>36</v>
+        <v>217</v>
       </c>
       <c r="H227" t="s">
-        <v>36</v>
+        <v>520</v>
       </c>
       <c r="I227" t="s">
-        <v>406</v>
+        <v>521</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="B228" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="C228" t="s">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="E228" t="s">
-        <v>351</v>
+        <v>223</v>
       </c>
       <c r="F228">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G228" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H228" t="s">
-        <v>438</v>
+        <v>36</v>
       </c>
       <c r="I228" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>513</v>
+        <v>464</v>
       </c>
       <c r="B229" t="s">
-        <v>514</v>
+        <v>465</v>
       </c>
       <c r="C229" t="s">
-        <v>138</v>
+        <v>343</v>
       </c>
       <c r="E229" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F229">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="G229" t="s">
-        <v>220</v>
+        <v>366</v>
       </c>
       <c r="H229" t="s">
-        <v>526</v>
+        <v>366</v>
       </c>
       <c r="I229" t="s">
-        <v>527</v>
+        <v>447</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="B230" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="C230" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="E230" t="s">
-        <v>226</v>
+        <v>358</v>
       </c>
       <c r="F230">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G230" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="H230" t="s">
-        <v>36</v>
+        <v>428</v>
       </c>
       <c r="I230" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
+        <v>468</v>
+      </c>
+      <c r="B231" t="s">
         <v>469</v>
       </c>
-      <c r="B231" t="s">
-        <v>470</v>
-      </c>
       <c r="C231" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="E231" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F231">
         <v>1.0</v>
       </c>
       <c r="G231" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H231" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I231" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="B232" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="C232" t="s">
-        <v>337</v>
+        <v>262</v>
       </c>
       <c r="E232" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F232">
         <v>1.0</v>
       </c>
       <c r="G232" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="H232" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="I232" t="s">
-        <v>479</v>
+        <v>523</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B233" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C233" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="E233" t="s">
-        <v>351</v>
+        <v>434</v>
       </c>
       <c r="F233">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G233" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H233" t="s">
-        <v>438</v>
+        <v>36</v>
       </c>
       <c r="I233" t="s">
-        <v>525</v>
+        <v>454</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>510</v>
+        <v>466</v>
       </c>
       <c r="B234" t="s">
-        <v>511</v>
+        <v>467</v>
       </c>
       <c r="C234" t="s">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="E234" t="s">
-        <v>351</v>
+        <v>434</v>
       </c>
       <c r="F234">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G234" t="s">
-        <v>352</v>
+        <v>526</v>
       </c>
       <c r="H234" t="s">
-        <v>352</v>
+        <v>52</v>
       </c>
       <c r="I234" t="s">
-        <v>529</v>
+        <v>361</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>530</v>
+        <v>497</v>
       </c>
       <c r="B235" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="C235" t="s">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="E235" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="F235">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="G235" t="s">
-        <v>36</v>
+        <v>526</v>
       </c>
       <c r="H235" t="s">
-        <v>36</v>
+        <v>527</v>
       </c>
       <c r="I235" t="s">
-        <v>460</v>
+        <v>521</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B236" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C236" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E236" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="F236">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G236" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H236" t="s">
-        <v>52</v>
+        <v>529</v>
       </c>
       <c r="I236" t="s">
-        <v>354</v>
+        <v>258</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>502</v>
+        <v>422</v>
       </c>
       <c r="B237" t="s">
-        <v>503</v>
+        <v>423</v>
       </c>
       <c r="C237" t="s">
-        <v>148</v>
+        <v>278</v>
       </c>
       <c r="E237" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F237">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G237" t="s">
-        <v>532</v>
+        <v>359</v>
       </c>
       <c r="H237" t="s">
-        <v>533</v>
+        <v>428</v>
       </c>
       <c r="I237" t="s">
-        <v>527</v>
+        <v>429</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>415</v>
+        <v>530</v>
       </c>
       <c r="B238" t="s">
-        <v>416</v>
+        <v>531</v>
       </c>
       <c r="C238" t="s">
-        <v>282</v>
+        <v>173</v>
       </c>
       <c r="E238" t="s">
-        <v>351</v>
+        <v>223</v>
       </c>
       <c r="F238">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G238" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H238" t="s">
-        <v>438</v>
+        <v>36</v>
       </c>
       <c r="I238" t="s">
-        <v>439</v>
+        <v>399</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B239" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C239" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E239" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F239">
         <v>2.0</v>
       </c>
       <c r="G239" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H239" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="I239" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B240" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C240" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E240" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F240">
         <v>2.0</v>
       </c>
       <c r="G240" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H240" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="I240" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="B241" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="C241" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="E241" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="F241">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G241" t="s">
-        <v>538</v>
+        <v>36</v>
       </c>
       <c r="H241" t="s">
-        <v>539</v>
+        <v>36</v>
       </c>
       <c r="I241" t="s">
-        <v>262</v>
+        <v>429</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B242" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C242" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E242" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F242">
         <v>2.0</v>
       </c>
       <c r="G242" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H242" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="I242" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="B243" t="s">
-        <v>541</v>
+        <v>508</v>
       </c>
       <c r="C243" t="s">
         <v>173</v>
       </c>
       <c r="E243" t="s">
-        <v>226</v>
+        <v>434</v>
       </c>
       <c r="F243">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G243" t="s">
-        <v>36</v>
+        <v>483</v>
       </c>
       <c r="H243" t="s">
-        <v>36</v>
+        <v>536</v>
       </c>
       <c r="I243" t="s">
-        <v>406</v>
+        <v>352</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>500</v>
+        <v>314</v>
       </c>
       <c r="B244" t="s">
-        <v>501</v>
+        <v>315</v>
       </c>
       <c r="C244" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="E244" t="s">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="F244">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G244" t="s">
         <v>36</v>
@@ -8462,50 +8447,50 @@
         <v>36</v>
       </c>
       <c r="I244" t="s">
-        <v>439</v>
+        <v>226</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="B245" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="C245" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="E245" t="s">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="F245">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G245" t="s">
-        <v>488</v>
+        <v>36</v>
       </c>
       <c r="H245" t="s">
-        <v>542</v>
+        <v>36</v>
       </c>
       <c r="I245" t="s">
-        <v>365</v>
+        <v>537</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>319</v>
+        <v>497</v>
       </c>
       <c r="B246" t="s">
-        <v>320</v>
+        <v>498</v>
       </c>
       <c r="C246" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="E246" t="s">
-        <v>226</v>
+        <v>434</v>
       </c>
       <c r="F246">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G246" t="s">
         <v>36</v>
@@ -8514,154 +8499,154 @@
         <v>36</v>
       </c>
       <c r="I246" t="s">
-        <v>229</v>
+        <v>396</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B247" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C247" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E247" t="s">
-        <v>226</v>
+        <v>434</v>
       </c>
       <c r="F247">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="G247" t="s">
-        <v>36</v>
+        <v>538</v>
       </c>
       <c r="H247" t="s">
-        <v>36</v>
+        <v>539</v>
       </c>
       <c r="I247" t="s">
-        <v>543</v>
+        <v>425</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B248" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C248" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E248" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F248">
         <v>2.0</v>
       </c>
       <c r="G248" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H248" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="I248" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="B249" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="C249" t="s">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="E249" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F249">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G249" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="H249" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="I249" t="s">
-        <v>401</v>
+        <v>523</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>502</v>
+        <v>320</v>
       </c>
       <c r="B250" t="s">
-        <v>503</v>
+        <v>321</v>
       </c>
       <c r="C250" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="E250" t="s">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="F250">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="G250" t="s">
-        <v>546</v>
+        <v>36</v>
       </c>
       <c r="H250" t="s">
-        <v>547</v>
+        <v>36</v>
       </c>
       <c r="I250" t="s">
-        <v>418</v>
+        <v>234</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="B251" t="s">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="C251" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="E251" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F251">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G251" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H251" t="s">
-        <v>352</v>
+        <v>428</v>
       </c>
       <c r="I251" t="s">
-        <v>529</v>
+        <v>449</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="B252" t="s">
-        <v>326</v>
+        <v>451</v>
       </c>
       <c r="C252" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="E252" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="F252">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G252" t="s">
         <v>36</v>
@@ -8670,102 +8655,102 @@
         <v>36</v>
       </c>
       <c r="I252" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>548</v>
+        <v>442</v>
       </c>
       <c r="B253" t="s">
-        <v>549</v>
+        <v>443</v>
       </c>
       <c r="C253" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E253" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F253">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G253" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H253" t="s">
-        <v>438</v>
+        <v>359</v>
       </c>
       <c r="I253" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>440</v>
+        <v>515</v>
       </c>
       <c r="B254" t="s">
-        <v>441</v>
+        <v>516</v>
       </c>
       <c r="C254" t="s">
-        <v>282</v>
+        <v>148</v>
       </c>
       <c r="E254" t="s">
-        <v>351</v>
+        <v>223</v>
       </c>
       <c r="F254">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G254" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H254" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="I254" t="s">
-        <v>479</v>
+        <v>226</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>456</v>
+        <v>507</v>
       </c>
       <c r="B255" t="s">
-        <v>457</v>
+        <v>508</v>
       </c>
       <c r="C255" t="s">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="E255" t="s">
-        <v>177</v>
+        <v>434</v>
       </c>
       <c r="F255">
         <v>4.0</v>
       </c>
       <c r="G255" t="s">
-        <v>36</v>
+        <v>526</v>
       </c>
       <c r="H255" t="s">
-        <v>36</v>
+        <v>366</v>
       </c>
       <c r="I255" t="s">
-        <v>179</v>
+        <v>429</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="B256" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="C256" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="E256" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F256">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G256" t="s">
         <v>36</v>
@@ -8774,177 +8759,177 @@
         <v>36</v>
       </c>
       <c r="I256" t="s">
-        <v>229</v>
+        <v>316</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B257" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C257" t="s">
-        <v>148</v>
+        <v>343</v>
       </c>
       <c r="E257" t="s">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="F257">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G257" t="s">
-        <v>532</v>
+        <v>359</v>
       </c>
       <c r="H257" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="I257" t="s">
-        <v>439</v>
+        <v>523</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>494</v>
+        <v>534</v>
       </c>
       <c r="B258" t="s">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="C258" t="s">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="E258" t="s">
-        <v>226</v>
+        <v>358</v>
       </c>
       <c r="F258">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G258" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="H258" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="I258" t="s">
-        <v>321</v>
+        <v>523</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B259" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C259" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="E259" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F259">
         <v>1.0</v>
       </c>
       <c r="G259" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H259" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="I259" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B260" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C260" t="s">
-        <v>337</v>
+        <v>262</v>
       </c>
       <c r="E260" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F260">
         <v>1.0</v>
       </c>
       <c r="G260" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H260" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="I260" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B261" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C261" t="s">
-        <v>337</v>
+        <v>206</v>
       </c>
       <c r="E261" t="s">
-        <v>351</v>
+        <v>223</v>
       </c>
       <c r="F261">
         <v>1.0</v>
       </c>
       <c r="G261" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H261" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="I261" t="s">
-        <v>529</v>
+        <v>399</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>536</v>
+        <v>320</v>
       </c>
       <c r="B262" t="s">
-        <v>537</v>
+        <v>321</v>
       </c>
       <c r="C262" t="s">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="E262" t="s">
-        <v>351</v>
+        <v>223</v>
       </c>
       <c r="F262">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G262" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H262" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="I262" t="s">
-        <v>529</v>
+        <v>316</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>521</v>
+        <v>544</v>
       </c>
       <c r="B263" t="s">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="C263" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="E263" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="F263">
         <v>1.0</v>
@@ -8956,24 +8941,24 @@
         <v>36</v>
       </c>
       <c r="I263" t="s">
-        <v>406</v>
+        <v>199</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B264" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C264" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E264" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F264">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G264" t="s">
         <v>36</v>
@@ -8982,154 +8967,154 @@
         <v>36</v>
       </c>
       <c r="I264" t="s">
-        <v>321</v>
+        <v>537</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="B265" t="s">
-        <v>551</v>
+        <v>518</v>
       </c>
       <c r="C265" t="s">
-        <v>182</v>
+        <v>278</v>
       </c>
       <c r="E265" t="s">
-        <v>177</v>
+        <v>358</v>
       </c>
       <c r="F265">
         <v>1.0</v>
       </c>
       <c r="G265" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="H265" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="I265" t="s">
-        <v>200</v>
+        <v>523</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>325</v>
+        <v>542</v>
       </c>
       <c r="B266" t="s">
-        <v>326</v>
+        <v>543</v>
       </c>
       <c r="C266" t="s">
-        <v>148</v>
+        <v>332</v>
       </c>
       <c r="E266" t="s">
-        <v>226</v>
+        <v>358</v>
       </c>
       <c r="F266">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G266" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="H266" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="I266" t="s">
-        <v>543</v>
+        <v>447</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="B267" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C267" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E267" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F267">
         <v>1.0</v>
       </c>
       <c r="G267" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H267" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="I267" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="B268" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="C268" t="s">
-        <v>337</v>
+        <v>148</v>
       </c>
       <c r="E268" t="s">
-        <v>351</v>
+        <v>177</v>
       </c>
       <c r="F268">
         <v>1.0</v>
       </c>
       <c r="G268" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H268" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="I268" t="s">
-        <v>479</v>
+        <v>199</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>523</v>
+        <v>339</v>
       </c>
       <c r="B269" t="s">
-        <v>524</v>
+        <v>340</v>
       </c>
       <c r="C269" t="s">
-        <v>282</v>
+        <v>148</v>
       </c>
       <c r="E269" t="s">
-        <v>351</v>
+        <v>223</v>
       </c>
       <c r="F269">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G269" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="H269" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="I269" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>550</v>
+        <v>495</v>
       </c>
       <c r="B270" t="s">
-        <v>551</v>
+        <v>496</v>
       </c>
       <c r="C270" t="s">
         <v>148</v>
       </c>
       <c r="E270" t="s">
-        <v>177</v>
+        <v>434</v>
       </c>
       <c r="F270">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G270" t="s">
         <v>36</v>
@@ -9138,24 +9123,24 @@
         <v>36</v>
       </c>
       <c r="I270" t="s">
-        <v>200</v>
+        <v>499</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>344</v>
+        <v>546</v>
       </c>
       <c r="B271" t="s">
-        <v>345</v>
+        <v>547</v>
       </c>
       <c r="C271" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="E271" t="s">
-        <v>226</v>
+        <v>548</v>
       </c>
       <c r="F271">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G271" t="s">
         <v>36</v>
@@ -9164,24 +9149,24 @@
         <v>36</v>
       </c>
       <c r="I271" t="s">
-        <v>543</v>
+        <v>204</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>500</v>
+        <v>549</v>
       </c>
       <c r="B272" t="s">
-        <v>501</v>
+        <v>550</v>
       </c>
       <c r="C272" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="E272" t="s">
-        <v>445</v>
+        <v>551</v>
       </c>
       <c r="F272">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G272" t="s">
         <v>36</v>
@@ -9190,7 +9175,7 @@
         <v>36</v>
       </c>
       <c r="I272" t="s">
-        <v>504</v>
+        <v>271</v>
       </c>
     </row>
     <row r="273" spans="1:9">
@@ -9200,14 +9185,11 @@
       <c r="B273" t="s">
         <v>553</v>
       </c>
-      <c r="C273" t="s">
-        <v>173</v>
-      </c>
       <c r="E273" t="s">
         <v>554</v>
       </c>
       <c r="F273">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G273" t="s">
         <v>36</v>
@@ -9216,21 +9198,18 @@
         <v>36</v>
       </c>
       <c r="I273" t="s">
-        <v>205</v>
+        <v>555</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>556</v>
-      </c>
-      <c r="C274" t="s">
-        <v>182</v>
+        <v>557</v>
       </c>
       <c r="E274" t="s">
-        <v>557</v>
+        <v>107</v>
       </c>
       <c r="F274">
         <v>1.0</v>
@@ -9242,7 +9221,7 @@
         <v>36</v>
       </c>
       <c r="I274" t="s">
-        <v>275</v>
+        <v>112</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -9253,10 +9232,10 @@
         <v>559</v>
       </c>
       <c r="E275" t="s">
-        <v>560</v>
+        <v>421</v>
       </c>
       <c r="F275">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G275" t="s">
         <v>36</v>
@@ -9265,18 +9244,18 @@
         <v>36</v>
       </c>
       <c r="I275" t="s">
-        <v>561</v>
+        <v>347</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B276" t="s">
-        <v>563</v>
+        <v>106</v>
       </c>
       <c r="E276" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F276">
         <v>1.0</v>
@@ -9293,16 +9272,19 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B277" t="s">
-        <v>565</v>
+        <v>562</v>
+      </c>
+      <c r="C277" t="s">
+        <v>148</v>
       </c>
       <c r="E277" t="s">
-        <v>432</v>
+        <v>139</v>
       </c>
       <c r="F277">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G277" t="s">
         <v>36</v>
@@ -9311,21 +9293,24 @@
         <v>36</v>
       </c>
       <c r="I277" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B278" t="s">
-        <v>106</v>
+        <v>562</v>
+      </c>
+      <c r="C278" t="s">
+        <v>138</v>
       </c>
       <c r="E278" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="F278">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G278" t="s">
         <v>36</v>
@@ -9334,24 +9319,24 @@
         <v>36</v>
       </c>
       <c r="I278" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>567</v>
+        <v>450</v>
       </c>
       <c r="B279" t="s">
-        <v>568</v>
+        <v>451</v>
       </c>
       <c r="C279" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="E279" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F279">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G279" t="s">
         <v>36</v>
@@ -9360,24 +9345,24 @@
         <v>36</v>
       </c>
       <c r="I279" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B280" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C280" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="E280" t="s">
-        <v>139</v>
+        <v>565</v>
       </c>
       <c r="F280">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G280" t="s">
         <v>36</v>
@@ -9386,24 +9371,24 @@
         <v>36</v>
       </c>
       <c r="I280" t="s">
-        <v>155</v>
+        <v>566</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>456</v>
+        <v>377</v>
       </c>
       <c r="B281" t="s">
-        <v>457</v>
+        <v>378</v>
       </c>
       <c r="C281" t="s">
         <v>173</v>
       </c>
       <c r="E281" t="s">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="F281">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G281" t="s">
         <v>36</v>
@@ -9412,24 +9397,24 @@
         <v>36</v>
       </c>
       <c r="I281" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="B282" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="C282" t="s">
         <v>173</v>
       </c>
       <c r="E282" t="s">
-        <v>571</v>
+        <v>223</v>
       </c>
       <c r="F282">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G282" t="s">
         <v>36</v>
@@ -9438,21 +9423,21 @@
         <v>36</v>
       </c>
       <c r="I282" t="s">
-        <v>572</v>
+        <v>537</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>382</v>
+        <v>320</v>
       </c>
       <c r="B283" t="s">
-        <v>383</v>
+        <v>321</v>
       </c>
       <c r="C283" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="E283" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="F283">
         <v>1.0</v>
@@ -9464,24 +9449,24 @@
         <v>36</v>
       </c>
       <c r="I283" t="s">
-        <v>234</v>
+        <v>399</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>521</v>
+        <v>339</v>
       </c>
       <c r="B284" t="s">
-        <v>522</v>
+        <v>340</v>
       </c>
       <c r="C284" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="E284" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F284">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G284" t="s">
         <v>36</v>
@@ -9490,24 +9475,24 @@
         <v>36</v>
       </c>
       <c r="I284" t="s">
-        <v>543</v>
+        <v>316</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>325</v>
+        <v>489</v>
       </c>
       <c r="B285" t="s">
-        <v>326</v>
+        <v>490</v>
       </c>
       <c r="C285" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E285" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F285">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G285" t="s">
         <v>36</v>
@@ -9516,24 +9501,24 @@
         <v>36</v>
       </c>
       <c r="I285" t="s">
-        <v>406</v>
+        <v>234</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>344</v>
+        <v>495</v>
       </c>
       <c r="B286" t="s">
-        <v>345</v>
+        <v>496</v>
       </c>
       <c r="C286" t="s">
         <v>138</v>
       </c>
       <c r="E286" t="s">
-        <v>226</v>
+        <v>434</v>
       </c>
       <c r="F286">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G286" t="s">
         <v>36</v>
@@ -9542,24 +9527,24 @@
         <v>36</v>
       </c>
       <c r="I286" t="s">
-        <v>321</v>
+        <v>567</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="B287" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C287" t="s">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="E287" t="s">
-        <v>226</v>
+        <v>434</v>
       </c>
       <c r="F287">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G287" t="s">
         <v>36</v>
@@ -9568,24 +9553,24 @@
         <v>36</v>
       </c>
       <c r="I287" t="s">
-        <v>237</v>
+        <v>511</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>500</v>
+        <v>466</v>
       </c>
       <c r="B288" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="C288" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="E288" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="F288">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="G288" t="s">
         <v>36</v>
@@ -9594,24 +9579,24 @@
         <v>36</v>
       </c>
       <c r="I288" t="s">
-        <v>573</v>
+        <v>352</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="B289" t="s">
-        <v>478</v>
+        <v>525</v>
       </c>
       <c r="C289" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E289" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="F289">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G289" t="s">
         <v>36</v>
@@ -9620,24 +9605,21 @@
         <v>36</v>
       </c>
       <c r="I289" t="s">
-        <v>517</v>
+        <v>435</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>471</v>
+        <v>568</v>
       </c>
       <c r="B290" t="s">
-        <v>472</v>
-      </c>
-      <c r="C290" t="s">
-        <v>173</v>
+        <v>569</v>
       </c>
       <c r="E290" t="s">
-        <v>445</v>
+        <v>570</v>
       </c>
       <c r="F290">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G290" t="s">
         <v>36</v>
@@ -9646,21 +9628,18 @@
         <v>36</v>
       </c>
       <c r="I290" t="s">
-        <v>365</v>
+        <v>178</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>530</v>
+        <v>571</v>
       </c>
       <c r="B291" t="s">
-        <v>531</v>
-      </c>
-      <c r="C291" t="s">
-        <v>138</v>
+        <v>572</v>
       </c>
       <c r="E291" t="s">
-        <v>445</v>
+        <v>570</v>
       </c>
       <c r="F291">
         <v>1.0</v>
@@ -9672,18 +9651,18 @@
         <v>36</v>
       </c>
       <c r="I291" t="s">
-        <v>446</v>
+        <v>257</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
+        <v>573</v>
+      </c>
+      <c r="B292" t="s">
         <v>574</v>
       </c>
-      <c r="B292" t="s">
-        <v>575</v>
-      </c>
       <c r="E292" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="F292">
         <v>2.0</v>
@@ -9695,18 +9674,18 @@
         <v>36</v>
       </c>
       <c r="I292" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B293" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E293" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="F293">
         <v>1.0</v>
@@ -9718,21 +9697,21 @@
         <v>36</v>
       </c>
       <c r="I293" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B294" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E294" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="F294">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G294" t="s">
         <v>36</v>
@@ -9741,44 +9720,47 @@
         <v>36</v>
       </c>
       <c r="I294" t="s">
-        <v>309</v>
+        <v>77</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
+        <v>579</v>
+      </c>
+      <c r="B295" t="s">
+        <v>580</v>
+      </c>
+      <c r="E295" t="s">
+        <v>570</v>
+      </c>
+      <c r="F295">
+        <v>1.0</v>
+      </c>
+      <c r="G295" t="s">
+        <v>36</v>
+      </c>
+      <c r="H295" t="s">
+        <v>36</v>
+      </c>
+      <c r="I295" t="s">
         <v>581</v>
-      </c>
-      <c r="B295" t="s">
-        <v>582</v>
-      </c>
-      <c r="E295" t="s">
-        <v>576</v>
-      </c>
-      <c r="F295">
-        <v>1.0</v>
-      </c>
-      <c r="G295" t="s">
-        <v>36</v>
-      </c>
-      <c r="H295" t="s">
-        <v>36</v>
-      </c>
-      <c r="I295" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>583</v>
+        <v>491</v>
       </c>
       <c r="B296" t="s">
-        <v>584</v>
+        <v>492</v>
+      </c>
+      <c r="C296" t="s">
+        <v>343</v>
       </c>
       <c r="E296" t="s">
-        <v>576</v>
+        <v>493</v>
       </c>
       <c r="F296">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G296" t="s">
         <v>36</v>
@@ -9787,21 +9769,24 @@
         <v>36</v>
       </c>
       <c r="I296" t="s">
-        <v>448</v>
+        <v>494</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>585</v>
+        <v>491</v>
       </c>
       <c r="B297" t="s">
-        <v>586</v>
+        <v>492</v>
+      </c>
+      <c r="C297" t="s">
+        <v>244</v>
       </c>
       <c r="E297" t="s">
-        <v>576</v>
+        <v>493</v>
       </c>
       <c r="F297">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G297" t="s">
         <v>36</v>
@@ -9810,21 +9795,21 @@
         <v>36</v>
       </c>
       <c r="I297" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B298" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C298" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="E298" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F298">
         <v>3.0</v>
@@ -9836,24 +9821,24 @@
         <v>36</v>
       </c>
       <c r="I298" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>496</v>
+        <v>583</v>
       </c>
       <c r="B299" t="s">
-        <v>497</v>
+        <v>584</v>
       </c>
       <c r="C299" t="s">
-        <v>248</v>
+        <v>343</v>
       </c>
       <c r="E299" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F299">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G299" t="s">
         <v>36</v>
@@ -9862,24 +9847,24 @@
         <v>36</v>
       </c>
       <c r="I299" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
-        <v>496</v>
+        <v>583</v>
       </c>
       <c r="B300" t="s">
-        <v>497</v>
+        <v>584</v>
       </c>
       <c r="C300" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E300" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F300">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G300" t="s">
         <v>36</v>
@@ -9888,21 +9873,21 @@
         <v>36</v>
       </c>
       <c r="I300" t="s">
-        <v>499</v>
+        <v>586</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B301" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C301" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="E301" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F301">
         <v>4.0</v>
@@ -9914,24 +9899,24 @@
         <v>36</v>
       </c>
       <c r="I301" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B302" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C302" t="s">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="E302" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F302">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G302" t="s">
         <v>36</v>
@@ -9940,24 +9925,24 @@
         <v>36</v>
       </c>
       <c r="I302" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B303" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C303" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="E303" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F303">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G303" t="s">
         <v>36</v>
@@ -9966,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="I303" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="304" spans="1:9">
@@ -9977,13 +9962,13 @@
         <v>590</v>
       </c>
       <c r="C304" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="E304" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F304">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G304" t="s">
         <v>36</v>
@@ -9997,19 +9982,19 @@
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B305" t="s">
         <v>590</v>
       </c>
       <c r="C305" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E305" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F305">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G305" t="s">
         <v>36</v>
@@ -10018,24 +10003,24 @@
         <v>36</v>
       </c>
       <c r="I305" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B306" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C306" t="s">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="E306" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F306">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G306" t="s">
         <v>36</v>
@@ -10044,21 +10029,21 @@
         <v>36</v>
       </c>
       <c r="I306" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B307" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C307" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="E307" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F307">
         <v>2.0</v>
@@ -10070,24 +10055,24 @@
         <v>36</v>
       </c>
       <c r="I307" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
+        <v>594</v>
+      </c>
+      <c r="B308" t="s">
         <v>595</v>
       </c>
-      <c r="B308" t="s">
-        <v>596</v>
-      </c>
       <c r="C308" t="s">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="E308" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F308">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G308" t="s">
         <v>36</v>
@@ -10096,24 +10081,24 @@
         <v>36</v>
       </c>
       <c r="I308" t="s">
-        <v>599</v>
+        <v>523</v>
       </c>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B309" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C309" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="E309" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F309">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G309" t="s">
         <v>36</v>
@@ -10122,24 +10107,24 @@
         <v>36</v>
       </c>
       <c r="I309" t="s">
-        <v>598</v>
+        <v>325</v>
       </c>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B310" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C310" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="E310" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F310">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G310" t="s">
         <v>36</v>
@@ -10148,24 +10133,24 @@
         <v>36</v>
       </c>
       <c r="I310" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B311" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C311" t="s">
-        <v>348</v>
+        <v>244</v>
       </c>
       <c r="E311" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F311">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G311" t="s">
         <v>36</v>
@@ -10174,21 +10159,21 @@
         <v>36</v>
       </c>
       <c r="I311" t="s">
-        <v>330</v>
+        <v>601</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B312" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="C312" t="s">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="E312" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F312">
         <v>2.0</v>
@@ -10200,24 +10185,24 @@
         <v>36</v>
       </c>
       <c r="I312" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B313" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="C313" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E313" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F313">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G313" t="s">
         <v>36</v>
@@ -10226,24 +10211,24 @@
         <v>36</v>
       </c>
       <c r="I313" t="s">
-        <v>607</v>
+        <v>325</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B314" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C314" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E314" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F314">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G314" t="s">
         <v>36</v>
@@ -10252,21 +10237,21 @@
         <v>36</v>
       </c>
       <c r="I314" t="s">
-        <v>515</v>
+        <v>604</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B315" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C315" t="s">
-        <v>282</v>
+        <v>332</v>
       </c>
       <c r="E315" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F315">
         <v>1.0</v>
@@ -10278,24 +10263,24 @@
         <v>36</v>
       </c>
       <c r="I315" t="s">
-        <v>330</v>
+        <v>604</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B316" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C316" t="s">
-        <v>348</v>
+        <v>244</v>
       </c>
       <c r="E316" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F316">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G316" t="s">
         <v>36</v>
@@ -10304,21 +10289,21 @@
         <v>36</v>
       </c>
       <c r="I316" t="s">
-        <v>610</v>
+        <v>509</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B317" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C317" t="s">
-        <v>266</v>
+        <v>332</v>
       </c>
       <c r="E317" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F317">
         <v>1.0</v>
@@ -10330,21 +10315,21 @@
         <v>36</v>
       </c>
       <c r="I317" t="s">
-        <v>610</v>
+        <v>325</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
+        <v>607</v>
+      </c>
+      <c r="B318" t="s">
         <v>608</v>
       </c>
-      <c r="B318" t="s">
-        <v>609</v>
-      </c>
       <c r="C318" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E318" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F318">
         <v>1.0</v>
@@ -10356,24 +10341,24 @@
         <v>36</v>
       </c>
       <c r="I318" t="s">
-        <v>610</v>
+        <v>523</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B319" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C319" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E319" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F319">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G319" t="s">
         <v>36</v>
@@ -10382,21 +10367,21 @@
         <v>36</v>
       </c>
       <c r="I319" t="s">
-        <v>515</v>
+        <v>609</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B320" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C320" t="s">
-        <v>337</v>
+        <v>262</v>
       </c>
       <c r="E320" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F320">
         <v>1.0</v>
@@ -10408,24 +10393,24 @@
         <v>36</v>
       </c>
       <c r="I320" t="s">
-        <v>330</v>
+        <v>523</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B321" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C321" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="E321" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F321">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G321" t="s">
         <v>36</v>
@@ -10434,24 +10419,24 @@
         <v>36</v>
       </c>
       <c r="I321" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B322" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C322" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E322" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F322">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G322" t="s">
         <v>36</v>
@@ -10460,21 +10445,21 @@
         <v>36</v>
       </c>
       <c r="I322" t="s">
-        <v>615</v>
+        <v>519</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
-        <v>613</v>
+        <v>561</v>
       </c>
       <c r="B323" t="s">
-        <v>614</v>
+        <v>562</v>
       </c>
       <c r="C323" t="s">
-        <v>266</v>
+        <v>173</v>
       </c>
       <c r="E323" t="s">
-        <v>498</v>
+        <v>139</v>
       </c>
       <c r="F323">
         <v>1.0</v>
@@ -10486,24 +10471,24 @@
         <v>36</v>
       </c>
       <c r="I323" t="s">
-        <v>529</v>
+        <v>168</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B324" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C324" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="E324" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F324">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G324" t="s">
         <v>36</v>
@@ -10512,21 +10497,21 @@
         <v>36</v>
       </c>
       <c r="I324" t="s">
-        <v>529</v>
+        <v>591</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
-        <v>613</v>
+        <v>491</v>
       </c>
       <c r="B325" t="s">
-        <v>614</v>
+        <v>492</v>
       </c>
       <c r="C325" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E325" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F325">
         <v>2.0</v>
@@ -10538,85 +10523,7 @@
         <v>36</v>
       </c>
       <c r="I325" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9">
-      <c r="A326" t="s">
-        <v>567</v>
-      </c>
-      <c r="B326" t="s">
-        <v>568</v>
-      </c>
-      <c r="C326" t="s">
-        <v>173</v>
-      </c>
-      <c r="E326" t="s">
-        <v>139</v>
-      </c>
-      <c r="F326">
-        <v>1.0</v>
-      </c>
-      <c r="G326" t="s">
-        <v>36</v>
-      </c>
-      <c r="H326" t="s">
-        <v>36</v>
-      </c>
-      <c r="I326" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9">
-      <c r="A327" t="s">
-        <v>616</v>
-      </c>
-      <c r="B327" t="s">
-        <v>617</v>
-      </c>
-      <c r="C327" t="s">
-        <v>248</v>
-      </c>
-      <c r="E327" t="s">
-        <v>498</v>
-      </c>
-      <c r="F327">
-        <v>3.0</v>
-      </c>
-      <c r="G327" t="s">
-        <v>36</v>
-      </c>
-      <c r="H327" t="s">
-        <v>36</v>
-      </c>
-      <c r="I327" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="328" spans="1:9">
-      <c r="A328" t="s">
-        <v>496</v>
-      </c>
-      <c r="B328" t="s">
-        <v>497</v>
-      </c>
-      <c r="C328" t="s">
-        <v>282</v>
-      </c>
-      <c r="E328" t="s">
-        <v>498</v>
-      </c>
-      <c r="F328">
-        <v>2.0</v>
-      </c>
-      <c r="G328" t="s">
-        <v>36</v>
-      </c>
-      <c r="H328" t="s">
-        <v>36</v>
-      </c>
-      <c r="I328" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
